--- a/data/ontap111.xlsx
+++ b/data/ontap111.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tdtam\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D88F41A2-AAFB-4B72-9974-015E623A9083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBC6ED28-8440-4178-9B75-9438552A341F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="911">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="896">
   <si>
     <t>Họ tên</t>
   </si>
@@ -1172,18 +1172,6 @@
     <t>Theo em, phát biểu nào đúng, phát biểu nào sai khi nói về phần mềm máy tính?</t>
   </si>
   <si>
-    <t>A.Bucket Fill</t>
-  </si>
-  <si>
-    <t>Heal</t>
-  </si>
-  <si>
-    <t>Gradient</t>
-  </si>
-  <si>
-    <t>Clone</t>
-  </si>
-  <si>
     <t>Để xoá chi tiết thừa của một bức ảnh, ta chọn lệnh Tools – Selection Tools – Heal.</t>
   </si>
   <si>
@@ -1751,9 +1739,6 @@
     <t>Thanh trạng thái (Status Bar).</t>
   </si>
   <si>
-    <t>.</t>
-  </si>
-  <si>
     <t>Phần mềm cung cấp cả mã nguồn để người dùng có thể tự sửa đổi, cải tiến, phát triển.</t>
   </si>
   <si>
@@ -1796,9 +1781,6 @@
     <t>Không có cách nào khắc phục.</t>
   </si>
   <si>
-    <t>https://www.gimp.org/downloads/</t>
-  </si>
-  <si>
     <t>Windows 9.</t>
   </si>
   <si>
@@ -1949,9 +1931,6 @@
     <t>Card đồ họa.</t>
   </si>
   <si>
-    <t>https://www.gimp.vn/downloads/</t>
-  </si>
-  <si>
     <t>Windows 11.</t>
   </si>
   <si>
@@ -2099,9 +2078,6 @@
     <t>Vẽ thêm những phần bị khuyết.</t>
   </si>
   <si>
-    <t>https://www.gim.org/downloads/</t>
-  </si>
-  <si>
     <t>Windows 8.</t>
   </si>
   <si>
@@ -2252,9 +2228,6 @@
     <t>Ổ cứng.</t>
   </si>
   <si>
-    <t>https://www.gimp.org/download</t>
-  </si>
-  <si>
     <t>Windows 10.</t>
   </si>
   <si>
@@ -2387,9 +2360,6 @@
     <t>Thanh chứa các thành phần sau trên màn hình làm việc của Windows được gọi là gì:</t>
   </si>
   <si>
-    <t>Để truy cập vào tiện ích quản lý ứng dụng cho thiết bị thông minh (điện thoại thông minh, máy tính bảng), em sẽ chọn biểu tượng nào?</t>
-  </si>
-  <si>
     <t>Phần mềm nguồn mở là?</t>
   </si>
   <si>
@@ -2444,12 +2414,6 @@
     <t>Bộ phận nào trong máy tính được ví như "não bộ", thực hiện các phép tính và điều khiển hoạt động của máy?</t>
   </si>
   <si>
-    <t>Trong GIMP, để sao chép pha trộn vùng chọn và vùng cần vẽ, ta vào menu Tools – Paint Tools, chọn lệnh nào sau đây?</t>
-  </si>
-  <si>
-    <t>Để tải và cài đặt phần mềm chỉnh sửa ảnh GIMP, truy cập vào địa chỉ nào sau đây?</t>
-  </si>
-  <si>
     <t>Phiên bản hệ điều hành nào là không có trong lịch sử phát triển của hệ điều hành Windows?</t>
   </si>
   <si>
@@ -2483,9 +2447,6 @@
     <t>Em hãy chọn phép tính nhị phân đúng nhất?</t>
   </si>
   <si>
-    <t>Hãy đổi số nhị phân 11012 sau sang số thập phân?</t>
-  </si>
-  <si>
     <t>Phép toán 110 + 111 cho kết quả nào sau đây?</t>
   </si>
   <si>
@@ -2567,658 +2528,229 @@
     <t>Hiện nay, việc sử dụng mạng internet để trao đổi thông tin rất phổ biến. Có nhiều ứng dụng để thực hiện gửi thư điện tử và mạng xã hội. Trong đó, sử dụng phổ biến nhất là gmail và facebook.</t>
   </si>
   <si>
+    <t> Chuyển phép tính cộng 13 + 17 = 30 trong hệ đếm thập phân sang hệ nhị phân, ta được</t>
+  </si>
+  <si>
+    <t>1111 + 1010 = 11101</t>
+  </si>
+  <si>
+    <t>1101 + 10001 = 11110</t>
+  </si>
+  <si>
+    <t>1101 + 10101 = 101101</t>
+  </si>
+  <si>
+    <t>10101 + 1000 = 101101</t>
+  </si>
+  <si>
+    <t>Cộng các số nhị phân 101000 + 110010, sau đó chuyển kết quả sang hệ thập phân ta được:</t>
+  </si>
+  <si>
+    <t>Máy chiếu</t>
+  </si>
+  <si>
+    <t>Tai nghe</t>
+  </si>
+  <si>
+    <t>Biết một màn hình có kích thước chiều dài và chiều rộng là 35.9 cm × 24.7 cm, hỏi màn hình đó có kích thước bao nhiêu inch? Biết 1 inch ≈ 2,54 cm.</t>
+  </si>
+  <si>
+    <t> 17.2 inch</t>
+  </si>
+  <si>
+    <t>17 inch</t>
+  </si>
+  <si>
+    <t>16.2 inch</t>
+  </si>
+  <si>
+    <t>Để in hóa đơn bán hàng, em dùng máy in</t>
+  </si>
+  <si>
+    <t>Kim</t>
+  </si>
+  <si>
+    <t>Laser</t>
+  </si>
+  <si>
+    <t>Phun</t>
+  </si>
+  <si>
+    <t>Nhiệt.</t>
+  </si>
+  <si>
+    <t>Theo em, nhược điểm của lưu trữ trực tuyến là gì?</t>
+  </si>
+  <si>
+    <t>Phải có Internet mới sử dụng được.</t>
+  </si>
+  <si>
+    <t>Không hạn chế thiết bị nhớ ngoài.</t>
+  </si>
+  <si>
+    <t>Không giới hạn số người được truy cập.</t>
+  </si>
+  <si>
+    <t>Sử dụng các tệp, thư mục dùng chung.</t>
+  </si>
+  <si>
+    <t>Em cần nhập từ khóa gì nếu muốn tìm thông tin về Hươu Sao?</t>
+  </si>
+  <si>
+    <t>Hươu.</t>
+  </si>
+  <si>
+    <t>Sao.</t>
+  </si>
+  <si>
+    <t>Hươu Sao.</t>
+  </si>
+  <si>
+    <t>Động vật.</t>
+  </si>
+  <si>
+    <t>Có thể dùng từ khóa tìm kiếm nào để hiển thị danh sách thư điện tử quan trọng?</t>
+  </si>
+  <si>
+    <t>Cancel.</t>
+  </si>
+  <si>
+    <t>VIP.</t>
+  </si>
+  <si>
+    <t>Important.</t>
+  </si>
+  <si>
+    <t>Close.</t>
+  </si>
+  <si>
+    <t>Em có thể cài đặt bảo mật hai lớp trên Facebook bằng cách:</t>
+  </si>
+  <si>
+    <t>Thêm số điện thoại để xác nhận mật khẩu khi đăng nhập trên thiết bị khác.</t>
+  </si>
+  <si>
+    <t>Mua điện thoại mới có tính bảo mật tốt hơn.</t>
+  </si>
+  <si>
+    <t>Corona.  </t>
+  </si>
+  <si>
+    <t>Virus Corona.   </t>
+  </si>
+  <si>
+    <t>“Virus Corona”. </t>
+  </si>
+  <si>
+    <t>Q133</t>
+  </si>
+  <si>
+    <t>Q134</t>
+  </si>
+  <si>
+    <t>Q135</t>
+  </si>
+  <si>
+    <t>Q136</t>
+  </si>
+  <si>
+    <t>Q137</t>
+  </si>
+  <si>
+    <t>Q138</t>
+  </si>
+  <si>
+    <t>Q139</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>1001</t>
+  </si>
+  <si>
+    <t>10000</t>
+  </si>
+  <si>
+    <t>110000</t>
+  </si>
+  <si>
+    <t>100110</t>
+  </si>
+  <si>
+    <t>110110</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>Tính 10 + 01 trong hệ nhị phân.</t>
+  </si>
+  <si>
+    <t>Thực hiện phép tính trên hệ nhị phân: 10100 + 111 trong hệ nhị phân.</t>
+  </si>
+  <si>
+    <t>Thực hiện phép tính trên hệ nhị phân: 11100 + 1010 trong hệ nhị phân.</t>
+  </si>
+  <si>
+    <t>Giá trị của số 111010 là bao nhiêu sang hệ thập phân:?</t>
+  </si>
+  <si>
+    <t>Tính 10101 + 11011 trong hệ nhị phân.</t>
+  </si>
+  <si>
+    <t>Tính 1111 + 0001 trong hệ nhị phân.</t>
+  </si>
+  <si>
+    <t>Tính 1011 + 0101 trong hệ nhị phân.</t>
+  </si>
+  <si>
+    <t>Tính 110 + 011 trong hệ nhị phân.</t>
+  </si>
+  <si>
+    <t>Trong phép cộng trong hệ nhị phân: 1+1+1=11</t>
+  </si>
+  <si>
+    <t>Trong phép cộng trong hệ nhị phân: 1+1=10</t>
+  </si>
+  <si>
+    <t>Hãy đổi số nhị phân 1101 sau sang số thập phân?</t>
+  </si>
+  <si>
     <r>
-      <t>Trong phép cộng nhị phân, 1+1=10</t>
+      <t>Kết quả của phép cộng trong hệ nhị phân: 101</t>
     </r>
     <r>
       <rPr>
         <b/>
         <vertAlign val="subscript"/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Trong phép cộng nhị phân, 1+1+1=11</t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
         <b/>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>2</t>
+      <t>+ 010 là 111</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <t>Kết quả của phép cộng 101</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">2 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>+ 010</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> là 111</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>0</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Tính 10</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> + 01</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>11</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Tính 110</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> + 011</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1001</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Tính 1011</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> + 0101</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>10000</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Tính 1111</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> + 0001</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Tính 10101</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> + 11011</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>110000</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Thực hiện phép tính trên hệ nhị phân: 11100</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> + 1010</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>100110</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Thực hiện phép tính trên hệ nhị phân: 10100</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> + 111</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>110110</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Giá trị của số 111010</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> là bao nhiêu sang hệ thập phân:?</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>58</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <vertAlign val="subscript"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>10</t>
-    </r>
-  </si>
-  <si>
-    <t> Chuyển phép tính cộng 13 + 17 = 30 trong hệ đếm thập phân sang hệ nhị phân, ta được</t>
-  </si>
-  <si>
-    <t>1111 + 1010 = 11101</t>
-  </si>
-  <si>
-    <t>1101 + 10001 = 11110</t>
-  </si>
-  <si>
-    <t>1101 + 10101 = 101101</t>
-  </si>
-  <si>
-    <t>10101 + 1000 = 101101</t>
-  </si>
-  <si>
-    <t>Cộng các số nhị phân 101000 + 110010, sau đó chuyển kết quả sang hệ thập phân ta được:</t>
-  </si>
-  <si>
-    <t>Máy chiếu</t>
-  </si>
-  <si>
-    <t>Tai nghe</t>
-  </si>
-  <si>
-    <t>Biết một màn hình có kích thước chiều dài và chiều rộng là 35.9 cm × 24.7 cm, hỏi màn hình đó có kích thước bao nhiêu inch? Biết 1 inch ≈ 2,54 cm.</t>
-  </si>
-  <si>
-    <t> 17.2 inch</t>
-  </si>
-  <si>
-    <t>17 inch</t>
-  </si>
-  <si>
-    <t>16.2 inch</t>
-  </si>
-  <si>
-    <t>Để in hóa đơn bán hàng, em dùng máy in</t>
-  </si>
-  <si>
-    <t>Kim</t>
-  </si>
-  <si>
-    <t>Laser</t>
-  </si>
-  <si>
-    <t>Phun</t>
-  </si>
-  <si>
-    <t>Nhiệt.</t>
-  </si>
-  <si>
-    <t>Theo em, nhược điểm của lưu trữ trực tuyến là gì?</t>
-  </si>
-  <si>
-    <t>Phải có Internet mới sử dụng được.</t>
-  </si>
-  <si>
-    <t>Không hạn chế thiết bị nhớ ngoài.</t>
-  </si>
-  <si>
-    <t>Không giới hạn số người được truy cập.</t>
-  </si>
-  <si>
-    <t>Sử dụng các tệp, thư mục dùng chung.</t>
-  </si>
-  <si>
-    <t>Em cần nhập từ khóa gì nếu muốn tìm thông tin về Hươu Sao?</t>
-  </si>
-  <si>
-    <t>Hươu.</t>
-  </si>
-  <si>
-    <t>Sao.</t>
-  </si>
-  <si>
-    <t>Hươu Sao.</t>
-  </si>
-  <si>
-    <t>Động vật.</t>
-  </si>
-  <si>
-    <t>Có thể dùng từ khóa tìm kiếm nào để hiển thị danh sách thư điện tử quan trọng?</t>
-  </si>
-  <si>
-    <t>Cancel.</t>
-  </si>
-  <si>
-    <t>VIP.</t>
-  </si>
-  <si>
-    <t>Important.</t>
-  </si>
-  <si>
-    <t>Close.</t>
-  </si>
-  <si>
-    <t>Em có thể cài đặt bảo mật hai lớp trên Facebook bằng cách:</t>
-  </si>
-  <si>
-    <t>Thêm số điện thoại để xác nhận mật khẩu khi đăng nhập trên thiết bị khác.</t>
-  </si>
-  <si>
-    <t>Mua điện thoại mới có tính bảo mật tốt hơn.</t>
-  </si>
-  <si>
-    <t>Corona.  </t>
-  </si>
-  <si>
-    <t>Virus Corona.   </t>
-  </si>
-  <si>
-    <t>“Virus Corona”. </t>
-  </si>
-  <si>
-    <t>Q133</t>
-  </si>
-  <si>
-    <t>Q134</t>
-  </si>
-  <si>
-    <t>Q135</t>
-  </si>
-  <si>
-    <t>Q136</t>
-  </si>
-  <si>
-    <t>Q137</t>
-  </si>
-  <si>
-    <t>Q138</t>
-  </si>
-  <si>
-    <t>Q139</t>
-  </si>
-  <si>
-    <t>Q140</t>
-  </si>
-  <si>
-    <t>Q141</t>
-  </si>
-  <si>
-    <t>Q142</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3257,20 +2789,26 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -3278,13 +2816,6 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
       <color rgb="FF333333"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -3292,7 +2823,7 @@
     <font>
       <b/>
       <vertAlign val="subscript"/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -3343,7 +2874,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3356,52 +2887,32 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3423,255 +2934,11 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>355600</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>82550</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="4+ Đề thi Giữa kì 1 Tin học 11 Kết nối tri thức (cấu trúc mới, có đáp án)">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6827FB68-29C4-A19C-6CE1-83509BFA198D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="3619500" y="1790700"/>
-          <a:ext cx="355600" cy="438150"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>336550</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2" descr="4+ Đề thi Giữa kì 1 Tin học 11 Kết nối tri thức (cấu trúc mới, có đáp án)">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA4B14CF-1E30-B1FE-A7D9-D64615B2FAA3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="6064250" y="1790700"/>
-          <a:ext cx="336550" cy="381000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3" descr="4+ Đề thi Giữa kì 1 Tin học 11 Kết nối tri thức (cấu trúc mới, có đáp án)">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4E4070F-4E3F-D814-159C-B3921CDD78C2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="8020050" y="1790700"/>
-          <a:ext cx="342900" cy="381000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>374650</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4" descr="4+ Đề thi Giữa kì 1 Tin học 11 Kết nối tri thức (cấu trúc mới, có đáp án)">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD4F2E12-8FEF-E97B-0974-33962DAB21BA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="9975850" y="1790700"/>
-          <a:ext cx="374650" cy="450850"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>394446</xdr:colOff>
-      <xdr:row>135</xdr:row>
+      <xdr:row>132</xdr:row>
       <xdr:rowOff>5976</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="65" cy="172227"/>
@@ -4011,13 +3278,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B161"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="24" customHeight="1">
+    <row r="1" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4025,7 +3292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>191</v>
       </c>
@@ -4033,7 +3300,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>192</v>
       </c>
@@ -4041,7 +3308,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>193</v>
       </c>
@@ -4049,7 +3316,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>194</v>
       </c>
@@ -4057,7 +3324,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>195</v>
       </c>
@@ -4065,7 +3332,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>196</v>
       </c>
@@ -4073,7 +3340,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>197</v>
       </c>
@@ -4081,7 +3348,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>198</v>
       </c>
@@ -4089,7 +3356,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>199</v>
       </c>
@@ -4097,7 +3364,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>200</v>
       </c>
@@ -4105,7 +3372,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>201</v>
       </c>
@@ -4113,7 +3380,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>202</v>
       </c>
@@ -4121,7 +3388,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>203</v>
       </c>
@@ -4129,7 +3396,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>204</v>
       </c>
@@ -4137,7 +3404,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>205</v>
       </c>
@@ -4145,7 +3412,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>206</v>
       </c>
@@ -4153,7 +3420,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>207</v>
       </c>
@@ -4161,7 +3428,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>208</v>
       </c>
@@ -4169,7 +3436,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>209</v>
       </c>
@@ -4177,7 +3444,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>210</v>
       </c>
@@ -4185,7 +3452,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>211</v>
       </c>
@@ -4193,7 +3460,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>212</v>
       </c>
@@ -4201,7 +3468,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>213</v>
       </c>
@@ -4209,7 +3476,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>214</v>
       </c>
@@ -4217,7 +3484,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>215</v>
       </c>
@@ -4225,7 +3492,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>216</v>
       </c>
@@ -4233,7 +3500,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>217</v>
       </c>
@@ -4241,7 +3508,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>218</v>
       </c>
@@ -4249,7 +3516,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>219</v>
       </c>
@@ -4257,7 +3524,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>220</v>
       </c>
@@ -4265,7 +3532,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>221</v>
       </c>
@@ -4273,7 +3540,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>222</v>
       </c>
@@ -4281,7 +3548,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>223</v>
       </c>
@@ -4289,7 +3556,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>224</v>
       </c>
@@ -4297,7 +3564,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>225</v>
       </c>
@@ -4305,7 +3572,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>226</v>
       </c>
@@ -4313,7 +3580,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>228</v>
       </c>
@@ -4321,7 +3588,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>229</v>
       </c>
@@ -4329,7 +3596,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>230</v>
       </c>
@@ -4337,7 +3604,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>231</v>
       </c>
@@ -4345,7 +3612,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>232</v>
       </c>
@@ -4353,7 +3620,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>233</v>
       </c>
@@ -4361,7 +3628,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>234</v>
       </c>
@@ -4369,7 +3636,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>235</v>
       </c>
@@ -4377,7 +3644,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>236</v>
       </c>
@@ -4385,7 +3652,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>237</v>
       </c>
@@ -4393,7 +3660,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>238</v>
       </c>
@@ -4401,7 +3668,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>239</v>
       </c>
@@ -4409,7 +3676,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>240</v>
       </c>
@@ -4417,7 +3684,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>241</v>
       </c>
@@ -4425,7 +3692,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>242</v>
       </c>
@@ -4433,7 +3700,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>243</v>
       </c>
@@ -4441,7 +3708,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>244</v>
       </c>
@@ -4449,7 +3716,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>245</v>
       </c>
@@ -4457,7 +3724,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>246</v>
       </c>
@@ -4465,7 +3732,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>247</v>
       </c>
@@ -4473,7 +3740,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>248</v>
       </c>
@@ -4481,7 +3748,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>249</v>
       </c>
@@ -4489,7 +3756,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>250</v>
       </c>
@@ -4497,7 +3764,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>251</v>
       </c>
@@ -4505,7 +3772,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>252</v>
       </c>
@@ -4513,7 +3780,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>253</v>
       </c>
@@ -4521,7 +3788,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>254</v>
       </c>
@@ -4529,7 +3796,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>255</v>
       </c>
@@ -4537,7 +3804,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>256</v>
       </c>
@@ -4545,7 +3812,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>213</v>
       </c>
@@ -4553,7 +3820,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>257</v>
       </c>
@@ -4561,7 +3828,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>258</v>
       </c>
@@ -4569,7 +3836,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>259</v>
       </c>
@@ -4577,7 +3844,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>260</v>
       </c>
@@ -4585,7 +3852,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>261</v>
       </c>
@@ -4593,7 +3860,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>262</v>
       </c>
@@ -4601,7 +3868,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>263</v>
       </c>
@@ -4609,7 +3876,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>264</v>
       </c>
@@ -4617,7 +3884,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>266</v>
       </c>
@@ -4625,7 +3892,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>267</v>
       </c>
@@ -4633,7 +3900,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>268</v>
       </c>
@@ -4641,7 +3908,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>269</v>
       </c>
@@ -4649,7 +3916,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>270</v>
       </c>
@@ -4657,7 +3924,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>271</v>
       </c>
@@ -4665,7 +3932,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>272</v>
       </c>
@@ -4673,7 +3940,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>273</v>
       </c>
@@ -4681,7 +3948,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>274</v>
       </c>
@@ -4689,7 +3956,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>275</v>
       </c>
@@ -4697,7 +3964,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>276</v>
       </c>
@@ -4705,7 +3972,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>277</v>
       </c>
@@ -4713,7 +3980,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>278</v>
       </c>
@@ -4721,7 +3988,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>279</v>
       </c>
@@ -4729,7 +3996,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>280</v>
       </c>
@@ -4737,7 +4004,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>281</v>
       </c>
@@ -4745,7 +4012,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>282</v>
       </c>
@@ -4753,7 +4020,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>283</v>
       </c>
@@ -4761,7 +4028,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>284</v>
       </c>
@@ -4769,7 +4036,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>285</v>
       </c>
@@ -4777,7 +4044,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>286</v>
       </c>
@@ -4785,7 +4052,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="97" spans="1:2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>287</v>
       </c>
@@ -4793,7 +4060,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="98" spans="1:2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>288</v>
       </c>
@@ -4801,7 +4068,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="99" spans="1:2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>289</v>
       </c>
@@ -4809,7 +4076,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>257</v>
       </c>
@@ -4817,7 +4084,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>290</v>
       </c>
@@ -4825,7 +4092,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="102" spans="1:2">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>291</v>
       </c>
@@ -4833,7 +4100,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="103" spans="1:2">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>292</v>
       </c>
@@ -4841,7 +4108,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="104" spans="1:2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>293</v>
       </c>
@@ -4849,7 +4116,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="105" spans="1:2">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>294</v>
       </c>
@@ -4857,7 +4124,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="106" spans="1:2">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>295</v>
       </c>
@@ -4865,7 +4132,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="107" spans="1:2">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>296</v>
       </c>
@@ -4873,7 +4140,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="108" spans="1:2">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>297</v>
       </c>
@@ -4881,7 +4148,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="109" spans="1:2">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>298</v>
       </c>
@@ -4889,7 +4156,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="110" spans="1:2">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>299</v>
       </c>
@@ -4897,7 +4164,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="111" spans="1:2">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>300</v>
       </c>
@@ -4905,7 +4172,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="112" spans="1:2">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>301</v>
       </c>
@@ -4913,7 +4180,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="113" spans="1:2">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>302</v>
       </c>
@@ -4921,7 +4188,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="114" spans="1:2">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>304</v>
       </c>
@@ -4929,7 +4196,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="115" spans="1:2">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>305</v>
       </c>
@@ -4937,7 +4204,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="116" spans="1:2">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>306</v>
       </c>
@@ -4945,7 +4212,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="117" spans="1:2">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>307</v>
       </c>
@@ -4953,7 +4220,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="118" spans="1:2">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>308</v>
       </c>
@@ -4961,7 +4228,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="119" spans="1:2">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>309</v>
       </c>
@@ -4969,7 +4236,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="120" spans="1:2">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>310</v>
       </c>
@@ -4977,7 +4244,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="121" spans="1:2">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>311</v>
       </c>
@@ -4985,7 +4252,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="122" spans="1:2">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>312</v>
       </c>
@@ -4993,7 +4260,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="123" spans="1:2">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>313</v>
       </c>
@@ -5001,7 +4268,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="124" spans="1:2">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>314</v>
       </c>
@@ -5009,7 +4276,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="125" spans="1:2">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>315</v>
       </c>
@@ -5017,7 +4284,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="126" spans="1:2">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>316</v>
       </c>
@@ -5025,7 +4292,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="127" spans="1:2">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>317</v>
       </c>
@@ -5033,7 +4300,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="128" spans="1:2">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>318</v>
       </c>
@@ -5041,7 +4308,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="129" spans="1:2">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>319</v>
       </c>
@@ -5049,7 +4316,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="130" spans="1:2">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>320</v>
       </c>
@@ -5057,7 +4324,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="131" spans="1:2">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>321</v>
       </c>
@@ -5065,7 +4332,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="132" spans="1:2">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>322</v>
       </c>
@@ -5073,7 +4340,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="133" spans="1:2">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>323</v>
       </c>
@@ -5081,7 +4348,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="134" spans="1:2">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>324</v>
       </c>
@@ -5089,7 +4356,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="135" spans="1:2">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>325</v>
       </c>
@@ -5097,7 +4364,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="136" spans="1:2">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>326</v>
       </c>
@@ -5105,7 +4372,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="137" spans="1:2">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>327</v>
       </c>
@@ -5113,7 +4380,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="138" spans="1:2">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>328</v>
       </c>
@@ -5121,7 +4388,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="139" spans="1:2">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>329</v>
       </c>
@@ -5129,7 +4396,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="140" spans="1:2">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>330</v>
       </c>
@@ -5137,7 +4404,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="141" spans="1:2">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>331</v>
       </c>
@@ -5145,7 +4412,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="142" spans="1:2">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>332</v>
       </c>
@@ -5153,7 +4420,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="143" spans="1:2">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>333</v>
       </c>
@@ -5161,7 +4428,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="144" spans="1:2">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>334</v>
       </c>
@@ -5169,7 +4436,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="145" spans="1:2">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>335</v>
       </c>
@@ -5177,7 +4444,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="146" spans="1:2">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>336</v>
       </c>
@@ -5185,7 +4452,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="147" spans="1:2">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>337</v>
       </c>
@@ -5193,7 +4460,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="148" spans="1:2">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>338</v>
       </c>
@@ -5201,7 +4468,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="149" spans="1:2">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>339</v>
       </c>
@@ -5209,7 +4476,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="150" spans="1:2">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>340</v>
       </c>
@@ -5217,7 +4484,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="151" spans="1:2">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>341</v>
       </c>
@@ -5225,7 +4492,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="152" spans="1:2">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>342</v>
       </c>
@@ -5233,7 +4500,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="153" spans="1:2">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>343</v>
       </c>
@@ -5241,7 +4508,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="154" spans="1:2">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>344</v>
       </c>
@@ -5249,7 +4516,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="155" spans="1:2">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>345</v>
       </c>
@@ -5257,7 +4524,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="156" spans="1:2">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>346</v>
       </c>
@@ -5265,7 +4532,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="157" spans="1:2">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>347</v>
       </c>
@@ -5273,7 +4540,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="158" spans="1:2">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>348</v>
       </c>
@@ -5281,7 +4548,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="159" spans="1:2">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>349</v>
       </c>
@@ -5289,7 +4556,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="160" spans="1:2">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>350</v>
       </c>
@@ -5297,7 +4564,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="161" spans="1:2">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>351</v>
       </c>
@@ -5313,3569 +4580,3493 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H143"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:H140"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="51.81640625" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="5" width="28" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="1" max="1" width="51.81640625" style="13" customWidth="1"/>
+    <col min="2" max="2" width="35" style="13" customWidth="1"/>
+    <col min="3" max="5" width="28" style="13" customWidth="1"/>
+    <col min="6" max="6" width="14" style="13" customWidth="1"/>
+    <col min="7" max="7" width="10" style="13" customWidth="1"/>
+    <col min="8" max="8" width="12" style="13" customWidth="1"/>
+    <col min="9" max="16384" width="8.7265625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28" customHeight="1">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:8" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="6" customFormat="1" ht="28">
-      <c r="A2" s="8" t="s">
+    <row r="2" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>613</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>663</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>711</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>564</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>614</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>712</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
+        <v>772</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>565</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>615</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>713</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>773</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>616</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>666</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>714</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="6" t="s">
+        <v>774</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>567</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C6" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>667</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>568</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>618</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>668</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>716</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
+        <v>776</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>569</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>619</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>670</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>719</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" s="6" customFormat="1" ht="28">
-      <c r="A3" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>568</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>620</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>671</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>720</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" s="6" customFormat="1" ht="28">
-      <c r="A4" s="8" t="s">
-        <v>781</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>569</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>621</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>672</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>721</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" s="6" customFormat="1">
-      <c r="A5" s="11" t="s">
-        <v>782</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>570</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>622</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>673</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>722</v>
-      </c>
-      <c r="F5" s="10" t="s">
+      <c r="D8" s="9" t="s">
+        <v>669</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>717</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>375</v>
       </c>
-      <c r="G5" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" s="6" customFormat="1">
-      <c r="A6" s="11" t="s">
-        <v>783</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>571</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>623</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>674</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>723</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" s="6" customFormat="1" ht="28" customHeight="1">
-      <c r="A7" s="11" t="s">
-        <v>784</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>572</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>572</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>572</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>572</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" s="6" customFormat="1">
-      <c r="A8" s="11" t="s">
-        <v>785</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>573</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>624</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>675</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>724</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="7" t="s">
         <v>18</v>
       </c>
       <c r="H8" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:8" s="6" customFormat="1">
-      <c r="A9" s="11" t="s">
-        <v>786</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>574</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>625</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>676</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>725</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>375</v>
-      </c>
-      <c r="G9" s="10" t="s">
+    <row r="9" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>570</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>620</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>670</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>718</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="G9" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:8" s="6" customFormat="1">
-      <c r="A10" s="11" t="s">
-        <v>787</v>
+    <row r="10" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
+        <v>778</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>575</v>
+        <v>760</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>626</v>
+        <v>763</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>677</v>
+        <v>766</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>726</v>
+        <v>769</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="G10" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>20</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="6" customFormat="1">
-      <c r="A11" s="11" t="s">
-        <v>788</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>769</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>772</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>775</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>778</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="10" t="s">
+    <row r="11" spans="1:8" s="8" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="6" t="s">
+        <v>779</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>761</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>764</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>767</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>770</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="G11" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:8" s="6" customFormat="1" ht="36" customHeight="1">
-      <c r="A12" s="11" t="s">
-        <v>789</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>770</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>773</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>776</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>779</v>
+    <row r="12" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="14" t="s">
+        <v>780</v>
+      </c>
+      <c r="B12" s="9">
+        <v>10110</v>
+      </c>
+      <c r="C12" s="9">
+        <v>1000</v>
+      </c>
+      <c r="D12" s="9">
+        <v>10000</v>
+      </c>
+      <c r="E12" s="9">
+        <v>1111</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>374</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="7" t="s">
         <v>22</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:8" s="6" customFormat="1">
-      <c r="A13" s="13" t="s">
-        <v>790</v>
-      </c>
-      <c r="B13" s="10">
-        <v>10110</v>
-      </c>
-      <c r="C13" s="10">
-        <v>1000</v>
-      </c>
-      <c r="D13" s="10">
-        <v>10000</v>
-      </c>
-      <c r="E13" s="10">
-        <v>1111</v>
-      </c>
-      <c r="F13" s="10" t="s">
+    <row r="13" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="14" t="s">
+        <v>781</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>762</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>765</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>768</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>771</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="14" t="s">
+        <v>782</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>571</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>621</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>671</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>719</v>
+      </c>
+      <c r="F14" s="9" t="s">
         <v>374</v>
       </c>
-      <c r="G13" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" s="6" customFormat="1">
-      <c r="A14" s="13" t="s">
-        <v>791</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>771</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>774</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>777</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>780</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="7" t="s">
         <v>24</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:8" s="6" customFormat="1">
-      <c r="A15" s="13" t="s">
-        <v>792</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>576</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>627</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>678</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>727</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="G15" s="10" t="s">
+    <row r="15" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="6" t="s">
+        <v>783</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>572</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>622</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>672</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>720</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="H15" s="10" t="s">
+      <c r="H15" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:8" s="6" customFormat="1" ht="28">
-      <c r="A16" s="14" t="s">
-        <v>793</v>
+    <row r="16" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="6" t="s">
+        <v>784</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="G16" s="7" t="s">
         <v>26</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:8" s="6" customFormat="1">
-      <c r="A17" s="14" t="s">
-        <v>794</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>578</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>629</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>680</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>729</v>
-      </c>
-      <c r="F17" s="10" t="s">
+    <row r="17" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>574</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>624</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>674</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>722</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="9" t="s">
+        <v>785</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>575</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>625</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>723</v>
+      </c>
+      <c r="F18" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G17" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" s="6" customFormat="1">
-      <c r="A18" s="11" t="s">
-        <v>527</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>579</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>630</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>681</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>730</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="G18" s="9" t="s">
+      <c r="G18" s="7" t="s">
         <v>28</v>
       </c>
       <c r="H18" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:8" s="6" customFormat="1">
-      <c r="A19" s="15" t="s">
-        <v>795</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>580</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>631</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>682</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>731</v>
-      </c>
-      <c r="F19" s="10" t="s">
+    <row r="19" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="6" t="s">
+        <v>786</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>576</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>626</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>676</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="F19" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="H19" s="10" t="s">
+      <c r="H19" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:8" s="6" customFormat="1">
-      <c r="A20" s="11" t="s">
-        <v>796</v>
+    <row r="20" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="9" t="s">
+        <v>787</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>732</v>
+        <v>725</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="G20" s="7" t="s">
         <v>30</v>
       </c>
       <c r="H20" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:8" s="6" customFormat="1" ht="28">
-      <c r="A21" s="15" t="s">
-        <v>797</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>582</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>633</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>684</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>733</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>373</v>
-      </c>
-      <c r="G21" s="10" t="s">
+    <row r="21" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="6" t="s">
+        <v>788</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>578</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>628</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>678</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>726</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="G21" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="H21" s="10" t="s">
+      <c r="H21" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:8" s="6" customFormat="1">
-      <c r="A22" s="11" t="s">
-        <v>798</v>
+    <row r="22" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="9" t="s">
+        <v>789</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="G22" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="G22" s="7" t="s">
         <v>32</v>
       </c>
       <c r="H22" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:8" s="6" customFormat="1" ht="28">
-      <c r="A23" s="15" t="s">
-        <v>799</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>584</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>635</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>686</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>735</v>
-      </c>
-      <c r="F23" s="10" t="s">
+    <row r="23" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="6" t="s">
+        <v>790</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>580</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>596</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>646</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>728</v>
+      </c>
+      <c r="F23" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="G23" s="10" t="s">
+      <c r="G23" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="H23" s="10" t="s">
+      <c r="H23" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:8" s="6" customFormat="1">
-      <c r="A24" s="11" t="s">
-        <v>800</v>
+    <row r="24" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="9" t="s">
+        <v>791</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>602</v>
+        <v>630</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>653</v>
+        <v>680</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="G24" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="G24" s="7" t="s">
         <v>34</v>
       </c>
       <c r="H24" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:8" s="6" customFormat="1" ht="56">
-      <c r="A25" s="15" t="s">
-        <v>801</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>586</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>636</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>687</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>737</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>373</v>
-      </c>
-      <c r="G25" s="10" t="s">
+    <row r="25" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="6" t="s">
+        <v>792</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>580</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>596</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>730</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="G25" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="H25" s="10" t="s">
+      <c r="H25" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:8" s="6" customFormat="1">
-      <c r="A26" s="11" t="s">
-        <v>802</v>
+    <row r="26" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="9" t="s">
+        <v>793</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>602</v>
+        <v>681</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="G26" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="7" t="s">
         <v>36</v>
       </c>
       <c r="H26" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:8" s="6" customFormat="1" ht="42">
-      <c r="A27" s="15" t="s">
-        <v>803</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>379</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>380</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>381</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="F27" s="10" t="s">
-        <v>375</v>
-      </c>
-      <c r="G27" s="10" t="s">
+    <row r="27" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="6" t="s">
+        <v>794</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>583</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>633</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>682</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>732</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="G27" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H27" s="10" t="s">
+      <c r="H27" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:8" s="6" customFormat="1">
-      <c r="A28" s="11" t="s">
-        <v>804</v>
+    <row r="28" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="9" t="s">
+        <v>795</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G28" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="G28" s="7" t="s">
         <v>38</v>
       </c>
       <c r="H28" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:8" s="6" customFormat="1" ht="28">
-      <c r="A29" s="15" t="s">
-        <v>805</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>588</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>639</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>689</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>740</v>
-      </c>
-      <c r="F29" s="10" t="s">
+    <row r="29" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="7" t="s">
+        <v>796</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>684</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>734</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>586</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>685</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>735</v>
+      </c>
+      <c r="F30" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G29" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" s="6" customFormat="1" ht="15">
-      <c r="A30" s="16" t="s">
-        <v>806</v>
-      </c>
-      <c r="B30" s="16" t="s">
-        <v>589</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>640</v>
-      </c>
-      <c r="D30" s="16" t="s">
-        <v>690</v>
-      </c>
-      <c r="E30" s="16" t="s">
-        <v>741</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="G30" s="9" t="s">
+      <c r="G30" s="7" t="s">
         <v>40</v>
       </c>
       <c r="H30" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:8" s="6" customFormat="1" ht="42">
-      <c r="A31" s="15" t="s">
-        <v>807</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>590</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>641</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>691</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>742</v>
-      </c>
-      <c r="F31" s="10" t="s">
+    <row r="31" spans="1:8" s="8" customFormat="1" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="7" t="s">
+        <v>797</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>587</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>637</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>686</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>736</v>
+      </c>
+      <c r="F31" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="G31" s="10" t="s">
+      <c r="G31" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="H31" s="10" t="s">
+      <c r="H31" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:8" s="6" customFormat="1" ht="15">
-      <c r="A32" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="B32" s="16" t="s">
-        <v>591</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>642</v>
-      </c>
-      <c r="D32" s="16" t="s">
-        <v>692</v>
-      </c>
-      <c r="E32" s="16" t="s">
-        <v>743</v>
+    <row r="32" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="9" t="s">
+        <v>798</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>588</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>638</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>687</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>737</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="G32" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="G32" s="7" t="s">
         <v>42</v>
       </c>
       <c r="H32" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:8" s="6" customFormat="1">
-      <c r="A33" s="15" t="s">
-        <v>808</v>
-      </c>
-      <c r="B33" s="10" t="s">
-        <v>592</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>643</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>693</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>744</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G33" s="10" t="s">
+    <row r="33" spans="1:8" s="8" customFormat="1" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>589</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>639</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>688</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>738</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="G33" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="H33" s="10" t="s">
+      <c r="H33" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:8" s="6" customFormat="1" ht="24.5" customHeight="1">
-      <c r="A34" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>593</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>694</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>745</v>
+    <row r="34" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="9" t="s">
+        <v>800</v>
+      </c>
+      <c r="B34" s="9">
+        <v>4</v>
+      </c>
+      <c r="C34" s="9">
+        <v>3</v>
+      </c>
+      <c r="D34" s="9">
+        <v>2</v>
+      </c>
+      <c r="E34" s="9">
+        <v>5</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="G34" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="G34" s="7" t="s">
         <v>44</v>
       </c>
       <c r="H34" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:8" s="6" customFormat="1" ht="42">
-      <c r="A35" s="15" t="s">
-        <v>810</v>
-      </c>
-      <c r="B35" s="10" t="s">
-        <v>594</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>645</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>695</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>746</v>
-      </c>
-      <c r="F35" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="G35" s="10" t="s">
+    <row r="35" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="7" t="s">
+        <v>801</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>640</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>689</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>739</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="G35" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="H35" s="10" t="s">
+      <c r="H35" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:8" s="6" customFormat="1" ht="26.5" customHeight="1">
-      <c r="A36" s="8" t="s">
-        <v>811</v>
+    <row r="36" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="9" t="s">
+        <v>802</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>374</v>
       </c>
-      <c r="G36" s="9" t="s">
+      <c r="G36" s="7" t="s">
         <v>46</v>
       </c>
       <c r="H36" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:8" s="6" customFormat="1" ht="28">
-      <c r="A37" s="15" t="s">
-        <v>812</v>
-      </c>
-      <c r="B37" s="10">
-        <v>4</v>
-      </c>
-      <c r="C37" s="10">
+    <row r="37" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="7" t="s">
+        <v>803</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>592</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>642</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>691</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>741</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="9" t="s">
+        <v>894</v>
+      </c>
+      <c r="B38" s="9">
+        <v>13</v>
+      </c>
+      <c r="C38" s="9">
+        <v>0</v>
+      </c>
+      <c r="D38" s="9">
+        <v>12</v>
+      </c>
+      <c r="E38" s="9">
         <v>3</v>
       </c>
-      <c r="D37" s="10">
-        <v>2</v>
-      </c>
-      <c r="E37" s="10">
-        <v>5</v>
-      </c>
-      <c r="F37" s="10" t="s">
-        <v>375</v>
-      </c>
-      <c r="G37" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" s="6" customFormat="1" ht="70">
-      <c r="A38" s="8" t="s">
-        <v>813</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>596</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>647</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>697</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>748</v>
-      </c>
       <c r="F38" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="G38" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38" s="7" t="s">
         <v>50</v>
       </c>
       <c r="H38" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:8" s="6" customFormat="1" ht="28">
-      <c r="A39" s="15" t="s">
-        <v>814</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>597</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>648</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>698</v>
-      </c>
-      <c r="E39" s="10" t="s">
-        <v>749</v>
-      </c>
-      <c r="F39" s="10" t="s">
+    <row r="39" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="6" t="s">
+        <v>804</v>
+      </c>
+      <c r="B39" s="6">
+        <v>1011</v>
+      </c>
+      <c r="C39" s="6">
+        <v>1101</v>
+      </c>
+      <c r="D39" s="6">
+        <v>1110</v>
+      </c>
+      <c r="E39" s="6">
+        <v>1111</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="6" t="s">
+        <v>805</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>692</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>742</v>
+      </c>
+      <c r="F40" s="9" t="s">
         <v>374</v>
       </c>
-      <c r="G39" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" s="6" customFormat="1">
-      <c r="A40" s="8" t="s">
-        <v>815</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="D40" s="9" t="s">
-        <v>699</v>
-      </c>
-      <c r="E40" s="9" t="s">
-        <v>750</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="G40" s="9" t="s">
+      <c r="G40" s="7" t="s">
         <v>52</v>
       </c>
       <c r="H40" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:8" s="6" customFormat="1">
-      <c r="A41" s="15" t="s">
-        <v>816</v>
-      </c>
-      <c r="B41" s="10">
-        <v>13</v>
-      </c>
-      <c r="C41" s="10">
-        <v>0</v>
-      </c>
-      <c r="D41" s="10">
+    <row r="41" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="7" t="s">
+        <v>806</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>594</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>644</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>693</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>743</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H41" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E41" s="10">
-        <v>3</v>
-      </c>
-      <c r="F41" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G41" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" s="6" customFormat="1">
-      <c r="A42" s="11" t="s">
-        <v>817</v>
-      </c>
-      <c r="B42" s="11">
-        <v>1011</v>
-      </c>
-      <c r="C42" s="11">
-        <v>1101</v>
-      </c>
-      <c r="D42" s="11">
-        <v>1110</v>
-      </c>
-      <c r="E42" s="11">
-        <v>1111</v>
+    </row>
+    <row r="42" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="9" t="s">
+        <v>807</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>595</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>744</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="G42" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="G42" s="7" t="s">
         <v>54</v>
       </c>
       <c r="H42" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:8" s="6" customFormat="1">
-      <c r="A43" s="11" t="s">
-        <v>818</v>
-      </c>
-      <c r="B43" s="11" t="s">
-        <v>599</v>
-      </c>
-      <c r="C43" s="11" t="s">
-        <v>650</v>
-      </c>
-      <c r="D43" s="11" t="s">
-        <v>700</v>
-      </c>
-      <c r="E43" s="11" t="s">
-        <v>751</v>
-      </c>
-      <c r="F43" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="G43" s="10" t="s">
+    <row r="43" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="7" t="s">
+        <v>808</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>596</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>646</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>580</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>728</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="H43" s="10" t="s">
+      <c r="H43" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:8" s="6" customFormat="1" ht="28">
-      <c r="A44" s="8" t="s">
-        <v>819</v>
+    <row r="44" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="9" t="s">
+        <v>809</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>375</v>
       </c>
-      <c r="G44" s="9" t="s">
+      <c r="G44" s="7" t="s">
         <v>56</v>
       </c>
       <c r="H44" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:8" s="6" customFormat="1" ht="28">
-      <c r="A45" s="15" t="s">
-        <v>820</v>
-      </c>
-      <c r="B45" s="10" t="s">
-        <v>601</v>
-      </c>
-      <c r="C45" s="10" t="s">
-        <v>652</v>
-      </c>
-      <c r="D45" s="10" t="s">
-        <v>702</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>753</v>
-      </c>
-      <c r="F45" s="10" t="s">
+    <row r="45" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="7" t="s">
+        <v>810</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>598</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>648</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>746</v>
+      </c>
+      <c r="F45" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="G45" s="10" t="s">
+      <c r="G45" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="H45" s="10" t="s">
+      <c r="H45" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="1:8" s="6" customFormat="1">
-      <c r="A46" s="8" t="s">
-        <v>821</v>
+    <row r="46" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="9" t="s">
+        <v>811</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>585</v>
+        <v>697</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>736</v>
+        <v>747</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G46" s="9" t="s">
+      <c r="G46" s="7" t="s">
         <v>58</v>
       </c>
       <c r="H46" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:8" s="6" customFormat="1" ht="28">
-      <c r="A47" s="15" t="s">
-        <v>822</v>
-      </c>
-      <c r="B47" s="10" t="s">
-        <v>603</v>
-      </c>
-      <c r="C47" s="10" t="s">
-        <v>654</v>
-      </c>
-      <c r="D47" s="10" t="s">
-        <v>703</v>
-      </c>
-      <c r="E47" s="10" t="s">
-        <v>754</v>
-      </c>
-      <c r="F47" s="10" t="s">
+    <row r="47" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>600</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>650</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>698</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>748</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="G47" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="9" t="s">
+        <v>813</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>601</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>651</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>699</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>749</v>
+      </c>
+      <c r="F48" s="9" t="s">
         <v>375</v>
       </c>
-      <c r="G47" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="H47" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" s="6" customFormat="1" ht="42">
-      <c r="A48" s="8" t="s">
-        <v>823</v>
-      </c>
-      <c r="B48" s="9" t="s">
-        <v>604</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>655</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>704</v>
-      </c>
-      <c r="E48" s="9" t="s">
-        <v>755</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="G48" s="9" t="s">
+      <c r="G48" s="7" t="s">
         <v>60</v>
       </c>
       <c r="H48" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:8" s="6" customFormat="1" ht="28">
+    <row r="49" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A49" s="15" t="s">
-        <v>824</v>
-      </c>
-      <c r="B49" s="10" t="s">
-        <v>605</v>
-      </c>
-      <c r="C49" s="10" t="s">
-        <v>656</v>
-      </c>
-      <c r="D49" s="10" t="s">
-        <v>705</v>
-      </c>
-      <c r="E49" s="10" t="s">
-        <v>756</v>
-      </c>
-      <c r="F49" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G49" s="10" t="s">
+        <v>814</v>
+      </c>
+      <c r="B49" s="15">
+        <v>45</v>
+      </c>
+      <c r="C49" s="15">
+        <v>30</v>
+      </c>
+      <c r="D49" s="15">
+        <v>85</v>
+      </c>
+      <c r="E49" s="15">
+        <v>70</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="G49" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="H49" s="10" t="s">
+      <c r="H49" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:8" s="6" customFormat="1" ht="42">
-      <c r="A50" s="8" t="s">
-        <v>825</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>606</v>
-      </c>
-      <c r="C50" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>706</v>
-      </c>
-      <c r="E50" s="9" t="s">
-        <v>757</v>
+    <row r="50" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="15" t="s">
+        <v>815</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>602</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>652</v>
+      </c>
+      <c r="D50" s="15" t="s">
+        <v>700</v>
+      </c>
+      <c r="E50" s="15" t="s">
+        <v>542</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>374</v>
       </c>
-      <c r="G50" s="9" t="s">
+      <c r="G50" s="7" t="s">
         <v>62</v>
       </c>
       <c r="H50" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:8" s="6" customFormat="1" ht="56">
+    <row r="51" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A51" s="15" t="s">
-        <v>826</v>
-      </c>
-      <c r="B51" s="10" t="s">
-        <v>607</v>
-      </c>
-      <c r="C51" s="10" t="s">
-        <v>658</v>
-      </c>
-      <c r="D51" s="10" t="s">
-        <v>707</v>
-      </c>
-      <c r="E51" s="10" t="s">
-        <v>758</v>
-      </c>
-      <c r="F51" s="10" t="s">
+        <v>816</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>603</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>653</v>
+      </c>
+      <c r="D51" s="15" t="s">
+        <v>701</v>
+      </c>
+      <c r="E51" s="15" t="s">
+        <v>750</v>
+      </c>
+      <c r="F51" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="G51" s="10" t="s">
+      <c r="G51" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="H51" s="10" t="s">
+      <c r="H51" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:8" s="6" customFormat="1" ht="23">
-      <c r="A52" s="17" t="s">
-        <v>827</v>
-      </c>
-      <c r="B52" s="18">
-        <v>45</v>
-      </c>
-      <c r="C52" s="18">
-        <v>30</v>
-      </c>
-      <c r="D52" s="18">
-        <v>85</v>
-      </c>
-      <c r="E52" s="18">
-        <v>70</v>
+    <row r="52" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="15" t="s">
+        <v>817</v>
+      </c>
+      <c r="B52" s="15" t="s">
+        <v>604</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>654</v>
+      </c>
+      <c r="D52" s="15" t="s">
+        <v>702</v>
+      </c>
+      <c r="E52" s="15" t="s">
+        <v>751</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="G52" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G52" s="7" t="s">
         <v>64</v>
       </c>
       <c r="H52" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:8" s="6" customFormat="1">
-      <c r="A53" s="17" t="s">
-        <v>828</v>
-      </c>
-      <c r="B53" s="18" t="s">
-        <v>608</v>
-      </c>
-      <c r="C53" s="18" t="s">
-        <v>659</v>
-      </c>
-      <c r="D53" s="18" t="s">
-        <v>708</v>
-      </c>
-      <c r="E53" s="18" t="s">
-        <v>546</v>
-      </c>
-      <c r="F53" s="10" t="s">
+    <row r="53" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="15" t="s">
+        <v>818</v>
+      </c>
+      <c r="B53" s="15" t="s">
+        <v>605</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>655</v>
+      </c>
+      <c r="D53" s="15" t="s">
+        <v>703</v>
+      </c>
+      <c r="E53" s="15" t="s">
+        <v>752</v>
+      </c>
+      <c r="F53" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="G53" s="10" t="s">
+      <c r="G53" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="H53" s="10" t="s">
+      <c r="H53" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:8" s="6" customFormat="1" ht="23">
-      <c r="A54" s="17" t="s">
-        <v>829</v>
-      </c>
-      <c r="B54" s="18" t="s">
-        <v>609</v>
-      </c>
-      <c r="C54" s="18" t="s">
-        <v>660</v>
-      </c>
-      <c r="D54" s="18" t="s">
-        <v>709</v>
-      </c>
-      <c r="E54" s="18" t="s">
-        <v>759</v>
+    <row r="54" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="15" t="s">
+        <v>819</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>606</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>656</v>
+      </c>
+      <c r="D54" s="15" t="s">
+        <v>704</v>
+      </c>
+      <c r="E54" s="15" t="s">
+        <v>753</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="G54" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="G54" s="7" t="s">
         <v>66</v>
       </c>
       <c r="H54" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:8" s="6" customFormat="1" ht="34.5">
-      <c r="A55" s="17" t="s">
-        <v>830</v>
-      </c>
-      <c r="B55" s="18" t="s">
-        <v>610</v>
-      </c>
-      <c r="C55" s="18" t="s">
-        <v>661</v>
-      </c>
-      <c r="D55" s="18" t="s">
-        <v>710</v>
-      </c>
-      <c r="E55" s="18" t="s">
-        <v>760</v>
-      </c>
-      <c r="F55" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G55" s="10" t="s">
+    <row r="55" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="15" t="s">
+        <v>820</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>607</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>657</v>
+      </c>
+      <c r="D55" s="15" t="s">
+        <v>705</v>
+      </c>
+      <c r="E55" s="15" t="s">
+        <v>754</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="G55" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="H55" s="10" t="s">
+      <c r="H55" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="1:8" s="6" customFormat="1" ht="23">
-      <c r="A56" s="17" t="s">
-        <v>831</v>
-      </c>
-      <c r="B56" s="18" t="s">
-        <v>611</v>
-      </c>
-      <c r="C56" s="18" t="s">
-        <v>662</v>
-      </c>
-      <c r="D56" s="18" t="s">
-        <v>711</v>
-      </c>
-      <c r="E56" s="18" t="s">
-        <v>761</v>
+    <row r="56" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="15" t="s">
+        <v>821</v>
+      </c>
+      <c r="B56" s="15" t="s">
+        <v>608</v>
+      </c>
+      <c r="C56" s="15" t="s">
+        <v>658</v>
+      </c>
+      <c r="D56" s="15" t="s">
+        <v>706</v>
+      </c>
+      <c r="E56" s="15" t="s">
+        <v>755</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="G56" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="G56" s="7" t="s">
         <v>68</v>
       </c>
       <c r="H56" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:8" s="6" customFormat="1" ht="23">
-      <c r="A57" s="17" t="s">
-        <v>832</v>
-      </c>
-      <c r="B57" s="18" t="s">
-        <v>612</v>
-      </c>
-      <c r="C57" s="18" t="s">
-        <v>663</v>
-      </c>
-      <c r="D57" s="18" t="s">
-        <v>712</v>
-      </c>
-      <c r="E57" s="18" t="s">
-        <v>762</v>
-      </c>
-      <c r="F57" s="10" t="s">
-        <v>373</v>
-      </c>
-      <c r="G57" s="10" t="s">
+    <row r="57" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="15" t="s">
+        <v>822</v>
+      </c>
+      <c r="B57" s="15" t="s">
+        <v>609</v>
+      </c>
+      <c r="C57" s="15" t="s">
+        <v>659</v>
+      </c>
+      <c r="D57" s="15" t="s">
+        <v>707</v>
+      </c>
+      <c r="E57" s="15" t="s">
+        <v>756</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G57" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="H57" s="10" t="s">
+      <c r="H57" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:8" s="6" customFormat="1" ht="23">
-      <c r="A58" s="17" t="s">
-        <v>833</v>
-      </c>
-      <c r="B58" s="18" t="s">
-        <v>613</v>
-      </c>
-      <c r="C58" s="18" t="s">
-        <v>664</v>
-      </c>
-      <c r="D58" s="18" t="s">
-        <v>713</v>
-      </c>
-      <c r="E58" s="18" t="s">
-        <v>763</v>
+    <row r="58" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="15" t="s">
+        <v>823</v>
+      </c>
+      <c r="B58" s="15" t="s">
+        <v>610</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>660</v>
+      </c>
+      <c r="D58" s="15" t="s">
+        <v>708</v>
+      </c>
+      <c r="E58" s="15" t="s">
+        <v>757</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="G58" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="G58" s="7" t="s">
         <v>70</v>
       </c>
       <c r="H58" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:8" s="6" customFormat="1" ht="23">
-      <c r="A59" s="17" t="s">
-        <v>834</v>
-      </c>
-      <c r="B59" s="18" t="s">
-        <v>614</v>
-      </c>
-      <c r="C59" s="18" t="s">
-        <v>665</v>
-      </c>
-      <c r="D59" s="18" t="s">
-        <v>714</v>
-      </c>
-      <c r="E59" s="18" t="s">
-        <v>764</v>
-      </c>
-      <c r="F59" s="10" t="s">
+    <row r="59" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="15" t="s">
+        <v>824</v>
+      </c>
+      <c r="B59" s="15" t="s">
+        <v>611</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>661</v>
+      </c>
+      <c r="D59" s="15" t="s">
+        <v>709</v>
+      </c>
+      <c r="E59" s="15" t="s">
+        <v>758</v>
+      </c>
+      <c r="F59" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="G59" s="10" t="s">
+      <c r="G59" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="H59" s="10" t="s">
+      <c r="H59" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:8" s="6" customFormat="1">
-      <c r="A60" s="17" t="s">
-        <v>835</v>
-      </c>
-      <c r="B60" s="18" t="s">
-        <v>615</v>
-      </c>
-      <c r="C60" s="18" t="s">
-        <v>666</v>
-      </c>
-      <c r="D60" s="18" t="s">
-        <v>715</v>
-      </c>
-      <c r="E60" s="18" t="s">
-        <v>765</v>
+    <row r="60" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="6" t="s">
+        <v>825</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>612</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>710</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>759</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G60" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="G60" s="7" t="s">
         <v>72</v>
       </c>
       <c r="H60" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:8" s="6" customFormat="1" ht="23">
-      <c r="A61" s="17" t="s">
-        <v>836</v>
-      </c>
-      <c r="B61" s="18" t="s">
-        <v>616</v>
-      </c>
-      <c r="C61" s="18" t="s">
-        <v>667</v>
-      </c>
-      <c r="D61" s="18" t="s">
-        <v>716</v>
-      </c>
-      <c r="E61" s="18" t="s">
-        <v>766</v>
-      </c>
-      <c r="F61" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="G61" s="10" t="s">
+    <row r="61" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>525</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G61" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="H61" s="10" t="s">
+      <c r="H61" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:8" s="6" customFormat="1" ht="23">
-      <c r="A62" s="17" t="s">
-        <v>837</v>
-      </c>
-      <c r="B62" s="18" t="s">
-        <v>617</v>
-      </c>
-      <c r="C62" s="18" t="s">
-        <v>668</v>
-      </c>
-      <c r="D62" s="18" t="s">
-        <v>717</v>
-      </c>
-      <c r="E62" s="18" t="s">
-        <v>767</v>
+    <row r="62" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>532</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>373</v>
       </c>
-      <c r="G62" s="9" t="s">
+      <c r="G62" s="7" t="s">
         <v>74</v>
       </c>
       <c r="H62" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:8" s="6" customFormat="1" ht="28">
-      <c r="A63" s="11" t="s">
-        <v>838</v>
-      </c>
-      <c r="B63" s="11" t="s">
-        <v>618</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>669</v>
-      </c>
-      <c r="D63" s="11" t="s">
-        <v>718</v>
-      </c>
-      <c r="E63" s="19" t="s">
-        <v>768</v>
-      </c>
-      <c r="F63" s="10" t="s">
+    <row r="63" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="6" t="s">
+        <v>533</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>534</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>535</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>536</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>537</v>
+      </c>
+      <c r="F63" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="G63" s="10" t="s">
+      <c r="G63" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="H63" s="10" t="s">
+      <c r="H63" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:8" s="6" customFormat="1">
-      <c r="A64" s="11" t="s">
-        <v>527</v>
-      </c>
-      <c r="B64" s="11" t="s">
-        <v>528</v>
-      </c>
-      <c r="C64" s="11" t="s">
-        <v>529</v>
-      </c>
-      <c r="D64" s="11" t="s">
-        <v>530</v>
-      </c>
-      <c r="E64" s="11" t="s">
-        <v>531</v>
+    <row r="64" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>542</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G64" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="G64" s="7" t="s">
         <v>76</v>
       </c>
       <c r="H64" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:8" s="6" customFormat="1">
-      <c r="A65" s="11" t="s">
-        <v>532</v>
-      </c>
-      <c r="B65" s="11" t="s">
-        <v>533</v>
-      </c>
-      <c r="C65" s="11" t="s">
-        <v>534</v>
-      </c>
-      <c r="D65" s="11" t="s">
-        <v>535</v>
-      </c>
-      <c r="E65" s="11" t="s">
-        <v>536</v>
-      </c>
-      <c r="F65" s="10" t="s">
-        <v>373</v>
-      </c>
-      <c r="G65" s="10" t="s">
+    <row r="65" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>545</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>546</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>547</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G65" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="H65" s="10" t="s">
+      <c r="H65" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="66" spans="1:8" s="6" customFormat="1">
-      <c r="A66" s="11" t="s">
-        <v>537</v>
-      </c>
-      <c r="B66" s="11" t="s">
-        <v>538</v>
-      </c>
-      <c r="C66" s="11" t="s">
-        <v>539</v>
-      </c>
-      <c r="D66" s="11" t="s">
-        <v>540</v>
-      </c>
-      <c r="E66" s="11" t="s">
-        <v>541</v>
+    <row r="66" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="6" t="s">
+        <v>548</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="E66" s="9" t="s">
+        <v>550</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="G66" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="G66" s="7" t="s">
         <v>78</v>
       </c>
       <c r="H66" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="67" spans="1:8" s="6" customFormat="1">
-      <c r="A67" s="11" t="s">
-        <v>542</v>
-      </c>
-      <c r="B67" s="11" t="s">
-        <v>543</v>
-      </c>
-      <c r="C67" s="11" t="s">
-        <v>544</v>
-      </c>
-      <c r="D67" s="11" t="s">
-        <v>545</v>
-      </c>
-      <c r="E67" s="11" t="s">
-        <v>546</v>
-      </c>
-      <c r="F67" s="10" t="s">
+    <row r="67" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="6" t="s">
+        <v>551</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>553</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="F67" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="G67" s="10" t="s">
+      <c r="G67" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="H67" s="10" t="s">
+      <c r="H67" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="68" spans="1:8" s="6" customFormat="1">
-      <c r="A68" s="11" t="s">
-        <v>547</v>
+    <row r="68" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="6" t="s">
+        <v>556</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="F68" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G68" s="9" t="s">
+      <c r="G68" s="7" t="s">
         <v>80</v>
       </c>
       <c r="H68" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="1:8" s="6" customFormat="1">
-      <c r="A69" s="11" t="s">
-        <v>552</v>
-      </c>
-      <c r="B69" s="10" t="s">
-        <v>553</v>
-      </c>
-      <c r="C69" s="10" t="s">
-        <v>551</v>
-      </c>
-      <c r="D69" s="10" t="s">
-        <v>549</v>
-      </c>
-      <c r="E69" s="10" t="s">
-        <v>554</v>
-      </c>
-      <c r="F69" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="G69" s="10" t="s">
+    <row r="69" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="9" t="s">
+        <v>831</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>832</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>833</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>834</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>835</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="G69" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="H69" s="10" t="s">
+      <c r="H69" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:8" s="6" customFormat="1">
-      <c r="A70" s="11" t="s">
-        <v>555</v>
-      </c>
-      <c r="B70" s="9" t="s">
-        <v>556</v>
-      </c>
-      <c r="C70" s="9" t="s">
-        <v>557</v>
-      </c>
-      <c r="D70" s="9" t="s">
-        <v>558</v>
-      </c>
-      <c r="E70" s="9" t="s">
-        <v>559</v>
+    <row r="70" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="6" t="s">
+        <v>836</v>
+      </c>
+      <c r="B70" s="10">
+        <v>90</v>
+      </c>
+      <c r="C70" s="9">
+        <v>100</v>
+      </c>
+      <c r="D70" s="9">
+        <v>85</v>
+      </c>
+      <c r="E70" s="9">
+        <v>70</v>
       </c>
       <c r="F70" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="G70" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G70" s="7" t="s">
         <v>82</v>
       </c>
       <c r="H70" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="71" spans="1:8" s="6" customFormat="1">
-      <c r="A71" s="11" t="s">
-        <v>560</v>
+    <row r="71" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="6" t="s">
+        <v>815</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>561</v>
-      </c>
-      <c r="C71" s="10" t="s">
-        <v>562</v>
-      </c>
-      <c r="D71" s="10" t="s">
-        <v>563</v>
-      </c>
-      <c r="E71" s="10" t="s">
-        <v>564</v>
-      </c>
-      <c r="F71" s="10" t="s">
+        <v>837</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="E71" s="9" t="s">
+        <v>838</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="G71" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H71" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="6" t="s">
+        <v>839</v>
+      </c>
+      <c r="B72" s="10" t="s">
+        <v>840</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>841</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>842</v>
+      </c>
+      <c r="E72" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="F72" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G71" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="H71" s="10" t="s">
+      <c r="G72" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="H72" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="72" spans="1:8" s="6" customFormat="1">
-      <c r="A72" s="10" t="s">
+    <row r="73" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="6" t="s">
+        <v>843</v>
+      </c>
+      <c r="B73" s="10" t="s">
+        <v>844</v>
+      </c>
+      <c r="C73" s="9" t="s">
+        <v>845</v>
+      </c>
+      <c r="D73" s="9" t="s">
+        <v>846</v>
+      </c>
+      <c r="E73" s="9" t="s">
+        <v>847</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="G73" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="H73" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="6" t="s">
+        <v>848</v>
+      </c>
+      <c r="B74" s="10" t="s">
+        <v>849</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>850</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>851</v>
+      </c>
+      <c r="E74" s="9" t="s">
+        <v>852</v>
+      </c>
+      <c r="F74" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G74" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="H74" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="6" t="s">
+        <v>853</v>
+      </c>
+      <c r="B75" s="10" t="s">
+        <v>854</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>855</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>856</v>
+      </c>
+      <c r="E75" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="G75" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="H75" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="6" t="s">
+        <v>858</v>
+      </c>
+      <c r="B76" s="10" t="s">
+        <v>859</v>
+      </c>
+      <c r="C76" s="9" t="s">
+        <v>860</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>861</v>
+      </c>
+      <c r="E76" s="9" t="s">
+        <v>862</v>
+      </c>
+      <c r="F76" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="G76" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H76" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="6" t="s">
         <v>863</v>
       </c>
-      <c r="B72" s="10" t="s">
+      <c r="B77" s="10" t="s">
         <v>864</v>
       </c>
-      <c r="C72" s="10" t="s">
+      <c r="C77" s="9" t="s">
         <v>865</v>
       </c>
-      <c r="D72" s="6" t="s">
+      <c r="D77" s="9" t="s">
+        <v>710</v>
+      </c>
+      <c r="E77" s="9" t="s">
+        <v>759</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G77" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H77" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="6" t="s">
+        <v>789</v>
+      </c>
+      <c r="B78" s="10" t="s">
         <v>866</v>
       </c>
-      <c r="E72" s="6" t="s">
+      <c r="C78" s="9" t="s">
         <v>867</v>
       </c>
-      <c r="F72" s="10" t="s">
-        <v>375</v>
-      </c>
-      <c r="G72" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="H72" s="10" t="s">
+      <c r="D78" s="9" t="s">
+        <v>868</v>
+      </c>
+      <c r="E78" s="9" t="s">
+        <v>727</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="G78" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="H78" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="73" spans="1:8" s="6" customFormat="1">
-      <c r="A73" s="11" t="s">
-        <v>868</v>
-      </c>
-      <c r="B73" s="21">
-        <v>90</v>
-      </c>
-      <c r="C73" s="10">
-        <v>100</v>
-      </c>
-      <c r="D73" s="10">
-        <v>85</v>
-      </c>
-      <c r="E73" s="10">
-        <v>70</v>
-      </c>
-      <c r="F73" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G73" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" s="6" customFormat="1">
-      <c r="A74" s="11" t="s">
-        <v>828</v>
-      </c>
-      <c r="B74" s="21" t="s">
-        <v>869</v>
-      </c>
-      <c r="C74" s="10" t="s">
-        <v>659</v>
-      </c>
-      <c r="D74" s="10" t="s">
-        <v>543</v>
-      </c>
-      <c r="E74" s="10" t="s">
-        <v>870</v>
-      </c>
-      <c r="F74" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="G74" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="H74" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" s="6" customFormat="1">
-      <c r="A75" s="11" t="s">
-        <v>871</v>
-      </c>
-      <c r="B75" s="21" t="s">
-        <v>872</v>
-      </c>
-      <c r="C75" s="10" t="s">
-        <v>873</v>
-      </c>
-      <c r="D75" s="10" t="s">
-        <v>874</v>
-      </c>
-      <c r="E75" s="10" t="s">
-        <v>760</v>
-      </c>
-      <c r="F75" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G75" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" s="6" customFormat="1">
-      <c r="A76" s="11" t="s">
-        <v>875</v>
-      </c>
-      <c r="B76" s="21" t="s">
-        <v>876</v>
-      </c>
-      <c r="C76" s="10" t="s">
-        <v>877</v>
-      </c>
-      <c r="D76" s="10" t="s">
-        <v>878</v>
-      </c>
-      <c r="E76" s="10" t="s">
-        <v>879</v>
-      </c>
-      <c r="F76" s="10" t="s">
-        <v>373</v>
-      </c>
-      <c r="G76" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="H76" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" s="6" customFormat="1">
-      <c r="A77" s="11" t="s">
-        <v>880</v>
-      </c>
-      <c r="B77" s="21" t="s">
-        <v>881</v>
-      </c>
-      <c r="C77" s="10" t="s">
-        <v>882</v>
-      </c>
-      <c r="D77" s="10" t="s">
-        <v>883</v>
-      </c>
-      <c r="E77" s="10" t="s">
-        <v>884</v>
-      </c>
-      <c r="F77" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G77" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" s="6" customFormat="1">
-      <c r="A78" s="11" t="s">
-        <v>885</v>
-      </c>
-      <c r="B78" s="21" t="s">
-        <v>886</v>
-      </c>
-      <c r="C78" s="10" t="s">
-        <v>887</v>
-      </c>
-      <c r="D78" s="10" t="s">
-        <v>888</v>
-      </c>
-      <c r="E78" s="10" t="s">
-        <v>889</v>
-      </c>
-      <c r="F78" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="G78" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="H78" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" s="6" customFormat="1">
-      <c r="A79" s="11" t="s">
-        <v>890</v>
-      </c>
-      <c r="B79" s="21" t="s">
-        <v>891</v>
-      </c>
-      <c r="C79" s="10" t="s">
-        <v>892</v>
-      </c>
-      <c r="D79" s="10" t="s">
-        <v>893</v>
-      </c>
-      <c r="E79" s="10" t="s">
-        <v>894</v>
-      </c>
-      <c r="F79" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="G79" s="10" t="s">
+    <row r="79" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="G79" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="H79" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" s="6" customFormat="1">
-      <c r="A80" s="11" t="s">
-        <v>895</v>
-      </c>
-      <c r="B80" s="21" t="s">
-        <v>896</v>
-      </c>
-      <c r="C80" s="10" t="s">
-        <v>897</v>
-      </c>
-      <c r="D80" s="10" t="s">
-        <v>718</v>
-      </c>
-      <c r="E80" s="10" t="s">
-        <v>768</v>
-      </c>
-      <c r="F80" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G80" s="10" t="s">
+      <c r="H79" s="7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="E80" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="F80" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="G80" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="H80" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" s="6" customFormat="1">
-      <c r="A81" s="11" t="s">
-        <v>799</v>
-      </c>
-      <c r="B81" s="21" t="s">
-        <v>898</v>
-      </c>
-      <c r="C81" s="10" t="s">
-        <v>899</v>
-      </c>
-      <c r="D81" s="10" t="s">
-        <v>900</v>
-      </c>
-      <c r="E81" s="10" t="s">
-        <v>735</v>
-      </c>
-      <c r="F81" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="G81" s="10" t="s">
+      <c r="H80" s="9" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="F81" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="G81" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="H81" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" s="6" customFormat="1">
-      <c r="A82" s="11" t="s">
-        <v>392</v>
-      </c>
-      <c r="B82" s="11" t="s">
-        <v>393</v>
+      <c r="H81" s="7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="B82" s="9" t="s">
+        <v>404</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="F82" s="10" t="s">
-        <v>412</v>
-      </c>
-      <c r="G82" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="F82" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="G82" s="7" t="s">
         <v>94</v>
       </c>
       <c r="H82" s="9" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="83" spans="1:8" s="6" customFormat="1">
-      <c r="A83" s="11" t="s">
-        <v>397</v>
-      </c>
-      <c r="B83" s="10" t="s">
-        <v>398</v>
-      </c>
-      <c r="C83" s="10" t="s">
-        <v>399</v>
-      </c>
-      <c r="D83" s="10" t="s">
-        <v>400</v>
-      </c>
-      <c r="E83" s="10" t="s">
-        <v>401</v>
+    <row r="83" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A83" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="C83" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="E83" s="9" t="s">
+        <v>413</v>
       </c>
       <c r="F83" s="9" t="s">
-        <v>412</v>
-      </c>
-      <c r="G83" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="G83" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="H83" s="10" t="s">
+      <c r="H83" s="7" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="84" spans="1:8" s="6" customFormat="1">
-      <c r="A84" s="11" t="s">
-        <v>402</v>
-      </c>
-      <c r="B84" s="9" t="s">
-        <v>403</v>
-      </c>
-      <c r="C84" s="9" t="s">
-        <v>404</v>
-      </c>
-      <c r="D84" s="9" t="s">
-        <v>405</v>
-      </c>
-      <c r="E84" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="F84" s="10" t="s">
-        <v>372</v>
-      </c>
-      <c r="G84" s="10" t="s">
+    <row r="84" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="E84" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="F84" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="G84" s="7" t="s">
         <v>96</v>
       </c>
       <c r="H84" s="9" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="85" spans="1:8" s="6" customFormat="1">
-      <c r="A85" s="11" t="s">
-        <v>407</v>
-      </c>
-      <c r="B85" s="10" t="s">
-        <v>408</v>
-      </c>
-      <c r="C85" s="10" t="s">
-        <v>409</v>
-      </c>
-      <c r="D85" s="10" t="s">
-        <v>410</v>
-      </c>
-      <c r="E85" s="10" t="s">
-        <v>411</v>
+    <row r="85" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="C85" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="E85" s="9" t="s">
+        <v>423</v>
       </c>
       <c r="F85" s="9" t="s">
-        <v>412</v>
-      </c>
-      <c r="G85" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="G85" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="H85" s="10" t="s">
+      <c r="H85" s="7" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="86" spans="1:8" s="6" customFormat="1" ht="28">
-      <c r="A86" s="15" t="s">
-        <v>413</v>
-      </c>
-      <c r="B86" s="10" t="s">
-        <v>414</v>
-      </c>
-      <c r="C86" s="10" t="s">
-        <v>415</v>
-      </c>
-      <c r="D86" s="10" t="s">
-        <v>416</v>
-      </c>
-      <c r="E86" s="10" t="s">
-        <v>417</v>
-      </c>
-      <c r="F86" s="10" t="s">
-        <v>412</v>
-      </c>
-      <c r="G86" s="10" t="s">
+    <row r="86" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="E86" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="G86" s="7" t="s">
         <v>98</v>
       </c>
       <c r="H86" s="9" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="87" spans="1:8" s="6" customFormat="1" ht="42">
-      <c r="A87" s="8" t="s">
-        <v>418</v>
+    <row r="87" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="9" t="s">
+        <v>430</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="F87" s="9" t="s">
-        <v>428</v>
-      </c>
-      <c r="G87" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="G87" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="H87" s="10" t="s">
+      <c r="H87" s="7" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="88" spans="1:8" s="6" customFormat="1" ht="28">
-      <c r="A88" s="15" t="s">
-        <v>423</v>
-      </c>
-      <c r="B88" s="10" t="s">
-        <v>424</v>
-      </c>
-      <c r="C88" s="10" t="s">
-        <v>425</v>
-      </c>
-      <c r="D88" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="E88" s="10" t="s">
-        <v>427</v>
-      </c>
-      <c r="F88" s="10" t="s">
-        <v>428</v>
-      </c>
-      <c r="G88" s="10" t="s">
+    <row r="88" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="E88" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="G88" s="7" t="s">
         <v>100</v>
       </c>
       <c r="H88" s="9" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="89" spans="1:8" s="6" customFormat="1" ht="28">
-      <c r="A89" s="8" t="s">
-        <v>429</v>
+    <row r="89" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="9" t="s">
+        <v>440</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="F89" s="9" t="s">
-        <v>428</v>
-      </c>
-      <c r="G89" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="G89" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="H89" s="10" t="s">
+      <c r="H89" s="7" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="90" spans="1:8" s="6" customFormat="1" ht="42">
-      <c r="A90" s="15" t="s">
-        <v>434</v>
-      </c>
-      <c r="B90" s="10" t="s">
-        <v>435</v>
-      </c>
-      <c r="C90" s="10" t="s">
-        <v>436</v>
-      </c>
-      <c r="D90" s="10" t="s">
-        <v>437</v>
-      </c>
-      <c r="E90" s="10" t="s">
-        <v>438</v>
-      </c>
-      <c r="F90" s="10" t="s">
-        <v>428</v>
-      </c>
-      <c r="G90" s="10" t="s">
+    <row r="90" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="6" t="s">
+        <v>826</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="E90" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="F90" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="G90" s="7" t="s">
         <v>102</v>
       </c>
       <c r="H90" s="9" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="91" spans="1:8" s="6" customFormat="1" ht="42">
-      <c r="A91" s="8" t="s">
-        <v>439</v>
+    <row r="91" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="9" t="s">
+        <v>827</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>440</v>
+        <v>386</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>441</v>
+        <v>385</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>442</v>
+        <v>384</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>443</v>
-      </c>
-      <c r="F91" s="9" t="s">
-        <v>412</v>
-      </c>
-      <c r="G91" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="G91" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="H91" s="10" t="s">
+      <c r="H91" s="7" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="92" spans="1:8" s="6" customFormat="1" ht="42">
-      <c r="A92" s="15" t="s">
-        <v>444</v>
-      </c>
-      <c r="B92" s="10" t="s">
-        <v>445</v>
-      </c>
-      <c r="C92" s="10" t="s">
-        <v>446</v>
-      </c>
-      <c r="D92" s="10" t="s">
-        <v>447</v>
-      </c>
-      <c r="E92" s="10" t="s">
-        <v>448</v>
-      </c>
-      <c r="F92" s="10" t="s">
+    <row r="92" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="7" t="s">
+        <v>828</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="E92" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="F92" s="9" t="s">
         <v>369</v>
       </c>
-      <c r="G92" s="10" t="s">
+      <c r="G92" s="7" t="s">
         <v>104</v>
       </c>
       <c r="H92" s="9" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="93" spans="1:8" s="6" customFormat="1" ht="15">
-      <c r="A93" s="16" t="s">
-        <v>839</v>
-      </c>
-      <c r="B93" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="C93" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="D93" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="E93" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="F93" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="G93" s="10" t="s">
+    <row r="93" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A93" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="E93" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="F93" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="G93" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="H93" s="10" t="s">
+      <c r="H93" s="7" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="94" spans="1:8" s="6" customFormat="1" ht="42">
-      <c r="A94" s="15" t="s">
-        <v>840</v>
-      </c>
-      <c r="B94" s="10" t="s">
-        <v>390</v>
-      </c>
-      <c r="C94" s="10" t="s">
-        <v>389</v>
-      </c>
-      <c r="D94" s="10" t="s">
-        <v>388</v>
-      </c>
-      <c r="E94" s="10" t="s">
-        <v>387</v>
+    <row r="94" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A94" s="9" t="s">
+        <v>829</v>
+      </c>
+      <c r="B94" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="C94" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="D94" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="E94" s="9" t="s">
+        <v>364</v>
       </c>
       <c r="F94" s="9" t="s">
-        <v>391</v>
-      </c>
-      <c r="G94" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="G94" s="7" t="s">
         <v>106</v>
       </c>
       <c r="H94" s="9" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="95" spans="1:8" s="6" customFormat="1">
-      <c r="A95" s="8" t="s">
-        <v>841</v>
-      </c>
-      <c r="B95" s="9" t="s">
-        <v>353</v>
-      </c>
-      <c r="C95" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="D95" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="E95" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="F95" s="10" t="s">
-        <v>369</v>
-      </c>
-      <c r="G95" s="10" t="s">
+    <row r="95" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A95" s="6" t="s">
+        <v>830</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="G95" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="H95" s="10" t="s">
+      <c r="H95" s="7" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="96" spans="1:8" s="6" customFormat="1" ht="28">
-      <c r="A96" s="8" t="s">
-        <v>378</v>
+    <row r="96" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="9" t="s">
+        <v>445</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>357</v>
+        <v>446</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>358</v>
+        <v>447</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>359</v>
+        <v>448</v>
       </c>
       <c r="E96" s="9" t="s">
-        <v>360</v>
+        <v>449</v>
       </c>
       <c r="F96" s="9" t="s">
         <v>370</v>
       </c>
-      <c r="G96" s="10" t="s">
+      <c r="G96" s="7" t="s">
         <v>108</v>
       </c>
       <c r="H96" s="9" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="97" spans="1:8" s="6" customFormat="1" ht="28">
-      <c r="A97" s="15" t="s">
-        <v>842</v>
-      </c>
-      <c r="B97" s="10" t="s">
-        <v>361</v>
-      </c>
-      <c r="C97" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="D97" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="E97" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="F97" s="10" t="s">
-        <v>371</v>
-      </c>
-      <c r="G97" s="10" t="s">
+    <row r="97" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A97" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="E97" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="F97" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="G97" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="H97" s="10" t="s">
+      <c r="H97" s="7" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="98" spans="1:8" s="6" customFormat="1">
-      <c r="A98" s="11" t="s">
-        <v>843</v>
-      </c>
-      <c r="B98" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="C98" s="11" t="s">
-        <v>366</v>
-      </c>
-      <c r="D98" s="11" t="s">
-        <v>367</v>
-      </c>
-      <c r="E98" s="11" t="s">
-        <v>368</v>
-      </c>
-      <c r="F98" s="9" t="s">
-        <v>372</v>
-      </c>
-      <c r="G98" s="10" t="s">
+    <row r="98" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="E98" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="F98" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="G98" s="7" t="s">
         <v>110</v>
       </c>
       <c r="H98" s="9" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="99" spans="1:8" s="6" customFormat="1" ht="28">
-      <c r="A99" s="15" t="s">
-        <v>449</v>
-      </c>
-      <c r="B99" s="10" t="s">
-        <v>450</v>
-      </c>
-      <c r="C99" s="10" t="s">
-        <v>451</v>
-      </c>
-      <c r="D99" s="10" t="s">
-        <v>452</v>
-      </c>
-      <c r="E99" s="10" t="s">
-        <v>453</v>
-      </c>
-      <c r="F99" s="10" t="s">
+    <row r="99" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="B99" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="C99" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="D99" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="E99" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="F99" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="G99" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="H99" s="7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A100" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="E100" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="F100" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="G99" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" s="6" customFormat="1">
-      <c r="A100" s="11" t="s">
-        <v>454</v>
-      </c>
-      <c r="B100" s="11" t="s">
-        <v>455</v>
-      </c>
-      <c r="C100" s="11" t="s">
-        <v>456</v>
-      </c>
-      <c r="D100" s="11" t="s">
-        <v>457</v>
-      </c>
-      <c r="E100" s="11" t="s">
-        <v>458</v>
-      </c>
-      <c r="F100" s="11" t="s">
-        <v>412</v>
-      </c>
-      <c r="G100" s="10" t="s">
+      <c r="G100" s="7" t="s">
         <v>112</v>
       </c>
       <c r="H100" s="9" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="101" spans="1:8" s="6" customFormat="1">
-      <c r="A101" s="11" t="s">
-        <v>459</v>
-      </c>
-      <c r="B101" s="11" t="s">
-        <v>460</v>
-      </c>
-      <c r="C101" s="11" t="s">
-        <v>461</v>
-      </c>
-      <c r="D101" s="11" t="s">
-        <v>462</v>
-      </c>
-      <c r="E101" s="11" t="s">
-        <v>463</v>
-      </c>
-      <c r="F101" s="11" t="s">
-        <v>412</v>
-      </c>
-      <c r="G101" s="10" t="s">
+    <row r="101" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="B101" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="C101" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="D101" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="E101" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="F101" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="G101" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="H101" s="10" t="s">
+      <c r="H101" s="7" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="102" spans="1:8" s="6" customFormat="1" ht="28">
-      <c r="A102" s="15" t="s">
-        <v>464</v>
-      </c>
-      <c r="B102" s="10" t="s">
-        <v>465</v>
-      </c>
-      <c r="C102" s="10" t="s">
-        <v>466</v>
-      </c>
-      <c r="D102" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="E102" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="F102" s="10" t="s">
-        <v>412</v>
-      </c>
-      <c r="G102" s="10" t="s">
+    <row r="102" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A102" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="E102" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="G102" s="7" t="s">
         <v>114</v>
       </c>
       <c r="H102" s="9" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="103" spans="1:8" s="6" customFormat="1" ht="28">
-      <c r="A103" s="8" t="s">
-        <v>469</v>
+    <row r="103" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A103" s="9" t="s">
+        <v>480</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="F103" s="9" t="s">
-        <v>370</v>
-      </c>
-      <c r="G103" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="G103" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="H103" s="10" t="s">
+      <c r="H103" s="7" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="104" spans="1:8" s="6" customFormat="1" ht="28">
-      <c r="A104" s="15" t="s">
-        <v>474</v>
-      </c>
-      <c r="B104" s="10" t="s">
-        <v>475</v>
-      </c>
-      <c r="C104" s="10" t="s">
-        <v>476</v>
-      </c>
-      <c r="D104" s="10" t="s">
-        <v>477</v>
-      </c>
-      <c r="E104" s="10" t="s">
-        <v>478</v>
-      </c>
-      <c r="F104" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="G104" s="10" t="s">
+    <row r="104" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>486</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="E104" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="F104" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="G104" s="7" t="s">
         <v>116</v>
       </c>
       <c r="H104" s="9" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="105" spans="1:8" s="6" customFormat="1" ht="28">
-      <c r="A105" s="8" t="s">
-        <v>479</v>
+    <row r="105" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A105" s="9" t="s">
+        <v>490</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="F105" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="G105" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="G105" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="H105" s="10" t="s">
+      <c r="H105" s="7" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="106" spans="1:8" s="6" customFormat="1" ht="42">
-      <c r="A106" s="15" t="s">
-        <v>484</v>
-      </c>
-      <c r="B106" s="10" t="s">
-        <v>485</v>
-      </c>
-      <c r="C106" s="10" t="s">
-        <v>486</v>
-      </c>
-      <c r="D106" s="10" t="s">
-        <v>487</v>
-      </c>
-      <c r="E106" s="10" t="s">
-        <v>488</v>
-      </c>
-      <c r="F106" s="10" t="s">
+    <row r="106" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A106" s="7" t="s">
+        <v>496</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>497</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>498</v>
+      </c>
+      <c r="D106" s="7" t="s">
         <v>499</v>
       </c>
-      <c r="G106" s="10" t="s">
+      <c r="E106" s="7" t="s">
+        <v>500</v>
+      </c>
+      <c r="F106" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="G106" s="7" t="s">
         <v>118</v>
       </c>
       <c r="H106" s="9" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="107" spans="1:8" s="6" customFormat="1" ht="42">
-      <c r="A107" s="8" t="s">
-        <v>489</v>
+    <row r="107" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A107" s="9" t="s">
+        <v>501</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="C107" s="9" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="F107" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="G107" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="G107" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="H107" s="10" t="s">
+      <c r="H107" s="7" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="108" spans="1:8" s="6" customFormat="1" ht="28">
-      <c r="A108" s="15" t="s">
-        <v>494</v>
-      </c>
-      <c r="B108" s="10" t="s">
-        <v>495</v>
-      </c>
-      <c r="C108" s="10" t="s">
-        <v>496</v>
-      </c>
-      <c r="D108" s="10" t="s">
-        <v>497</v>
-      </c>
-      <c r="E108" s="10" t="s">
-        <v>498</v>
-      </c>
-      <c r="F108" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="G108" s="10" t="s">
+    <row r="108" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A108" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>509</v>
+      </c>
+      <c r="E108" s="7" t="s">
+        <v>510</v>
+      </c>
+      <c r="F108" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="G108" s="7" t="s">
         <v>120</v>
       </c>
       <c r="H108" s="9" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="109" spans="1:8" s="6" customFormat="1" ht="42">
-      <c r="A109" s="8" t="s">
-        <v>500</v>
+    <row r="109" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A109" s="9" t="s">
+        <v>511</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>501</v>
+        <v>512</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="F109" s="9" t="s">
-        <v>370</v>
-      </c>
-      <c r="G109" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="G109" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="H109" s="10" t="s">
+      <c r="H109" s="7" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="110" spans="1:8" s="6" customFormat="1" ht="28">
-      <c r="A110" s="15" t="s">
-        <v>505</v>
-      </c>
-      <c r="B110" s="10" t="s">
-        <v>506</v>
-      </c>
-      <c r="C110" s="10" t="s">
-        <v>507</v>
-      </c>
-      <c r="D110" s="10" t="s">
-        <v>508</v>
-      </c>
-      <c r="E110" s="10" t="s">
-        <v>509</v>
-      </c>
-      <c r="F110" s="10" t="s">
-        <v>428</v>
-      </c>
-      <c r="G110" s="10" t="s">
+    <row r="110" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A110" s="7" t="s">
+        <v>516</v>
+      </c>
+      <c r="B110" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>518</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="E110" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="F110" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="G110" s="7" t="s">
         <v>122</v>
       </c>
       <c r="H110" s="9" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="111" spans="1:8" s="6" customFormat="1" ht="28">
-      <c r="A111" s="8" t="s">
-        <v>510</v>
-      </c>
-      <c r="B111" s="9" t="s">
-        <v>511</v>
-      </c>
-      <c r="C111" s="9" t="s">
-        <v>512</v>
-      </c>
-      <c r="D111" s="9" t="s">
-        <v>513</v>
-      </c>
-      <c r="E111" s="9" t="s">
-        <v>514</v>
-      </c>
+    <row r="111" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A111" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="B111" s="9"/>
+      <c r="C111" s="9"/>
+      <c r="D111" s="9"/>
+      <c r="E111" s="9"/>
       <c r="F111" s="9" t="s">
-        <v>525</v>
-      </c>
-      <c r="G111" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="G111" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="H111" s="10" t="s">
+      <c r="H111" s="7" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="112" spans="1:8" s="6" customFormat="1" ht="28">
-      <c r="A112" s="15" t="s">
-        <v>515</v>
-      </c>
-      <c r="B112" s="10" t="s">
-        <v>516</v>
-      </c>
-      <c r="C112" s="10" t="s">
-        <v>517</v>
-      </c>
-      <c r="D112" s="10" t="s">
-        <v>518</v>
-      </c>
-      <c r="E112" s="10" t="s">
-        <v>519</v>
-      </c>
-      <c r="F112" s="10" t="s">
-        <v>369</v>
-      </c>
-      <c r="G112" s="10" t="s">
+    <row r="112" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A112" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="B112" s="7"/>
+      <c r="C112" s="7"/>
+      <c r="D112" s="7"/>
+      <c r="E112" s="7"/>
+      <c r="F112" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="G112" s="7" t="s">
         <v>124</v>
       </c>
       <c r="H112" s="9" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="113" spans="1:8" s="6" customFormat="1" ht="42">
-      <c r="A113" s="8" t="s">
-        <v>520</v>
-      </c>
-      <c r="B113" s="9" t="s">
-        <v>521</v>
-      </c>
-      <c r="C113" s="9" t="s">
-        <v>522</v>
-      </c>
-      <c r="D113" s="9" t="s">
-        <v>523</v>
-      </c>
-      <c r="E113" s="9" t="s">
-        <v>524</v>
-      </c>
+    <row r="113" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A113" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="B113" s="9"/>
+      <c r="C113" s="9"/>
+      <c r="D113" s="9"/>
+      <c r="E113" s="9"/>
       <c r="F113" s="9" t="s">
-        <v>526</v>
-      </c>
-      <c r="G113" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="G113" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="H113" s="10" t="s">
+      <c r="H113" s="7" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="114" spans="1:8" s="6" customFormat="1" ht="28">
-      <c r="A114" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="B114" s="10"/>
-      <c r="C114" s="10"/>
-      <c r="D114" s="10"/>
-      <c r="E114" s="10"/>
-      <c r="F114" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="G114" s="10" t="s">
+    <row r="114" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A114" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B114" s="7"/>
+      <c r="C114" s="7"/>
+      <c r="D114" s="7"/>
+      <c r="E114" s="7"/>
+      <c r="F114" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="G114" s="7" t="s">
         <v>126</v>
       </c>
       <c r="H114" s="9" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="115" spans="1:8" s="6" customFormat="1">
-      <c r="A115" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="B115" s="9"/>
-      <c r="C115" s="9"/>
-      <c r="D115" s="9"/>
-      <c r="E115" s="9"/>
-      <c r="F115" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="G115" s="10" t="s">
+    <row r="115" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A115" s="6" t="s">
+        <v>893</v>
+      </c>
+      <c r="B115" s="6"/>
+      <c r="C115" s="6"/>
+      <c r="D115" s="6"/>
+      <c r="E115" s="6"/>
+      <c r="F115" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G115" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="H115" s="10" t="s">
+      <c r="H115" s="7" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="116" spans="1:8" s="6" customFormat="1">
-      <c r="A116" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="B116" s="10"/>
-      <c r="C116" s="10"/>
-      <c r="D116" s="10"/>
-      <c r="E116" s="10"/>
-      <c r="F116" s="10" t="s">
+    <row r="116" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A116" s="6" t="s">
+        <v>892</v>
+      </c>
+      <c r="B116" s="6"/>
+      <c r="C116" s="6"/>
+      <c r="D116" s="6"/>
+      <c r="E116" s="6"/>
+      <c r="F116" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="G116" s="10" t="s">
+      <c r="G116" s="7" t="s">
         <v>128</v>
       </c>
       <c r="H116" s="9" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="117" spans="1:8" s="6" customFormat="1" ht="28">
-      <c r="A117" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="B117" s="9"/>
-      <c r="C117" s="9"/>
-      <c r="D117" s="9"/>
-      <c r="E117" s="9"/>
-      <c r="F117" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="G117" s="10" t="s">
+    <row r="117" spans="1:8" s="8" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+      <c r="A117" s="6" t="s">
+        <v>895</v>
+      </c>
+      <c r="B117" s="6"/>
+      <c r="C117" s="6"/>
+      <c r="D117" s="6"/>
+      <c r="E117" s="6"/>
+      <c r="F117" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G117" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="H117" s="10" t="s">
+      <c r="H117" s="7" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="118" spans="1:8" s="6" customFormat="1" ht="16">
-      <c r="A118" s="11" t="s">
-        <v>844</v>
-      </c>
-      <c r="B118" s="11"/>
-      <c r="C118" s="11"/>
-      <c r="D118" s="11"/>
-      <c r="E118" s="11"/>
-      <c r="F118" s="11" t="s">
+    <row r="118" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A118" s="6" t="s">
+        <v>561</v>
+      </c>
+      <c r="B118" s="6"/>
+      <c r="C118" s="6"/>
+      <c r="D118" s="6"/>
+      <c r="E118" s="6"/>
+      <c r="F118" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="G118" s="10" t="s">
+      <c r="G118" s="7" t="s">
         <v>130</v>
       </c>
       <c r="H118" s="9" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="119" spans="1:8" s="6" customFormat="1" ht="16">
-      <c r="A119" s="11" t="s">
-        <v>845</v>
-      </c>
-      <c r="B119" s="11"/>
-      <c r="C119" s="11"/>
-      <c r="D119" s="11"/>
-      <c r="E119" s="11"/>
-      <c r="F119" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="G119" s="10" t="s">
+    <row r="119" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A119" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="B119" s="9"/>
+      <c r="C119" s="9"/>
+      <c r="D119" s="9"/>
+      <c r="E119" s="9"/>
+      <c r="F119" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="G119" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="H119" s="10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" s="6" customFormat="1" ht="16">
-      <c r="A120" s="11" t="s">
-        <v>846</v>
-      </c>
-      <c r="B120" s="11"/>
-      <c r="C120" s="11"/>
-      <c r="D120" s="11"/>
-      <c r="E120" s="11"/>
-      <c r="F120" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="G120" s="10" t="s">
+      <c r="H119" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A120" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="B120" s="7"/>
+      <c r="C120" s="7"/>
+      <c r="D120" s="7"/>
+      <c r="E120" s="7"/>
+      <c r="F120" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G120" s="7" t="s">
         <v>132</v>
       </c>
       <c r="H120" s="9" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" s="6" customFormat="1">
-      <c r="A121" s="11" t="s">
-        <v>565</v>
-      </c>
-      <c r="B121" s="11"/>
-      <c r="C121" s="11"/>
-      <c r="D121" s="11"/>
-      <c r="E121" s="11"/>
-      <c r="F121" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="G121" s="10" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A121" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="B121" s="9"/>
+      <c r="C121" s="9"/>
+      <c r="D121" s="9"/>
+      <c r="E121" s="9"/>
+      <c r="F121" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G121" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="H121" s="10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" s="6" customFormat="1" ht="28">
-      <c r="A122" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="B122" s="10"/>
-      <c r="C122" s="10"/>
-      <c r="D122" s="10"/>
-      <c r="E122" s="10"/>
-      <c r="F122" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="G122" s="10" t="s">
+      <c r="H121" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A122" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B122" s="9"/>
+      <c r="C122" s="9"/>
+      <c r="D122" s="9"/>
+      <c r="E122" s="9"/>
+      <c r="F122" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="G122" s="7" t="s">
         <v>134</v>
       </c>
       <c r="H122" s="9" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="123" spans="1:8" s="6" customFormat="1">
-      <c r="A123" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="B123" s="9"/>
-      <c r="C123" s="9"/>
-      <c r="D123" s="9"/>
-      <c r="E123" s="9"/>
-      <c r="F123" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G123" s="10" t="s">
+    <row r="123" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A123" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="B123" s="7"/>
+      <c r="C123" s="7"/>
+      <c r="D123" s="7"/>
+      <c r="E123" s="7"/>
+      <c r="F123" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="G123" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="H123" s="10" t="s">
+      <c r="H123" s="7" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="124" spans="1:8" s="6" customFormat="1" ht="28">
-      <c r="A124" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="B124" s="10"/>
-      <c r="C124" s="10"/>
-      <c r="D124" s="10"/>
-      <c r="E124" s="10"/>
-      <c r="F124" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="G124" s="10" t="s">
+    <row r="124" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A124" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="B124" s="9"/>
+      <c r="C124" s="9"/>
+      <c r="D124" s="9"/>
+      <c r="E124" s="9"/>
+      <c r="F124" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="G124" s="7" t="s">
         <v>136</v>
       </c>
       <c r="H124" s="9" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="125" spans="1:8" s="6" customFormat="1">
-      <c r="A125" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="B125" s="10"/>
-      <c r="C125" s="10"/>
-      <c r="D125" s="10"/>
-      <c r="E125" s="10"/>
-      <c r="F125" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="G125" s="10" t="s">
+    <row r="125" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A125" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="B125" s="7"/>
+      <c r="C125" s="7"/>
+      <c r="D125" s="7"/>
+      <c r="E125" s="7"/>
+      <c r="F125" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="G125" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="H125" s="10" t="s">
+      <c r="H125" s="7" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="126" spans="1:8" s="6" customFormat="1">
-      <c r="A126" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="B126" s="9"/>
-      <c r="C126" s="9"/>
-      <c r="D126" s="9"/>
-      <c r="E126" s="9"/>
-      <c r="F126" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="G126" s="10" t="s">
+    <row r="126" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A126" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="B126" s="7"/>
+      <c r="C126" s="7"/>
+      <c r="D126" s="7"/>
+      <c r="E126" s="7"/>
+      <c r="F126" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="G126" s="7" t="s">
         <v>138</v>
       </c>
       <c r="H126" s="9" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="127" spans="1:8" s="6" customFormat="1">
-      <c r="A127" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="B127" s="10"/>
-      <c r="C127" s="10"/>
-      <c r="D127" s="10"/>
-      <c r="E127" s="10"/>
-      <c r="F127" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="G127" s="10" t="s">
+    <row r="127" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A127" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="B127" s="9"/>
+      <c r="C127" s="9"/>
+      <c r="D127" s="9"/>
+      <c r="E127" s="9"/>
+      <c r="F127" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G127" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="H127" s="10" t="s">
+      <c r="H127" s="7" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="128" spans="1:8" s="6" customFormat="1">
-      <c r="A128" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="B128" s="9"/>
-      <c r="C128" s="9"/>
-      <c r="D128" s="9"/>
-      <c r="E128" s="9"/>
-      <c r="F128" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="G128" s="10" t="s">
+    <row r="128" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A128" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="B128" s="7"/>
+      <c r="C128" s="7"/>
+      <c r="D128" s="7"/>
+      <c r="E128" s="7"/>
+      <c r="F128" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="G128" s="7" t="s">
         <v>145</v>
       </c>
       <c r="H128" s="9" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="129" spans="1:8" s="6" customFormat="1">
-      <c r="A129" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="B129" s="9"/>
-      <c r="C129" s="9"/>
-      <c r="D129" s="9"/>
-      <c r="E129" s="9"/>
-      <c r="F129" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="G129" s="10" t="s">
+    <row r="129" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A129" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="B129" s="7"/>
+      <c r="C129" s="7"/>
+      <c r="D129" s="7"/>
+      <c r="E129" s="7"/>
+      <c r="F129" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G129" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="H129" s="10" t="s">
+      <c r="H129" s="7" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="130" spans="1:8" s="6" customFormat="1">
-      <c r="A130" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="B130" s="10"/>
-      <c r="C130" s="10"/>
-      <c r="D130" s="10"/>
-      <c r="E130" s="10"/>
-      <c r="F130" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="G130" s="10" t="s">
+    <row r="130" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A130" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="B130" s="9"/>
+      <c r="C130" s="9"/>
+      <c r="D130" s="9"/>
+      <c r="E130" s="9"/>
+      <c r="F130" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="G130" s="7" t="s">
         <v>149</v>
       </c>
       <c r="H130" s="9" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="131" spans="1:8" s="6" customFormat="1">
-      <c r="A131" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="B131" s="9"/>
-      <c r="C131" s="9"/>
-      <c r="D131" s="9"/>
-      <c r="E131" s="9"/>
-      <c r="F131" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="G131" s="10" t="s">
+    <row r="131" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A131" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="B131" s="7"/>
+      <c r="C131" s="7"/>
+      <c r="D131" s="7"/>
+      <c r="E131" s="7"/>
+      <c r="F131" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="G131" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="H131" s="10" t="s">
+      <c r="H131" s="7" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="132" spans="1:8" s="6" customFormat="1">
-      <c r="A132" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="B132" s="9"/>
-      <c r="C132" s="9"/>
-      <c r="D132" s="9"/>
-      <c r="E132" s="9"/>
-      <c r="F132" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="G132" s="10" t="s">
+    <row r="132" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A132" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="B132" s="6"/>
+      <c r="C132" s="6"/>
+      <c r="D132" s="6"/>
+      <c r="E132" s="6"/>
+      <c r="F132" s="11" t="s">
+        <v>876</v>
+      </c>
+      <c r="G132" s="7" t="s">
         <v>151</v>
       </c>
       <c r="H132" s="9" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="133" spans="1:8" s="6" customFormat="1">
-      <c r="A133" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="B133" s="10"/>
-      <c r="C133" s="10"/>
-      <c r="D133" s="10"/>
-      <c r="E133" s="10"/>
-      <c r="F133" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="G133" s="10" t="s">
+    <row r="133" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A133" s="6" t="s">
+        <v>884</v>
+      </c>
+      <c r="B133" s="6"/>
+      <c r="C133" s="6"/>
+      <c r="D133" s="6"/>
+      <c r="E133" s="6"/>
+      <c r="F133" s="11" t="s">
+        <v>877</v>
+      </c>
+      <c r="G133" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="H133" s="10" t="s">
+      <c r="H133" s="7" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="134" spans="1:8" s="6" customFormat="1">
-      <c r="A134" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="B134" s="9"/>
-      <c r="C134" s="9"/>
-      <c r="D134" s="9"/>
-      <c r="E134" s="9"/>
-      <c r="F134" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="G134" s="10" t="s">
-        <v>901</v>
+    <row r="134" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A134" s="6" t="s">
+        <v>891</v>
+      </c>
+      <c r="B134" s="6"/>
+      <c r="C134" s="6"/>
+      <c r="D134" s="6"/>
+      <c r="E134" s="6"/>
+      <c r="F134" s="11" t="s">
+        <v>878</v>
+      </c>
+      <c r="G134" s="7" t="s">
+        <v>869</v>
       </c>
       <c r="H134" s="9" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="135" spans="1:8" s="6" customFormat="1" ht="16">
-      <c r="A135" s="11" t="s">
-        <v>566</v>
-      </c>
-      <c r="B135" s="11"/>
-      <c r="C135" s="11"/>
-      <c r="D135" s="11"/>
-      <c r="E135" s="11"/>
-      <c r="F135" s="20" t="s">
-        <v>847</v>
-      </c>
-      <c r="G135" s="10" t="s">
-        <v>902</v>
-      </c>
-      <c r="H135" s="10" t="s">
+    <row r="135" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A135" s="6" t="s">
+        <v>890</v>
+      </c>
+      <c r="B135" s="6"/>
+      <c r="C135" s="6"/>
+      <c r="D135" s="6"/>
+      <c r="E135" s="6"/>
+      <c r="F135" s="11" t="s">
+        <v>879</v>
+      </c>
+      <c r="G135" s="9" t="s">
+        <v>870</v>
+      </c>
+      <c r="H135" s="7" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="136" spans="1:8" s="6" customFormat="1" ht="16">
-      <c r="A136" s="11" t="s">
-        <v>848</v>
-      </c>
-      <c r="B136" s="11"/>
-      <c r="C136" s="11"/>
-      <c r="D136" s="11"/>
-      <c r="E136" s="11"/>
-      <c r="F136" s="20" t="s">
-        <v>849</v>
-      </c>
-      <c r="G136" s="10" t="s">
-        <v>903</v>
+    <row r="136" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A136" s="6" t="s">
+        <v>889</v>
+      </c>
+      <c r="B136" s="6"/>
+      <c r="C136" s="6"/>
+      <c r="D136" s="6"/>
+      <c r="E136" s="6"/>
+      <c r="F136" s="11" t="s">
+        <v>879</v>
+      </c>
+      <c r="G136" s="7" t="s">
+        <v>871</v>
       </c>
       <c r="H136" s="9" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="137" spans="1:8" s="6" customFormat="1" ht="16">
-      <c r="A137" s="11" t="s">
-        <v>850</v>
-      </c>
-      <c r="B137" s="11"/>
-      <c r="C137" s="11"/>
-      <c r="D137" s="11"/>
-      <c r="E137" s="11"/>
-      <c r="F137" s="20" t="s">
-        <v>851</v>
-      </c>
-      <c r="G137" s="10" t="s">
-        <v>904</v>
-      </c>
-      <c r="H137" s="10" t="s">
+    <row r="137" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A137" s="6" t="s">
+        <v>888</v>
+      </c>
+      <c r="B137" s="6"/>
+      <c r="C137" s="6"/>
+      <c r="D137" s="6"/>
+      <c r="E137" s="6"/>
+      <c r="F137" s="11" t="s">
+        <v>880</v>
+      </c>
+      <c r="G137" s="9" t="s">
+        <v>872</v>
+      </c>
+      <c r="H137" s="7" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="138" spans="1:8" s="6" customFormat="1" ht="16">
-      <c r="A138" s="11" t="s">
-        <v>852</v>
-      </c>
-      <c r="B138" s="11"/>
-      <c r="C138" s="11"/>
-      <c r="D138" s="11"/>
-      <c r="E138" s="11"/>
-      <c r="F138" s="20" t="s">
-        <v>853</v>
-      </c>
-      <c r="G138" s="10" t="s">
-        <v>905</v>
+    <row r="138" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A138" s="6" t="s">
+        <v>886</v>
+      </c>
+      <c r="B138" s="6"/>
+      <c r="C138" s="6"/>
+      <c r="D138" s="6"/>
+      <c r="E138" s="6"/>
+      <c r="F138" s="11" t="s">
+        <v>881</v>
+      </c>
+      <c r="G138" s="7" t="s">
+        <v>873</v>
       </c>
       <c r="H138" s="9" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="139" spans="1:8" s="6" customFormat="1" ht="16">
-      <c r="A139" s="11" t="s">
-        <v>854</v>
-      </c>
-      <c r="B139" s="11"/>
-      <c r="C139" s="11"/>
-      <c r="D139" s="11"/>
-      <c r="E139" s="11"/>
-      <c r="F139" s="20" t="s">
-        <v>853</v>
-      </c>
-      <c r="G139" s="10" t="s">
-        <v>906</v>
-      </c>
-      <c r="H139" s="10" t="s">
+    <row r="139" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A139" s="6" t="s">
+        <v>885</v>
+      </c>
+      <c r="B139" s="6"/>
+      <c r="C139" s="6"/>
+      <c r="D139" s="6"/>
+      <c r="E139" s="6"/>
+      <c r="F139" s="11" t="s">
+        <v>882</v>
+      </c>
+      <c r="G139" s="9" t="s">
+        <v>874</v>
+      </c>
+      <c r="H139" s="7" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="140" spans="1:8" s="6" customFormat="1" ht="16">
-      <c r="A140" s="11" t="s">
-        <v>855</v>
-      </c>
-      <c r="B140" s="11"/>
-      <c r="C140" s="11"/>
-      <c r="D140" s="11"/>
-      <c r="E140" s="11"/>
-      <c r="F140" s="20" t="s">
-        <v>856</v>
-      </c>
-      <c r="G140" s="10" t="s">
-        <v>907</v>
+    <row r="140" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A140" s="6" t="s">
+        <v>887</v>
+      </c>
+      <c r="B140" s="6"/>
+      <c r="C140" s="6"/>
+      <c r="D140" s="6"/>
+      <c r="E140" s="6"/>
+      <c r="F140" s="11" t="s">
+        <v>883</v>
+      </c>
+      <c r="G140" s="7" t="s">
+        <v>875</v>
       </c>
       <c r="H140" s="9" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" s="6" customFormat="1" ht="16">
-      <c r="A141" s="11" t="s">
-        <v>857</v>
-      </c>
-      <c r="B141" s="11"/>
-      <c r="C141" s="11"/>
-      <c r="D141" s="11"/>
-      <c r="E141" s="11"/>
-      <c r="F141" s="20" t="s">
-        <v>858</v>
-      </c>
-      <c r="G141" s="10" t="s">
-        <v>908</v>
-      </c>
-      <c r="H141" s="10" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8" s="6" customFormat="1" ht="16">
-      <c r="A142" s="11" t="s">
-        <v>859</v>
-      </c>
-      <c r="B142" s="11"/>
-      <c r="C142" s="11"/>
-      <c r="D142" s="11"/>
-      <c r="E142" s="11"/>
-      <c r="F142" s="20" t="s">
-        <v>860</v>
-      </c>
-      <c r="G142" s="10" t="s">
-        <v>909</v>
-      </c>
-      <c r="H142" s="9" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" s="6" customFormat="1" ht="16">
-      <c r="A143" s="11" t="s">
-        <v>861</v>
-      </c>
-      <c r="B143" s="11"/>
-      <c r="C143" s="11"/>
-      <c r="D143" s="11"/>
-      <c r="E143" s="11"/>
-      <c r="F143" s="20" t="s">
-        <v>862</v>
-      </c>
-      <c r="G143" s="10" t="s">
-        <v>910</v>
-      </c>
-      <c r="H143" s="10" t="s">
         <v>156</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A13"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="18">
+    <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="5"/>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>190</v>
       </c>

--- a/data/ontap111.xlsx
+++ b/data/ontap111.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tdtam\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73960C09-28ED-4317-A116-971EF6D55214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD6325A9-1B2E-4501-9FBD-C4B99109DA6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2418" uniqueCount="1682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2422" uniqueCount="1685">
   <si>
     <t>Họ tên</t>
   </si>
@@ -2073,36 +2073,12 @@
     <t>Cơ chế "plug &amp; play" giúp hệ điều hành?</t>
   </si>
   <si>
-    <t>a) nhận biết thiết bị ngoại vi và hỗ trợ cài đặt các chương trình điều khiển một cách thụ động</t>
-  </si>
-  <si>
-    <t>b) Nhận biết thiết bị nội hàm và hỗ trợ cài đặt các chương trình điều khiển một cách tự động</t>
-  </si>
-  <si>
-    <t>c) Xóa bỏ thiết bị ngoại vi và hỗ trợ cài đặt các chương trình điều khiển một cách tự động</t>
-  </si>
-  <si>
-    <t>d) Nhận biết thiết bị ngoại vi và hỗ trợ cài đặt các chương trình điều khiển một cách tự động</t>
-  </si>
-  <si>
     <t>Q091</t>
   </si>
   <si>
     <t>Theo em, phát biểu nào đúng, phát biểu nào sai khi nói về phần mềm máy tính?</t>
   </si>
   <si>
-    <t>a) Hệ điều hành Windows là phần mềm tự do.</t>
-  </si>
-  <si>
-    <t>b) Phần mềm đóng gói được thiết kế dựa trên những yêu cầu chung của nhiểu người.</t>
-  </si>
-  <si>
-    <t>c) Phần mềm mã nguồn mở là phần mềm không có bản quyền, phần mềm mã nguồn đóng là phần mềm có bản quyền.</t>
-  </si>
-  <si>
-    <t>d) Phần mềm mã nguồn mở càng phát triển thì chắc chắn thị trường phần mềm thương mại càng suy giảm.</t>
-  </si>
-  <si>
     <t>SĐSS</t>
   </si>
   <si>
@@ -2112,18 +2088,6 @@
     <t>Cho hai số A, B và C là các biểu diễn dạng nhị phân:  A = 10110; B = 1100101; C = 11.</t>
   </si>
   <si>
-    <t>a) Số A biểu diễn số 44 trong hệ thập phân.</t>
-  </si>
-  <si>
-    <t>b) Kết quả phép toán A + B là 1111011.</t>
-  </si>
-  <si>
-    <t>c) Kết quả phép toán A AND C là 111210.</t>
-  </si>
-  <si>
-    <t>d) Máy tính thực hiện các phép toán nhị phân bằng cách kết hợp các mạch logic.</t>
-  </si>
-  <si>
     <t>SĐSĐ</t>
   </si>
   <si>
@@ -2133,18 +2097,6 @@
     <t>Hiện nay, việc sử dụng mạng internet để trao đổi thông tin rất phổ biến. Có nhiều ứng dụng để thực hiện gửi thư điện tử và mạng xã hội. Trong đó, sử dụng phổ biến nhất là gmail và facebook.</t>
   </si>
   <si>
-    <t>a) Gmail là một dịch vụ gửi thư điện tử không thể đính kèm tệp tin.</t>
-  </si>
-  <si>
-    <t>b) Tất cả thông tin chúng ta chia sẻ trên facebook đều ở chế độ công khai, chúng ta không thể để ở chế độ riêng tư chỉ mình biết.</t>
-  </si>
-  <si>
-    <t>c) Facebook khi đã được bảo mật bằng 2 lớp nhưng chúng ta không thể chia sẻ tất cả thông tin cá nhân của mình lên trang cá nhân để đảm bảo an toàn dữ liệu.</t>
-  </si>
-  <si>
-    <t>d) Để phân loại thư điện tự chúng ta sử dụng Nhãn cho các thư.</t>
-  </si>
-  <si>
     <t>Q094</t>
   </si>
   <si>
@@ -3105,18 +3057,9 @@
     <t>Máy in laser công nghiệp nặng</t>
   </si>
   <si>
-    <t>Máy in phun màu 6 màu mực C. Máy in kim khổ A4</t>
-  </si>
-  <si>
     <t>Một cửa hàng tiện lợi cần trang bị máy in hóa đơn thanh toán cho khách hàng với yêu cầu: tốc độ in cực nhanh, thiết kế nhỏ gọn, không tốn chi phí thay mực rời. Lựa chọn máy in nào sau đây là tối ưu nhất?</t>
   </si>
   <si>
-    <t>Tháo máy chiếu ra để hàn thêm cổng HDMI D. Sử dụng dây mạng LAN để cắm trực tiếp vào máy chiếu</t>
-  </si>
-  <si>
-    <t>Bắt buộc phải mua máy tính xách tay mới có cổng VGA B. Sử dụng bộ chuyển đổi tín hiệu từ HDMI sang VGA phù hợp.</t>
-  </si>
-  <si>
     <t>Thầy giáo muốn kết nối máy tính xách tay với máy chiếu trong hội trường để giảng dạy. Máy tính xách tay chỉ có cổng HDMI, trong khi máy chiếu đời cũ chỉ có cổng kết nối VGA. Giải pháp kỹ thuật xử lý tình huống này là gì?</t>
   </si>
   <si>
@@ -5071,6 +5014,72 @@
   </si>
   <si>
     <t>Giá trị của số 111010 là bao nhiêu sang hệ thập phân?</t>
+  </si>
+  <si>
+    <t>Bắt buộc phải mua máy tính xách tay mới có cổng VGA</t>
+  </si>
+  <si>
+    <t>Sử dụng bộ chuyển đổi tín hiệu từ HDMI sang VGA phù hợp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tháo máy chiếu ra để hàn thêm cổng HDMI </t>
+  </si>
+  <si>
+    <t>Sử dụng dây mạng LAN để cắm trực tiếp vào máy chiếu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Máy in phun màu 6 màu mực </t>
+  </si>
+  <si>
+    <t>Máy in kim khổ A4</t>
+  </si>
+  <si>
+    <t>Nhận biết thiết bị ngoại vi và hỗ trợ cài đặt các chương trình điều khiển một cách thụ động</t>
+  </si>
+  <si>
+    <t>Nhận biết thiết bị nội hàm và hỗ trợ cài đặt các chương trình điều khiển một cách tự động</t>
+  </si>
+  <si>
+    <t>Xóa bỏ thiết bị ngoại vi và hỗ trợ cài đặt các chương trình điều khiển một cách tự động</t>
+  </si>
+  <si>
+    <t>Nhận biết thiết bị ngoại vi và hỗ trợ cài đặt các chương trình điều khiển một cách tự động</t>
+  </si>
+  <si>
+    <t>Hệ điều hành Windows là phần mềm tự do.</t>
+  </si>
+  <si>
+    <t>Phần mềm đóng gói được thiết kế dựa trên những yêu cầu chung của nhiểu người.</t>
+  </si>
+  <si>
+    <t>Phần mềm mã nguồn mở là phần mềm không có bản quyền, phần mềm mã nguồn đóng là phần mềm có bản quyền.</t>
+  </si>
+  <si>
+    <t>Phần mềm mã nguồn mở càng phát triển thì chắc chắn thị trường phần mềm thương mại càng suy giảm.</t>
+  </si>
+  <si>
+    <t>Số A biểu diễn số 44 trong hệ thập phân.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Kết quả phép toán A + B là 1111011.</t>
+  </si>
+  <si>
+    <t>Kết quả phép toán A AND C là 111210.</t>
+  </si>
+  <si>
+    <t>Máy tính thực hiện các phép toán nhị phân bằng cách kết hợp các mạch logic.</t>
+  </si>
+  <si>
+    <t>Gmail là một dịch vụ gửi thư điện tử không thể đính kèm tệp tin.</t>
+  </si>
+  <si>
+    <t>Tất cả thông tin chúng ta chia sẻ trên facebook đều ở chế độ công khai, chúng ta không thể để ở chế độ riêng tư chỉ mình biết.</t>
+  </si>
+  <si>
+    <t>Facebook khi đã được bảo mật bằng 2 lớp nhưng chúng ta không thể chia sẻ tất cả thông tin cá nhân của mình lên trang cá nhân để đảm bảo an toàn dữ liệu.</t>
+  </si>
+  <si>
+    <t>Để phân loại thư điện tự chúng ta sử dụng Nhãn cho các thư.</t>
   </si>
 </sst>
 </file>
@@ -6866,19 +6875,19 @@
     </row>
     <row r="2" spans="1:14" ht="37.5">
       <c r="A2" s="8" t="s">
-        <v>1462</v>
+        <v>1443</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1461</v>
+        <v>1442</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>1460</v>
+        <v>1441</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>1459</v>
+        <v>1440</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>1458</v>
+        <v>1439</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>186</v>
@@ -6898,19 +6907,19 @@
     </row>
     <row r="3" spans="1:14" ht="25">
       <c r="A3" s="8" t="s">
-        <v>1457</v>
+        <v>1438</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>1456</v>
+        <v>1437</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>1455</v>
+        <v>1436</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>1454</v>
+        <v>1435</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>1453</v>
+        <v>1434</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>200</v>
@@ -6930,19 +6939,19 @@
     </row>
     <row r="4" spans="1:14" ht="25">
       <c r="A4" s="8" t="s">
-        <v>1452</v>
+        <v>1433</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>1451</v>
+        <v>1432</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>1450</v>
+        <v>1431</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>1449</v>
+        <v>1430</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>1448</v>
+        <v>1429</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>186</v>
@@ -6962,19 +6971,19 @@
     </row>
     <row r="5" spans="1:14" ht="37.5">
       <c r="A5" s="8" t="s">
-        <v>1447</v>
+        <v>1428</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>1446</v>
+        <v>1427</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>1445</v>
+        <v>1426</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>1444</v>
+        <v>1425</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>1443</v>
+        <v>1424</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>186</v>
@@ -6994,19 +7003,19 @@
     </row>
     <row r="6" spans="1:14" ht="37.5">
       <c r="A6" s="8" t="s">
-        <v>1442</v>
+        <v>1423</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>1441</v>
+        <v>1422</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>1440</v>
+        <v>1421</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>1439</v>
+        <v>1420</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>1438</v>
+        <v>1419</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>193</v>
@@ -7026,19 +7035,19 @@
     </row>
     <row r="7" spans="1:14" ht="25">
       <c r="A7" s="8" t="s">
-        <v>1437</v>
+        <v>1418</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>1436</v>
+        <v>1417</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>189</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>1435</v>
+        <v>1416</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>1434</v>
+        <v>1415</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>200</v>
@@ -7058,19 +7067,19 @@
     </row>
     <row r="8" spans="1:14" ht="25">
       <c r="A8" s="8" t="s">
-        <v>1433</v>
+        <v>1414</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>1432</v>
+        <v>1413</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>1431</v>
+        <v>1412</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>1430</v>
+        <v>1411</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>1429</v>
+        <v>1410</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>186</v>
@@ -7090,19 +7099,19 @@
     </row>
     <row r="9" spans="1:14" ht="25">
       <c r="A9" s="8" t="s">
-        <v>1428</v>
+        <v>1409</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>1427</v>
+        <v>1408</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>1426</v>
+        <v>1407</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>1425</v>
+        <v>1406</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>1424</v>
+        <v>1405</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>186</v>
@@ -7122,19 +7131,19 @@
     </row>
     <row r="10" spans="1:14" ht="25">
       <c r="A10" s="8" t="s">
-        <v>1423</v>
+        <v>1404</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>1422</v>
+        <v>1403</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>1358</v>
+        <v>1339</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>1421</v>
+        <v>1402</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>1420</v>
+        <v>1401</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>200</v>
@@ -7154,19 +7163,19 @@
     </row>
     <row r="11" spans="1:14" ht="37.5">
       <c r="A11" s="8" t="s">
-        <v>1419</v>
+        <v>1400</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>1418</v>
+        <v>1399</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>1417</v>
+        <v>1398</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>1416</v>
+        <v>1397</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>1415</v>
+        <v>1396</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>193</v>
@@ -7186,19 +7195,19 @@
     </row>
     <row r="12" spans="1:14" ht="62.5">
       <c r="A12" s="8" t="s">
-        <v>1414</v>
+        <v>1395</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>1413</v>
+        <v>1394</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>1412</v>
+        <v>1393</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>1411</v>
+        <v>1392</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>1410</v>
+        <v>1391</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>200</v>
@@ -7218,19 +7227,19 @@
     </row>
     <row r="13" spans="1:14" ht="50">
       <c r="A13" s="8" t="s">
-        <v>1409</v>
+        <v>1390</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>1408</v>
+        <v>1389</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>1407</v>
+        <v>1388</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>1406</v>
+        <v>1387</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>1405</v>
+        <v>1386</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>200</v>
@@ -7250,19 +7259,19 @@
     </row>
     <row r="14" spans="1:14" ht="50">
       <c r="A14" s="8" t="s">
-        <v>1404</v>
+        <v>1385</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>1403</v>
+        <v>1384</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>1402</v>
+        <v>1383</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>1401</v>
+        <v>1382</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>1400</v>
+        <v>1381</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>200</v>
@@ -7282,19 +7291,19 @@
     </row>
     <row r="15" spans="1:14" ht="37.5">
       <c r="A15" s="8" t="s">
-        <v>1399</v>
+        <v>1380</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>1398</v>
+        <v>1379</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>1397</v>
+        <v>1378</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>1396</v>
+        <v>1377</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>1395</v>
+        <v>1376</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>200</v>
@@ -7314,19 +7323,19 @@
     </row>
     <row r="16" spans="1:14" ht="62.5">
       <c r="A16" s="8" t="s">
-        <v>1394</v>
+        <v>1375</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>1393</v>
+        <v>1374</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>1392</v>
+        <v>1373</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>1391</v>
+        <v>1372</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>1390</v>
+        <v>1371</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>200</v>
@@ -7346,19 +7355,19 @@
     </row>
     <row r="17" spans="1:14" ht="50">
       <c r="A17" s="8" t="s">
-        <v>1389</v>
+        <v>1370</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>1388</v>
+        <v>1369</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>1387</v>
+        <v>1368</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>1386</v>
+        <v>1367</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>1385</v>
+        <v>1366</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>200</v>
@@ -7378,19 +7387,19 @@
     </row>
     <row r="18" spans="1:14" ht="37.5">
       <c r="A18" s="8" t="s">
-        <v>1384</v>
+        <v>1365</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>1383</v>
+        <v>1364</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>1382</v>
+        <v>1363</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>1381</v>
+        <v>1362</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>1380</v>
+        <v>1361</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>200</v>
@@ -7410,19 +7419,19 @@
     </row>
     <row r="19" spans="1:14" ht="37.5">
       <c r="A19" s="8" t="s">
-        <v>1379</v>
+        <v>1360</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>1378</v>
+        <v>1359</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>1377</v>
+        <v>1358</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>1376</v>
+        <v>1357</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>1375</v>
+        <v>1356</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>186</v>
@@ -7442,19 +7451,19 @@
     </row>
     <row r="20" spans="1:14" ht="50">
       <c r="A20" s="8" t="s">
-        <v>1374</v>
+        <v>1355</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>1373</v>
+        <v>1354</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>1372</v>
+        <v>1353</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>1371</v>
+        <v>1352</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>1370</v>
+        <v>1351</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>186</v>
@@ -7474,19 +7483,19 @@
     </row>
     <row r="21" spans="1:14" ht="50">
       <c r="A21" s="8" t="s">
-        <v>1369</v>
+        <v>1350</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>1368</v>
+        <v>1349</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>1367</v>
+        <v>1348</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>1366</v>
+        <v>1347</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>1365</v>
+        <v>1346</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>200</v>
@@ -7506,19 +7515,19 @@
     </row>
     <row r="22" spans="1:14" ht="75">
       <c r="A22" s="8" t="s">
-        <v>1364</v>
+        <v>1345</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>1363</v>
+        <v>1344</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>1362</v>
+        <v>1343</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>1361</v>
+        <v>1342</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>1360</v>
+        <v>1341</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>200</v>
@@ -7538,19 +7547,19 @@
     </row>
     <row r="23" spans="1:14" ht="37.5">
       <c r="A23" s="8" t="s">
-        <v>1359</v>
+        <v>1340</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>1358</v>
+        <v>1339</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>1357</v>
+        <v>1338</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>1356</v>
+        <v>1337</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>1355</v>
+        <v>1336</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>186</v>
@@ -7570,19 +7579,19 @@
     </row>
     <row r="24" spans="1:14" ht="50">
       <c r="A24" s="8" t="s">
-        <v>1354</v>
+        <v>1335</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>1353</v>
+        <v>1334</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>1352</v>
+        <v>1333</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>1351</v>
+        <v>1332</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>1350</v>
+        <v>1331</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>200</v>
@@ -7602,19 +7611,19 @@
     </row>
     <row r="25" spans="1:14" ht="62.5">
       <c r="A25" s="8" t="s">
-        <v>1349</v>
+        <v>1330</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>1348</v>
+        <v>1329</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>1347</v>
+        <v>1328</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>1346</v>
+        <v>1327</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>1345</v>
+        <v>1326</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>193</v>
@@ -7634,19 +7643,19 @@
     </row>
     <row r="26" spans="1:14" ht="37.5">
       <c r="A26" s="8" t="s">
-        <v>1344</v>
+        <v>1325</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>1343</v>
+        <v>1324</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>1342</v>
+        <v>1323</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>1341</v>
+        <v>1322</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>1340</v>
+        <v>1321</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>186</v>
@@ -7666,19 +7675,19 @@
     </row>
     <row r="27" spans="1:14" ht="25">
       <c r="A27" s="8" t="s">
-        <v>1339</v>
+        <v>1320</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>1338</v>
+        <v>1319</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>1337</v>
+        <v>1318</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>1336</v>
+        <v>1317</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>1335</v>
+        <v>1316</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>186</v>
@@ -7698,19 +7707,19 @@
     </row>
     <row r="28" spans="1:14" ht="25">
       <c r="A28" s="8" t="s">
-        <v>1334</v>
+        <v>1315</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>1333</v>
+        <v>1314</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>1332</v>
+        <v>1313</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>1331</v>
+        <v>1312</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>1330</v>
+        <v>1311</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>200</v>
@@ -7730,19 +7739,19 @@
     </row>
     <row r="29" spans="1:14" ht="25">
       <c r="A29" s="8" t="s">
-        <v>1329</v>
+        <v>1310</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>1328</v>
+        <v>1309</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>1327</v>
+        <v>1308</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>1326</v>
+        <v>1307</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>1325</v>
+        <v>1306</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>193</v>
@@ -7762,19 +7771,19 @@
     </row>
     <row r="30" spans="1:14" ht="25">
       <c r="A30" s="8" t="s">
-        <v>1324</v>
+        <v>1305</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>1323</v>
+        <v>1304</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>1322</v>
+        <v>1303</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>1321</v>
+        <v>1302</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>1320</v>
+        <v>1301</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>186</v>
@@ -7794,19 +7803,19 @@
     </row>
     <row r="31" spans="1:14" ht="25">
       <c r="A31" s="8" t="s">
-        <v>1319</v>
+        <v>1300</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>1318</v>
+        <v>1299</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>1317</v>
+        <v>1298</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>183</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>1312</v>
+        <v>1293</v>
       </c>
       <c r="F31" s="7" t="s">
         <v>200</v>
@@ -7826,19 +7835,19 @@
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="8" t="s">
-        <v>1316</v>
+        <v>1297</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>1315</v>
+        <v>1296</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>1314</v>
+        <v>1295</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>1313</v>
+        <v>1294</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>1312</v>
+        <v>1293</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>193</v>
@@ -7858,19 +7867,19 @@
     </row>
     <row r="33" spans="1:14" ht="37.5">
       <c r="A33" s="8" t="s">
-        <v>1311</v>
+        <v>1292</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>1310</v>
+        <v>1291</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>1309</v>
+        <v>1290</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>1308</v>
+        <v>1289</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>1307</v>
+        <v>1288</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>186</v>
@@ -7890,19 +7899,19 @@
     </row>
     <row r="34" spans="1:14" ht="25">
       <c r="A34" s="8" t="s">
-        <v>1306</v>
+        <v>1287</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>1305</v>
+        <v>1286</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>1304</v>
+        <v>1285</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>1303</v>
+        <v>1284</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>1302</v>
+        <v>1283</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>186</v>
@@ -7922,19 +7931,19 @@
     </row>
     <row r="35" spans="1:14" ht="25">
       <c r="A35" s="8" t="s">
-        <v>1301</v>
+        <v>1282</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>1300</v>
+        <v>1281</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>1299</v>
+        <v>1280</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>1298</v>
+        <v>1279</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>1297</v>
+        <v>1278</v>
       </c>
       <c r="F35" s="7" t="s">
         <v>200</v>
@@ -7954,19 +7963,19 @@
     </row>
     <row r="36" spans="1:14" ht="25">
       <c r="A36" s="8" t="s">
-        <v>1296</v>
+        <v>1277</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>1295</v>
+        <v>1276</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>1294</v>
+        <v>1275</v>
       </c>
       <c r="D36" s="9" t="s">
         <v>221</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>1293</v>
+        <v>1274</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>193</v>
@@ -7986,19 +7995,19 @@
     </row>
     <row r="37" spans="1:14" ht="25">
       <c r="A37" s="8" t="s">
-        <v>1292</v>
+        <v>1273</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>1291</v>
+        <v>1272</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>1290</v>
+        <v>1271</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>1289</v>
+        <v>1270</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>1288</v>
+        <v>1269</v>
       </c>
       <c r="F37" s="7" t="s">
         <v>200</v>
@@ -8018,19 +8027,19 @@
     </row>
     <row r="38" spans="1:14" ht="75">
       <c r="A38" s="8" t="s">
-        <v>1287</v>
+        <v>1268</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>1286</v>
+        <v>1267</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>1285</v>
+        <v>1266</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>1284</v>
+        <v>1265</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>1283</v>
+        <v>1264</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>193</v>
@@ -8048,21 +8057,21 @@
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
     </row>
-    <row r="39" spans="1:14" ht="50">
+    <row r="39" spans="1:14" ht="37.5">
       <c r="A39" s="8" t="s">
-        <v>1282</v>
+        <v>1263</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>1281</v>
+        <v>1262</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>1280</v>
+        <v>1261</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>1279</v>
+        <v>1260</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>1278</v>
+        <v>1259</v>
       </c>
       <c r="F39" s="7" t="s">
         <v>186</v>
@@ -8082,19 +8091,19 @@
     </row>
     <row r="40" spans="1:14" ht="37.5">
       <c r="A40" s="8" t="s">
-        <v>1277</v>
+        <v>1258</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>1276</v>
+        <v>1257</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>1275</v>
+        <v>1256</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>1274</v>
+        <v>1255</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>1273</v>
+        <v>1254</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>178</v>
@@ -8114,19 +8123,19 @@
     </row>
     <row r="41" spans="1:14" ht="50">
       <c r="A41" s="8" t="s">
-        <v>1272</v>
+        <v>1253</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>1271</v>
+        <v>1252</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>1270</v>
+        <v>1251</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>1269</v>
+        <v>1250</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>1268</v>
+        <v>1249</v>
       </c>
       <c r="F41" s="7" t="s">
         <v>200</v>
@@ -8146,19 +8155,19 @@
     </row>
     <row r="42" spans="1:14" ht="37.5">
       <c r="A42" s="8" t="s">
-        <v>1267</v>
+        <v>1248</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>1266</v>
+        <v>1247</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>1265</v>
+        <v>1246</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>1264</v>
+        <v>1245</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>1263</v>
+        <v>1244</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>193</v>
@@ -8178,19 +8187,19 @@
     </row>
     <row r="43" spans="1:14" ht="25">
       <c r="A43" s="8" t="s">
-        <v>1262</v>
+        <v>1243</v>
       </c>
       <c r="B43" s="9" t="s">
         <v>215</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>1261</v>
+        <v>1242</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>1260</v>
+        <v>1241</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>1259</v>
+        <v>1240</v>
       </c>
       <c r="F43" s="7" t="s">
         <v>186</v>
@@ -8210,19 +8219,19 @@
     </row>
     <row r="44" spans="1:14" ht="75">
       <c r="A44" s="8" t="s">
-        <v>1258</v>
+        <v>1239</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>1257</v>
+        <v>1238</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>1256</v>
+        <v>1237</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>1255</v>
+        <v>1236</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>1254</v>
+        <v>1235</v>
       </c>
       <c r="F44" s="7" t="s">
         <v>178</v>
@@ -8242,19 +8251,19 @@
     </row>
     <row r="45" spans="1:14" ht="50">
       <c r="A45" s="8" t="s">
-        <v>1253</v>
+        <v>1234</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>1252</v>
+        <v>1233</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>1251</v>
+        <v>1232</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>1250</v>
+        <v>1231</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>1249</v>
+        <v>1230</v>
       </c>
       <c r="F45" s="7" t="s">
         <v>200</v>
@@ -8274,19 +8283,19 @@
     </row>
     <row r="46" spans="1:14" ht="50">
       <c r="A46" s="8" t="s">
-        <v>1248</v>
+        <v>1229</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>1247</v>
+        <v>1228</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>1246</v>
+        <v>1227</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>1245</v>
+        <v>1226</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>1244</v>
+        <v>1225</v>
       </c>
       <c r="F46" s="7" t="s">
         <v>193</v>
@@ -8306,19 +8315,19 @@
     </row>
     <row r="47" spans="1:14" ht="62.5">
       <c r="A47" s="8" t="s">
-        <v>1243</v>
+        <v>1224</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>1242</v>
+        <v>1223</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>1241</v>
+        <v>1222</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>1240</v>
+        <v>1221</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>1239</v>
+        <v>1220</v>
       </c>
       <c r="F47" s="7" t="s">
         <v>186</v>
@@ -8338,19 +8347,19 @@
     </row>
     <row r="48" spans="1:14" ht="50">
       <c r="A48" s="8" t="s">
-        <v>1238</v>
+        <v>1219</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>1237</v>
+        <v>1218</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>1236</v>
+        <v>1217</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>1235</v>
+        <v>1216</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>1234</v>
+        <v>1215</v>
       </c>
       <c r="F48" s="7" t="s">
         <v>193</v>
@@ -8370,19 +8379,19 @@
     </row>
     <row r="49" spans="1:14" ht="50">
       <c r="A49" s="8" t="s">
-        <v>1233</v>
+        <v>1214</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>1232</v>
+        <v>1213</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>1231</v>
+        <v>1212</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>1230</v>
+        <v>1211</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>1229</v>
+        <v>1210</v>
       </c>
       <c r="F49" s="7" t="s">
         <v>200</v>
@@ -8402,19 +8411,19 @@
     </row>
     <row r="50" spans="1:14" ht="62.5">
       <c r="A50" s="8" t="s">
-        <v>1228</v>
+        <v>1209</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>1227</v>
+        <v>1208</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>1226</v>
+        <v>1207</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>1225</v>
+        <v>1206</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>1224</v>
+        <v>1205</v>
       </c>
       <c r="F50" s="7" t="s">
         <v>178</v>
@@ -8434,19 +8443,19 @@
     </row>
     <row r="51" spans="1:14" ht="37.5">
       <c r="A51" s="8" t="s">
-        <v>1223</v>
+        <v>1204</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>1222</v>
+        <v>1203</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>1221</v>
+        <v>1202</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>1220</v>
+        <v>1201</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>1219</v>
+        <v>1200</v>
       </c>
       <c r="F51" s="7" t="s">
         <v>193</v>
@@ -8466,19 +8475,19 @@
     </row>
     <row r="52" spans="1:14" ht="25">
       <c r="A52" s="8" t="s">
-        <v>1218</v>
+        <v>1199</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>1217</v>
+        <v>1198</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>1216</v>
+        <v>1197</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>1215</v>
+        <v>1196</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>1214</v>
+        <v>1195</v>
       </c>
       <c r="F52" s="7" t="s">
         <v>200</v>
@@ -8498,19 +8507,19 @@
     </row>
     <row r="53" spans="1:14" ht="25">
       <c r="A53" s="8" t="s">
-        <v>1213</v>
+        <v>1194</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>1212</v>
+        <v>1193</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>1211</v>
+        <v>1192</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>1210</v>
+        <v>1191</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>1209</v>
+        <v>1190</v>
       </c>
       <c r="F53" s="7" t="s">
         <v>193</v>
@@ -8530,19 +8539,19 @@
     </row>
     <row r="54" spans="1:14" ht="25">
       <c r="A54" s="8" t="s">
-        <v>1208</v>
+        <v>1189</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>1207</v>
+        <v>1188</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>1206</v>
+        <v>1187</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>1205</v>
+        <v>1186</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>1190</v>
+        <v>1171</v>
       </c>
       <c r="F54" s="7" t="s">
         <v>200</v>
@@ -8562,19 +8571,19 @@
     </row>
     <row r="55" spans="1:14" ht="25">
       <c r="A55" s="8" t="s">
-        <v>1204</v>
+        <v>1185</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>1203</v>
+        <v>1184</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>1202</v>
+        <v>1183</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>1201</v>
+        <v>1182</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>1200</v>
+        <v>1181</v>
       </c>
       <c r="F55" s="7" t="s">
         <v>186</v>
@@ -8594,19 +8603,19 @@
     </row>
     <row r="56" spans="1:14" ht="25">
       <c r="A56" s="8" t="s">
-        <v>1199</v>
+        <v>1180</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>1093</v>
+        <v>1074</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>1091</v>
+        <v>1072</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>1092</v>
+        <v>1073</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>1096</v>
+        <v>1077</v>
       </c>
       <c r="F56" s="7" t="s">
         <v>178</v>
@@ -8626,19 +8635,19 @@
     </row>
     <row r="57" spans="1:14" ht="25">
       <c r="A57" s="8" t="s">
-        <v>1198</v>
+        <v>1179</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>1197</v>
+        <v>1178</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>1196</v>
+        <v>1177</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>1195</v>
+        <v>1176</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>1194</v>
+        <v>1175</v>
       </c>
       <c r="F57" s="7" t="s">
         <v>193</v>
@@ -8658,19 +8667,19 @@
     </row>
     <row r="58" spans="1:14" ht="37.5">
       <c r="A58" s="8" t="s">
-        <v>1193</v>
+        <v>1174</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>1192</v>
+        <v>1173</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>1191</v>
+        <v>1172</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>1190</v>
+        <v>1171</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>1189</v>
+        <v>1170</v>
       </c>
       <c r="F58" s="7" t="s">
         <v>200</v>
@@ -8690,19 +8699,19 @@
     </row>
     <row r="59" spans="1:14">
       <c r="A59" s="8" t="s">
-        <v>1188</v>
+        <v>1169</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>1187</v>
+        <v>1168</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>1186</v>
+        <v>1167</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>1185</v>
+        <v>1166</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>826</v>
+        <v>810</v>
       </c>
       <c r="F59" s="7" t="s">
         <v>186</v>
@@ -8722,19 +8731,19 @@
     </row>
     <row r="60" spans="1:14" ht="37.5">
       <c r="A60" s="8" t="s">
-        <v>1184</v>
+        <v>1165</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>1183</v>
+        <v>1164</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>1182</v>
+        <v>1163</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>1181</v>
+        <v>1162</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>1180</v>
+        <v>1161</v>
       </c>
       <c r="F60" s="7" t="s">
         <v>200</v>
@@ -8754,19 +8763,19 @@
     </row>
     <row r="61" spans="1:14" ht="37.5">
       <c r="A61" s="8" t="s">
-        <v>1179</v>
+        <v>1160</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>1178</v>
+        <v>1159</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>1177</v>
+        <v>1158</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>1176</v>
+        <v>1157</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>1175</v>
+        <v>1156</v>
       </c>
       <c r="F61" s="7" t="s">
         <v>186</v>
@@ -8786,19 +8795,19 @@
     </row>
     <row r="62" spans="1:14" ht="50">
       <c r="A62" s="8" t="s">
-        <v>1174</v>
+        <v>1155</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>1173</v>
+        <v>1154</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>1172</v>
+        <v>1153</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>1171</v>
+        <v>1152</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>1170</v>
+        <v>1151</v>
       </c>
       <c r="F62" s="7" t="s">
         <v>200</v>
@@ -8818,19 +8827,19 @@
     </row>
     <row r="63" spans="1:14" ht="62.5">
       <c r="A63" s="8" t="s">
-        <v>1169</v>
+        <v>1150</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>1168</v>
+        <v>1149</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>1167</v>
+        <v>1148</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>1166</v>
+        <v>1147</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>1165</v>
+        <v>1146</v>
       </c>
       <c r="F63" s="7" t="s">
         <v>193</v>
@@ -8850,19 +8859,19 @@
     </row>
     <row r="64" spans="1:14" ht="37.5">
       <c r="A64" s="8" t="s">
-        <v>1164</v>
+        <v>1145</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>1163</v>
+        <v>1144</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>1162</v>
+        <v>1143</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>1161</v>
+        <v>1142</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>1160</v>
+        <v>1141</v>
       </c>
       <c r="F64" s="7" t="s">
         <v>200</v>
@@ -8880,21 +8889,21 @@
       <c r="M64" s="2"/>
       <c r="N64" s="2"/>
     </row>
-    <row r="65" spans="1:14" ht="50">
+    <row r="65" spans="1:14" ht="37.5">
       <c r="A65" s="8" t="s">
-        <v>1159</v>
+        <v>1140</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>1158</v>
+        <v>1139</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>1157</v>
+        <v>1138</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>1156</v>
+        <v>1137</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>1155</v>
+        <v>1136</v>
       </c>
       <c r="F65" s="7" t="s">
         <v>200</v>
@@ -8914,19 +8923,19 @@
     </row>
     <row r="66" spans="1:14" ht="37.5">
       <c r="A66" s="8" t="s">
-        <v>1154</v>
+        <v>1135</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>1153</v>
+        <v>1134</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>1152</v>
+        <v>1133</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>1151</v>
+        <v>1132</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>1141</v>
+        <v>1122</v>
       </c>
       <c r="F66" s="7" t="s">
         <v>193</v>
@@ -8946,19 +8955,19 @@
     </row>
     <row r="67" spans="1:14" ht="50">
       <c r="A67" s="8" t="s">
-        <v>1150</v>
+        <v>1131</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>1149</v>
+        <v>1130</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>1148</v>
+        <v>1129</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>1147</v>
+        <v>1128</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>1146</v>
+        <v>1127</v>
       </c>
       <c r="F67" s="7" t="s">
         <v>200</v>
@@ -8978,19 +8987,19 @@
     </row>
     <row r="68" spans="1:14" ht="25">
       <c r="A68" s="8" t="s">
-        <v>1145</v>
+        <v>1126</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>1144</v>
+        <v>1125</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>1143</v>
+        <v>1124</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>1142</v>
+        <v>1123</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>1141</v>
+        <v>1122</v>
       </c>
       <c r="F68" s="7" t="s">
         <v>193</v>
@@ -9010,19 +9019,19 @@
     </row>
     <row r="69" spans="1:14" ht="25">
       <c r="A69" s="8" t="s">
-        <v>1140</v>
+        <v>1121</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>1139</v>
+        <v>1120</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>1138</v>
+        <v>1119</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>1137</v>
+        <v>1118</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>1136</v>
+        <v>1117</v>
       </c>
       <c r="F69" s="7" t="s">
         <v>200</v>
@@ -9042,19 +9051,19 @@
     </row>
     <row r="70" spans="1:14" ht="25">
       <c r="A70" s="8" t="s">
-        <v>1135</v>
+        <v>1116</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>859</v>
+        <v>843</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>1134</v>
+        <v>1115</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>1133</v>
+        <v>1114</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>1132</v>
+        <v>1113</v>
       </c>
       <c r="F70" s="7" t="s">
         <v>178</v>
@@ -9074,19 +9083,19 @@
     </row>
     <row r="71" spans="1:14" ht="25">
       <c r="A71" s="8" t="s">
-        <v>1131</v>
+        <v>1112</v>
       </c>
       <c r="B71" s="9">
         <v>10011</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>1130</v>
+        <v>1111</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>1129</v>
+        <v>1110</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>1128</v>
+        <v>1109</v>
       </c>
       <c r="F71" s="7" t="s">
         <v>186</v>
@@ -9106,19 +9115,19 @@
     </row>
     <row r="72" spans="1:14" ht="25">
       <c r="A72" s="8" t="s">
-        <v>1127</v>
+        <v>1108</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>1126</v>
+        <v>1107</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>1125</v>
+        <v>1106</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>1124</v>
+        <v>1105</v>
       </c>
       <c r="E72" s="9" t="s">
-        <v>1123</v>
+        <v>1104</v>
       </c>
       <c r="F72" s="7" t="s">
         <v>200</v>
@@ -9138,7 +9147,7 @@
     </row>
     <row r="73" spans="1:14" ht="25">
       <c r="A73" s="8" t="s">
-        <v>1122</v>
+        <v>1103</v>
       </c>
       <c r="B73" s="9">
         <v>1011</v>
@@ -9170,7 +9179,7 @@
     </row>
     <row r="74" spans="1:14" ht="25">
       <c r="A74" s="8" t="s">
-        <v>1121</v>
+        <v>1102</v>
       </c>
       <c r="B74" s="9" t="s">
         <v>441</v>
@@ -9179,10 +9188,10 @@
         <v>523</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>826</v>
+        <v>810</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>1120</v>
+        <v>1101</v>
       </c>
       <c r="F74" s="7" t="s">
         <v>193</v>
@@ -9202,19 +9211,19 @@
     </row>
     <row r="75" spans="1:14" ht="50">
       <c r="A75" s="8" t="s">
-        <v>1119</v>
+        <v>1100</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>1118</v>
+        <v>1099</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>1117</v>
+        <v>1098</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>1116</v>
+        <v>1097</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>1115</v>
+        <v>1096</v>
       </c>
       <c r="F75" s="7" t="s">
         <v>200</v>
@@ -9234,7 +9243,7 @@
     </row>
     <row r="76" spans="1:14" ht="25">
       <c r="A76" s="8" t="s">
-        <v>1114</v>
+        <v>1095</v>
       </c>
       <c r="B76" s="9">
         <v>11000</v>
@@ -9266,7 +9275,7 @@
     </row>
     <row r="77" spans="1:14">
       <c r="A77" s="8" t="s">
-        <v>1113</v>
+        <v>1094</v>
       </c>
       <c r="B77" s="9" t="s">
         <v>441</v>
@@ -9298,10 +9307,10 @@
     </row>
     <row r="78" spans="1:14">
       <c r="A78" s="8" t="s">
-        <v>1112</v>
+        <v>1093</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>1111</v>
+        <v>1092</v>
       </c>
       <c r="C78" s="9" t="s">
         <v>441</v>
@@ -9330,19 +9339,19 @@
     </row>
     <row r="79" spans="1:14">
       <c r="A79" s="8" t="s">
-        <v>1110</v>
+        <v>1091</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>1109</v>
+        <v>1090</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>1108</v>
+        <v>1089</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>1107</v>
+        <v>1088</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>1106</v>
+        <v>1087</v>
       </c>
       <c r="F79" s="7" t="s">
         <v>186</v>
@@ -9362,19 +9371,19 @@
     </row>
     <row r="80" spans="1:14">
       <c r="A80" s="8" t="s">
-        <v>1105</v>
+        <v>1086</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>1092</v>
+        <v>1073</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>1096</v>
+        <v>1077</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>1093</v>
+        <v>1074</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>1091</v>
+        <v>1072</v>
       </c>
       <c r="F80" s="7" t="s">
         <v>178</v>
@@ -9394,19 +9403,19 @@
     </row>
     <row r="81" spans="1:14">
       <c r="A81" s="8" t="s">
-        <v>1104</v>
+        <v>1085</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>1103</v>
+        <v>1084</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>1102</v>
+        <v>1083</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>1101</v>
+        <v>1082</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>1100</v>
+        <v>1081</v>
       </c>
       <c r="F81" s="7" t="s">
         <v>193</v>
@@ -9426,19 +9435,19 @@
     </row>
     <row r="82" spans="1:14">
       <c r="A82" s="8" t="s">
-        <v>1099</v>
+        <v>1080</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>1098</v>
+        <v>1079</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>1097</v>
+        <v>1078</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>1091</v>
+        <v>1072</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>1096</v>
+        <v>1077</v>
       </c>
       <c r="F82" s="7" t="s">
         <v>200</v>
@@ -9458,19 +9467,19 @@
     </row>
     <row r="83" spans="1:14">
       <c r="A83" s="8" t="s">
-        <v>1095</v>
+        <v>1076</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>1094</v>
+        <v>1075</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>1093</v>
+        <v>1074</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>1092</v>
+        <v>1073</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>1091</v>
+        <v>1072</v>
       </c>
       <c r="F83" s="7" t="s">
         <v>186</v>
@@ -9490,7 +9499,7 @@
     </row>
     <row r="84" spans="1:14">
       <c r="A84" s="8" t="s">
-        <v>1090</v>
+        <v>1071</v>
       </c>
       <c r="B84" s="9" t="s">
         <v>460</v>
@@ -9522,19 +9531,19 @@
     </row>
     <row r="85" spans="1:14">
       <c r="A85" s="8" t="s">
-        <v>1089</v>
+        <v>1070</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>1088</v>
+        <v>1069</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>1087</v>
+        <v>1068</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>1086</v>
+        <v>1067</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>1085</v>
+        <v>1066</v>
       </c>
       <c r="F85" s="7" t="s">
         <v>193</v>
@@ -9554,19 +9563,19 @@
     </row>
     <row r="86" spans="1:14">
       <c r="A86" s="8" t="s">
-        <v>1084</v>
+        <v>1065</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>1083</v>
+        <v>1064</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>1082</v>
+        <v>1063</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>1081</v>
+        <v>1062</v>
       </c>
       <c r="E86" s="9" t="s">
-        <v>1080</v>
+        <v>1061</v>
       </c>
       <c r="F86" s="7" t="s">
         <v>200</v>
@@ -9586,19 +9595,19 @@
     </row>
     <row r="87" spans="1:14" ht="25">
       <c r="A87" s="8" t="s">
-        <v>1079</v>
+        <v>1060</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>1078</v>
+        <v>1059</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>1077</v>
+        <v>1058</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>1037</v>
+        <v>1018</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>1076</v>
+        <v>1057</v>
       </c>
       <c r="F87" s="7" t="s">
         <v>186</v>
@@ -9618,19 +9627,19 @@
     </row>
     <row r="88" spans="1:14" ht="25">
       <c r="A88" s="8" t="s">
-        <v>1075</v>
+        <v>1056</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>1074</v>
+        <v>1055</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>1073</v>
+        <v>1054</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>1072</v>
+        <v>1053</v>
       </c>
       <c r="E88" s="9" t="s">
-        <v>1071</v>
+        <v>1052</v>
       </c>
       <c r="F88" s="7" t="s">
         <v>178</v>
@@ -9650,19 +9659,19 @@
     </row>
     <row r="89" spans="1:14" ht="25">
       <c r="A89" s="8" t="s">
-        <v>1070</v>
+        <v>1051</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>1069</v>
+        <v>1050</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>1068</v>
+        <v>1049</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>1067</v>
+        <v>1048</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>1066</v>
+        <v>1047</v>
       </c>
       <c r="F89" s="7" t="s">
         <v>193</v>
@@ -9682,19 +9691,19 @@
     </row>
     <row r="90" spans="1:14" ht="25">
       <c r="A90" s="8" t="s">
-        <v>1065</v>
+        <v>1046</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>1064</v>
+        <v>1045</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>1063</v>
+        <v>1044</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>1062</v>
+        <v>1043</v>
       </c>
       <c r="E90" s="9" t="s">
-        <v>1061</v>
+        <v>1042</v>
       </c>
       <c r="F90" s="7" t="s">
         <v>200</v>
@@ -9714,19 +9723,19 @@
     </row>
     <row r="91" spans="1:14" ht="25">
       <c r="A91" s="8" t="s">
-        <v>1060</v>
+        <v>1041</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>1059</v>
+        <v>1040</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>1058</v>
+        <v>1039</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>1057</v>
+        <v>1038</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>1056</v>
+        <v>1037</v>
       </c>
       <c r="F91" s="7" t="s">
         <v>186</v>
@@ -9746,25 +9755,25 @@
     </row>
     <row r="92" spans="1:14" ht="25">
       <c r="A92" s="8" t="s">
-        <v>1055</v>
+        <v>1036</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>1054</v>
+        <v>1035</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>1053</v>
+        <v>1034</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>1052</v>
+        <v>1033</v>
       </c>
       <c r="E92" s="9" t="s">
-        <v>1051</v>
+        <v>1032</v>
       </c>
       <c r="F92" s="7" t="s">
         <v>186</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="H92" s="4" t="s">
         <v>180</v>
@@ -9778,25 +9787,25 @@
     </row>
     <row r="93" spans="1:14" ht="25">
       <c r="A93" s="8" t="s">
-        <v>1050</v>
+        <v>1031</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>1049</v>
+        <v>1030</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>1048</v>
+        <v>1029</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>1047</v>
+        <v>1028</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>1046</v>
+        <v>1027</v>
       </c>
       <c r="F93" s="7" t="s">
         <v>178</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>693</v>
+        <v>685</v>
       </c>
       <c r="H93" s="4" t="s">
         <v>180</v>
@@ -9810,25 +9819,25 @@
     </row>
     <row r="94" spans="1:14" ht="37.5">
       <c r="A94" s="8" t="s">
-        <v>1045</v>
+        <v>1026</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>1044</v>
+        <v>1025</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>1043</v>
+        <v>1024</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>1042</v>
+        <v>1023</v>
       </c>
       <c r="E94" s="9" t="s">
-        <v>1041</v>
+        <v>1022</v>
       </c>
       <c r="F94" s="7" t="s">
         <v>193</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>700</v>
+        <v>688</v>
       </c>
       <c r="H94" s="4" t="s">
         <v>180</v>
@@ -9842,25 +9851,25 @@
     </row>
     <row r="95" spans="1:14" ht="25">
       <c r="A95" s="8" t="s">
-        <v>1040</v>
+        <v>1021</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>1039</v>
+        <v>1020</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>1038</v>
+        <v>1019</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>1037</v>
+        <v>1018</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>1036</v>
+        <v>1017</v>
       </c>
       <c r="F95" s="7" t="s">
         <v>200</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>706</v>
+        <v>690</v>
       </c>
       <c r="H95" s="4" t="s">
         <v>180</v>
@@ -9874,25 +9883,25 @@
     </row>
     <row r="96" spans="1:14" ht="37.5">
       <c r="A96" s="8" t="s">
-        <v>1035</v>
+        <v>1016</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>1034</v>
+        <v>1015</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>1033</v>
+        <v>1014</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>1032</v>
+        <v>1013</v>
       </c>
       <c r="E96" s="9" t="s">
-        <v>1031</v>
+        <v>1012</v>
       </c>
       <c r="F96" s="7" t="s">
         <v>193</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>712</v>
+        <v>696</v>
       </c>
       <c r="H96" s="4" t="s">
         <v>180</v>
@@ -9906,19 +9915,25 @@
     </row>
     <row r="97" spans="1:14" ht="62.5">
       <c r="A97" s="8" t="s">
-        <v>1030</v>
+        <v>1011</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>1029</v>
-      </c>
-      <c r="C97" s="9"/>
+        <v>1663</v>
+      </c>
+      <c r="C97" s="9" t="s">
+        <v>1664</v>
+      </c>
       <c r="D97" s="9" t="s">
-        <v>1028</v>
-      </c>
-      <c r="E97" s="9"/>
-      <c r="F97" s="7"/>
+        <v>1665</v>
+      </c>
+      <c r="E97" s="9" t="s">
+        <v>1666</v>
+      </c>
+      <c r="F97" s="7" t="s">
+        <v>200</v>
+      </c>
       <c r="G97" s="4" t="s">
-        <v>718</v>
+        <v>702</v>
       </c>
       <c r="H97" s="4" t="s">
         <v>180</v>
@@ -9932,23 +9947,25 @@
     </row>
     <row r="98" spans="1:14" ht="62.5">
       <c r="A98" s="8" t="s">
-        <v>1027</v>
+        <v>1010</v>
       </c>
       <c r="B98" s="9" t="s">
         <v>461</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>1026</v>
-      </c>
-      <c r="D98" s="9"/>
+        <v>1667</v>
+      </c>
+      <c r="D98" s="9" t="s">
+        <v>1668</v>
+      </c>
       <c r="E98" s="9" t="s">
-        <v>1025</v>
+        <v>1009</v>
       </c>
       <c r="F98" s="7" t="s">
         <v>186</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>724</v>
+        <v>708</v>
       </c>
       <c r="H98" s="4" t="s">
         <v>180</v>
@@ -9962,25 +9979,25 @@
     </row>
     <row r="99" spans="1:14" ht="25">
       <c r="A99" s="8" t="s">
-        <v>1024</v>
+        <v>1008</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>1023</v>
+        <v>1007</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>1022</v>
+        <v>1006</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>1020</v>
+        <v>1004</v>
       </c>
       <c r="F99" s="7" t="s">
         <v>200</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>730</v>
+        <v>714</v>
       </c>
       <c r="H99" s="4" t="s">
         <v>180</v>
@@ -9994,25 +10011,25 @@
     </row>
     <row r="100" spans="1:14" ht="62.5">
       <c r="A100" s="8" t="s">
-        <v>1019</v>
+        <v>1003</v>
       </c>
       <c r="B100" s="9" t="s">
-        <v>1018</v>
+        <v>1002</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>1017</v>
+        <v>1001</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>1016</v>
+        <v>1000</v>
       </c>
       <c r="E100" s="9" t="s">
-        <v>1015</v>
+        <v>999</v>
       </c>
       <c r="F100" s="7" t="s">
         <v>200</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>736</v>
+        <v>720</v>
       </c>
       <c r="H100" s="4" t="s">
         <v>180</v>
@@ -10026,25 +10043,25 @@
     </row>
     <row r="101" spans="1:14" ht="87.5">
       <c r="A101" s="8" t="s">
-        <v>1014</v>
+        <v>998</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>1013</v>
+        <v>997</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>1012</v>
+        <v>996</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>1011</v>
+        <v>995</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>1010</v>
+        <v>994</v>
       </c>
       <c r="F101" s="7" t="s">
         <v>193</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>742</v>
+        <v>726</v>
       </c>
       <c r="H101" s="4" t="s">
         <v>180</v>
@@ -10058,25 +10075,25 @@
     </row>
     <row r="102" spans="1:14" ht="25">
       <c r="A102" s="8" t="s">
-        <v>1009</v>
+        <v>993</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>1008</v>
+        <v>992</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>1007</v>
+        <v>991</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>1006</v>
+        <v>990</v>
       </c>
       <c r="E102" s="9" t="s">
-        <v>1005</v>
+        <v>989</v>
       </c>
       <c r="F102" s="7" t="s">
         <v>200</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>748</v>
+        <v>732</v>
       </c>
       <c r="H102" s="4" t="s">
         <v>180</v>
@@ -10090,25 +10107,25 @@
     </row>
     <row r="103" spans="1:14">
       <c r="A103" s="8" t="s">
-        <v>1004</v>
+        <v>988</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>856</v>
+        <v>840</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>1003</v>
+        <v>987</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>1002</v>
+        <v>986</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>1001</v>
+        <v>985</v>
       </c>
       <c r="F103" s="7" t="s">
         <v>186</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>755</v>
+        <v>739</v>
       </c>
       <c r="H103" s="4" t="s">
         <v>180</v>
@@ -10122,7 +10139,7 @@
     </row>
     <row r="104" spans="1:14">
       <c r="A104" s="8" t="s">
-        <v>1000</v>
+        <v>984</v>
       </c>
       <c r="B104" s="9" t="s">
         <v>471</v>
@@ -10131,7 +10148,7 @@
         <v>470</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>998</v>
+        <v>982</v>
       </c>
       <c r="E104" s="9" t="s">
         <v>472</v>
@@ -10140,7 +10157,7 @@
         <v>178</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>761</v>
+        <v>745</v>
       </c>
       <c r="H104" s="4" t="s">
         <v>180</v>
@@ -10154,13 +10171,13 @@
     </row>
     <row r="105" spans="1:14">
       <c r="A105" s="8" t="s">
-        <v>999</v>
+        <v>983</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>998</v>
+        <v>982</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>997</v>
+        <v>981</v>
       </c>
       <c r="D105" s="9" t="s">
         <v>471</v>
@@ -10172,7 +10189,7 @@
         <v>193</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>767</v>
+        <v>751</v>
       </c>
       <c r="H105" s="4" t="s">
         <v>180</v>
@@ -10186,25 +10203,25 @@
     </row>
     <row r="106" spans="1:14" ht="25">
       <c r="A106" s="8" t="s">
-        <v>996</v>
+        <v>980</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>995</v>
+        <v>979</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>991</v>
+        <v>975</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>994</v>
+        <v>978</v>
       </c>
       <c r="E106" s="9" t="s">
-        <v>993</v>
+        <v>977</v>
       </c>
       <c r="F106" s="7" t="s">
         <v>200</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>773</v>
+        <v>757</v>
       </c>
       <c r="H106" s="4" t="s">
         <v>180</v>
@@ -10218,25 +10235,25 @@
     </row>
     <row r="107" spans="1:14" ht="25">
       <c r="A107" s="8" t="s">
-        <v>992</v>
+        <v>976</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>991</v>
+        <v>975</v>
       </c>
       <c r="C107" s="9" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>989</v>
+        <v>973</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>988</v>
+        <v>972</v>
       </c>
       <c r="F107" s="7" t="s">
         <v>186</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>779</v>
+        <v>763</v>
       </c>
       <c r="H107" s="4" t="s">
         <v>180</v>
@@ -10250,25 +10267,25 @@
     </row>
     <row r="108" spans="1:14" ht="37.5">
       <c r="A108" s="8" t="s">
-        <v>987</v>
+        <v>971</v>
       </c>
       <c r="B108" s="9" t="s">
-        <v>986</v>
+        <v>970</v>
       </c>
       <c r="C108" s="9" t="s">
-        <v>985</v>
+        <v>969</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>984</v>
+        <v>968</v>
       </c>
       <c r="E108" s="9" t="s">
-        <v>983</v>
+        <v>967</v>
       </c>
       <c r="F108" s="7" t="s">
         <v>200</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>786</v>
+        <v>770</v>
       </c>
       <c r="H108" s="4" t="s">
         <v>180</v>
@@ -10282,25 +10299,25 @@
     </row>
     <row r="109" spans="1:14">
       <c r="A109" s="8" t="s">
-        <v>982</v>
+        <v>966</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>913</v>
+        <v>897</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>981</v>
+        <v>965</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>915</v>
+        <v>899</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>914</v>
+        <v>898</v>
       </c>
       <c r="F109" s="7" t="s">
         <v>193</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>792</v>
+        <v>776</v>
       </c>
       <c r="H109" s="4" t="s">
         <v>180</v>
@@ -10314,25 +10331,25 @@
     </row>
     <row r="110" spans="1:14" ht="25">
       <c r="A110" s="8" t="s">
-        <v>980</v>
+        <v>964</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>979</v>
+        <v>963</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>978</v>
+        <v>962</v>
       </c>
       <c r="D110" s="9" t="s">
-        <v>915</v>
+        <v>899</v>
       </c>
       <c r="E110" s="9" t="s">
-        <v>914</v>
+        <v>898</v>
       </c>
       <c r="F110" s="7" t="s">
         <v>200</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>799</v>
+        <v>783</v>
       </c>
       <c r="H110" s="4" t="s">
         <v>180</v>
@@ -10346,25 +10363,25 @@
     </row>
     <row r="111" spans="1:14" ht="25">
       <c r="A111" s="8" t="s">
-        <v>977</v>
+        <v>961</v>
       </c>
       <c r="B111" s="9" t="s">
-        <v>976</v>
+        <v>960</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>975</v>
+        <v>959</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>974</v>
+        <v>958</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>973</v>
+        <v>957</v>
       </c>
       <c r="F111" s="7" t="s">
         <v>200</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>802</v>
+        <v>786</v>
       </c>
       <c r="H111" s="4" t="s">
         <v>180</v>
@@ -10378,25 +10395,25 @@
     </row>
     <row r="112" spans="1:14" ht="25">
       <c r="A112" s="8" t="s">
-        <v>972</v>
+        <v>956</v>
       </c>
       <c r="B112" s="9" t="s">
-        <v>971</v>
+        <v>955</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>970</v>
+        <v>954</v>
       </c>
       <c r="D112" s="9" t="s">
-        <v>969</v>
+        <v>953</v>
       </c>
       <c r="E112" s="9" t="s">
-        <v>968</v>
+        <v>952</v>
       </c>
       <c r="F112" s="7" t="s">
         <v>178</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>805</v>
+        <v>789</v>
       </c>
       <c r="H112" s="4" t="s">
         <v>180</v>
@@ -10410,25 +10427,25 @@
     </row>
     <row r="113" spans="1:14" ht="37.5">
       <c r="A113" s="8" t="s">
-        <v>967</v>
+        <v>951</v>
       </c>
       <c r="B113" s="9" t="s">
-        <v>966</v>
+        <v>950</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>965</v>
+        <v>949</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>964</v>
+        <v>948</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>963</v>
+        <v>947</v>
       </c>
       <c r="F113" s="7" t="s">
         <v>193</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>807</v>
+        <v>791</v>
       </c>
       <c r="H113" s="4" t="s">
         <v>180</v>
@@ -10442,25 +10459,25 @@
     </row>
     <row r="114" spans="1:14" ht="25">
       <c r="A114" s="8" t="s">
-        <v>962</v>
+        <v>946</v>
       </c>
       <c r="B114" s="9" t="s">
-        <v>961</v>
+        <v>945</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>960</v>
+        <v>944</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>959</v>
+        <v>943</v>
       </c>
       <c r="E114" s="9" t="s">
-        <v>958</v>
+        <v>942</v>
       </c>
       <c r="F114" s="7" t="s">
         <v>200</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>809</v>
+        <v>793</v>
       </c>
       <c r="H114" s="4" t="s">
         <v>180</v>
@@ -10474,25 +10491,25 @@
     </row>
     <row r="115" spans="1:14" ht="25">
       <c r="A115" s="8" t="s">
-        <v>957</v>
+        <v>941</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>956</v>
+        <v>940</v>
       </c>
       <c r="C115" s="9" t="s">
-        <v>955</v>
+        <v>939</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>954</v>
+        <v>938</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>953</v>
+        <v>937</v>
       </c>
       <c r="F115" s="7" t="s">
         <v>186</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>811</v>
+        <v>795</v>
       </c>
       <c r="H115" s="4" t="s">
         <v>180</v>
@@ -10506,25 +10523,25 @@
     </row>
     <row r="116" spans="1:14" ht="25">
       <c r="A116" s="8" t="s">
-        <v>952</v>
+        <v>936</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>951</v>
+        <v>935</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>950</v>
+        <v>934</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>949</v>
+        <v>933</v>
       </c>
       <c r="E116" s="9" t="s">
-        <v>948</v>
+        <v>932</v>
       </c>
       <c r="F116" s="7" t="s">
         <v>178</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>813</v>
+        <v>797</v>
       </c>
       <c r="H116" s="4" t="s">
         <v>180</v>
@@ -10538,25 +10555,25 @@
     </row>
     <row r="117" spans="1:14" ht="25">
       <c r="A117" s="8" t="s">
-        <v>947</v>
+        <v>931</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>946</v>
+        <v>930</v>
       </c>
       <c r="C117" s="9" t="s">
-        <v>945</v>
+        <v>929</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>944</v>
+        <v>928</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>943</v>
+        <v>927</v>
       </c>
       <c r="F117" s="7" t="s">
         <v>193</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>815</v>
+        <v>799</v>
       </c>
       <c r="H117" s="4" t="s">
         <v>180</v>
@@ -10570,25 +10587,25 @@
     </row>
     <row r="118" spans="1:14" ht="25">
       <c r="A118" s="8" t="s">
-        <v>942</v>
+        <v>926</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>941</v>
+        <v>925</v>
       </c>
       <c r="C118" s="9" t="s">
-        <v>940</v>
+        <v>924</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>939</v>
+        <v>923</v>
       </c>
       <c r="E118" s="9" t="s">
-        <v>938</v>
+        <v>922</v>
       </c>
       <c r="F118" s="7" t="s">
         <v>193</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>817</v>
+        <v>801</v>
       </c>
       <c r="H118" s="4" t="s">
         <v>180</v>
@@ -10602,25 +10619,25 @@
     </row>
     <row r="119" spans="1:14" ht="25">
       <c r="A119" s="8" t="s">
-        <v>937</v>
+        <v>921</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>936</v>
+        <v>920</v>
       </c>
       <c r="C119" s="9" t="s">
-        <v>935</v>
+        <v>919</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>934</v>
+        <v>918</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>933</v>
+        <v>917</v>
       </c>
       <c r="F119" s="7" t="s">
         <v>193</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>820</v>
+        <v>804</v>
       </c>
       <c r="H119" s="4" t="s">
         <v>180</v>
@@ -10634,25 +10651,25 @@
     </row>
     <row r="120" spans="1:14" ht="62.5">
       <c r="A120" s="8" t="s">
-        <v>932</v>
+        <v>916</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>931</v>
+        <v>915</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>930</v>
+        <v>914</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>929</v>
+        <v>913</v>
       </c>
       <c r="E120" s="9" t="s">
-        <v>928</v>
+        <v>912</v>
       </c>
       <c r="F120" s="7" t="s">
         <v>200</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>824</v>
+        <v>808</v>
       </c>
       <c r="H120" s="4" t="s">
         <v>180</v>
@@ -10666,25 +10683,25 @@
     </row>
     <row r="121" spans="1:14" ht="50">
       <c r="A121" s="8" t="s">
-        <v>927</v>
+        <v>911</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>926</v>
+        <v>910</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>925</v>
+        <v>909</v>
       </c>
       <c r="D121" s="9" t="s">
-        <v>924</v>
+        <v>908</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>923</v>
+        <v>907</v>
       </c>
       <c r="F121" s="7" t="s">
         <v>200</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>827</v>
+        <v>811</v>
       </c>
       <c r="H121" s="4" t="s">
         <v>180</v>
@@ -10698,25 +10715,25 @@
     </row>
     <row r="122" spans="1:14" ht="62.5">
       <c r="A122" s="8" t="s">
-        <v>922</v>
+        <v>906</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>921</v>
+        <v>905</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>920</v>
+        <v>904</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>919</v>
+        <v>903</v>
       </c>
       <c r="E122" s="9" t="s">
-        <v>918</v>
+        <v>902</v>
       </c>
       <c r="F122" s="7" t="s">
         <v>200</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>830</v>
+        <v>814</v>
       </c>
       <c r="H122" s="4" t="s">
         <v>180</v>
@@ -10730,25 +10747,25 @@
     </row>
     <row r="123" spans="1:14" ht="25">
       <c r="A123" s="8" t="s">
-        <v>917</v>
+        <v>901</v>
       </c>
       <c r="B123" s="9" t="s">
-        <v>916</v>
+        <v>900</v>
       </c>
       <c r="C123" s="9" t="s">
-        <v>915</v>
+        <v>899</v>
       </c>
       <c r="D123" s="9" t="s">
-        <v>914</v>
+        <v>898</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>913</v>
+        <v>897</v>
       </c>
       <c r="F123" s="7" t="s">
         <v>200</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>833</v>
+        <v>817</v>
       </c>
       <c r="H123" s="4" t="s">
         <v>180</v>
@@ -10762,25 +10779,25 @@
     </row>
     <row r="124" spans="1:14" ht="25">
       <c r="A124" s="8" t="s">
-        <v>912</v>
+        <v>896</v>
       </c>
       <c r="B124" s="9" t="s">
-        <v>911</v>
+        <v>895</v>
       </c>
       <c r="C124" s="9" t="s">
-        <v>910</v>
+        <v>894</v>
       </c>
       <c r="D124" s="9" t="s">
-        <v>909</v>
+        <v>893</v>
       </c>
       <c r="E124" s="9" t="s">
-        <v>908</v>
+        <v>892</v>
       </c>
       <c r="F124" s="7" t="s">
         <v>186</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>836</v>
+        <v>820</v>
       </c>
       <c r="H124" s="4" t="s">
         <v>180</v>
@@ -10794,25 +10811,25 @@
     </row>
     <row r="125" spans="1:14" ht="50">
       <c r="A125" s="8" t="s">
-        <v>907</v>
+        <v>891</v>
       </c>
       <c r="B125" s="9" t="s">
-        <v>906</v>
+        <v>890</v>
       </c>
       <c r="C125" s="9" t="s">
-        <v>905</v>
+        <v>889</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>904</v>
+        <v>888</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>903</v>
+        <v>887</v>
       </c>
       <c r="F125" s="7" t="s">
         <v>186</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>839</v>
+        <v>823</v>
       </c>
       <c r="H125" s="4" t="s">
         <v>180</v>
@@ -10826,25 +10843,25 @@
     </row>
     <row r="126" spans="1:14" ht="37.5">
       <c r="A126" s="8" t="s">
-        <v>902</v>
+        <v>886</v>
       </c>
       <c r="B126" s="9" t="s">
-        <v>901</v>
+        <v>885</v>
       </c>
       <c r="C126" s="9" t="s">
-        <v>900</v>
+        <v>884</v>
       </c>
       <c r="D126" s="9" t="s">
-        <v>899</v>
+        <v>883</v>
       </c>
       <c r="E126" s="9" t="s">
-        <v>898</v>
+        <v>882</v>
       </c>
       <c r="F126" s="7" t="s">
         <v>178</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>842</v>
+        <v>826</v>
       </c>
       <c r="H126" s="4" t="s">
         <v>180</v>
@@ -10876,7 +10893,7 @@
         <v>186</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>845</v>
+        <v>829</v>
       </c>
       <c r="H127" s="4" t="s">
         <v>180</v>
@@ -10908,7 +10925,7 @@
         <v>193</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>848</v>
+        <v>832</v>
       </c>
       <c r="H128" s="4" t="s">
         <v>180</v>
@@ -10940,7 +10957,7 @@
         <v>200</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>851</v>
+        <v>835</v>
       </c>
       <c r="H129" s="4" t="s">
         <v>180</v>
@@ -10972,7 +10989,7 @@
         <v>200</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>854</v>
+        <v>838</v>
       </c>
       <c r="H130" s="4" t="s">
         <v>180</v>
@@ -11004,7 +11021,7 @@
         <v>186</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>857</v>
+        <v>841</v>
       </c>
       <c r="H131" s="4" t="s">
         <v>180</v>
@@ -11036,7 +11053,7 @@
         <v>200</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>860</v>
+        <v>844</v>
       </c>
       <c r="H132" s="4" t="s">
         <v>180</v>
@@ -11068,7 +11085,7 @@
         <v>178</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>863</v>
+        <v>847</v>
       </c>
       <c r="H133" s="4" t="s">
         <v>180</v>
@@ -11100,7 +11117,7 @@
         <v>186</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>866</v>
+        <v>850</v>
       </c>
       <c r="H134" s="4" t="s">
         <v>180</v>
@@ -11132,7 +11149,7 @@
         <v>193</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>869</v>
+        <v>853</v>
       </c>
       <c r="H135" s="4" t="s">
         <v>180</v>
@@ -11164,7 +11181,7 @@
         <v>193</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>871</v>
+        <v>855</v>
       </c>
       <c r="H136" s="4" t="s">
         <v>180</v>
@@ -11196,7 +11213,7 @@
         <v>186</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>874</v>
+        <v>858</v>
       </c>
       <c r="H137" s="4" t="s">
         <v>180</v>
@@ -11228,7 +11245,7 @@
         <v>193</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>877</v>
+        <v>861</v>
       </c>
       <c r="H138" s="4" t="s">
         <v>180</v>
@@ -11260,7 +11277,7 @@
         <v>186</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>880</v>
+        <v>864</v>
       </c>
       <c r="H139" s="4" t="s">
         <v>180</v>
@@ -11292,7 +11309,7 @@
         <v>186</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>882</v>
+        <v>866</v>
       </c>
       <c r="H140" s="4" t="s">
         <v>180</v>
@@ -11324,7 +11341,7 @@
         <v>178</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>1542</v>
+        <v>1523</v>
       </c>
       <c r="H141" s="4" t="s">
         <v>180</v>
@@ -11356,7 +11373,7 @@
         <v>186</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>1543</v>
+        <v>1524</v>
       </c>
       <c r="H142" s="4" t="s">
         <v>180</v>
@@ -11388,7 +11405,7 @@
         <v>186</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>1544</v>
+        <v>1525</v>
       </c>
       <c r="H143" s="4" t="s">
         <v>180</v>
@@ -11420,7 +11437,7 @@
         <v>178</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>1545</v>
+        <v>1526</v>
       </c>
       <c r="H144" s="4" t="s">
         <v>180</v>
@@ -11452,7 +11469,7 @@
         <v>200</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>1546</v>
+        <v>1527</v>
       </c>
       <c r="H145" s="4" t="s">
         <v>180</v>
@@ -11484,7 +11501,7 @@
         <v>193</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>1547</v>
+        <v>1528</v>
       </c>
       <c r="H146" s="4" t="s">
         <v>180</v>
@@ -11516,7 +11533,7 @@
         <v>193</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>1548</v>
+        <v>1529</v>
       </c>
       <c r="H147" s="4" t="s">
         <v>180</v>
@@ -11548,7 +11565,7 @@
         <v>178</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>1549</v>
+        <v>1530</v>
       </c>
       <c r="H148" s="4" t="s">
         <v>180</v>
@@ -11580,7 +11597,7 @@
         <v>193</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>1550</v>
+        <v>1531</v>
       </c>
       <c r="H149" s="4" t="s">
         <v>180</v>
@@ -11612,7 +11629,7 @@
         <v>186</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>1551</v>
+        <v>1532</v>
       </c>
       <c r="H150" s="4" t="s">
         <v>180</v>
@@ -11644,7 +11661,7 @@
         <v>193</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>1552</v>
+        <v>1533</v>
       </c>
       <c r="H151" s="4" t="s">
         <v>180</v>
@@ -11676,7 +11693,7 @@
         <v>178</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>1553</v>
+        <v>1534</v>
       </c>
       <c r="H152" s="4" t="s">
         <v>180</v>
@@ -11708,7 +11725,7 @@
         <v>200</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>1554</v>
+        <v>1535</v>
       </c>
       <c r="H153" s="4" t="s">
         <v>180</v>
@@ -11740,7 +11757,7 @@
         <v>186</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>1555</v>
+        <v>1536</v>
       </c>
       <c r="H154" s="4" t="s">
         <v>180</v>
@@ -11772,7 +11789,7 @@
         <v>178</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>1556</v>
+        <v>1537</v>
       </c>
       <c r="H155" s="4" t="s">
         <v>180</v>
@@ -11804,7 +11821,7 @@
         <v>193</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>1557</v>
+        <v>1538</v>
       </c>
       <c r="H156" s="4" t="s">
         <v>180</v>
@@ -11836,7 +11853,7 @@
         <v>193</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>1558</v>
+        <v>1539</v>
       </c>
       <c r="H157" s="4" t="s">
         <v>180</v>
@@ -11868,7 +11885,7 @@
         <v>200</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>1559</v>
+        <v>1540</v>
       </c>
       <c r="H158" s="4" t="s">
         <v>180</v>
@@ -11900,7 +11917,7 @@
         <v>200</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>1560</v>
+        <v>1541</v>
       </c>
       <c r="H159" s="4" t="s">
         <v>180</v>
@@ -11932,7 +11949,7 @@
         <v>193</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>1561</v>
+        <v>1542</v>
       </c>
       <c r="H160" s="4" t="s">
         <v>180</v>
@@ -11964,7 +11981,7 @@
         <v>200</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>1562</v>
+        <v>1543</v>
       </c>
       <c r="H161" s="4" t="s">
         <v>180</v>
@@ -11996,7 +12013,7 @@
         <v>186</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>1563</v>
+        <v>1544</v>
       </c>
       <c r="H162" s="4" t="s">
         <v>180</v>
@@ -12028,7 +12045,7 @@
         <v>200</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>1564</v>
+        <v>1545</v>
       </c>
       <c r="H163" s="4" t="s">
         <v>180</v>
@@ -12060,7 +12077,7 @@
         <v>193</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>1565</v>
+        <v>1546</v>
       </c>
       <c r="H164" s="4" t="s">
         <v>180</v>
@@ -12092,7 +12109,7 @@
         <v>200</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>1566</v>
+        <v>1547</v>
       </c>
       <c r="H165" s="4" t="s">
         <v>180</v>
@@ -12124,7 +12141,7 @@
         <v>178</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>1567</v>
+        <v>1548</v>
       </c>
       <c r="H166" s="4" t="s">
         <v>180</v>
@@ -12156,7 +12173,7 @@
         <v>186</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>1568</v>
+        <v>1549</v>
       </c>
       <c r="H167" s="4" t="s">
         <v>180</v>
@@ -12188,7 +12205,7 @@
         <v>200</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>1569</v>
+        <v>1550</v>
       </c>
       <c r="H168" s="4" t="s">
         <v>180</v>
@@ -12220,7 +12237,7 @@
         <v>178</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>1570</v>
+        <v>1551</v>
       </c>
       <c r="H169" s="4" t="s">
         <v>180</v>
@@ -12252,7 +12269,7 @@
         <v>186</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>1571</v>
+        <v>1552</v>
       </c>
       <c r="H170" s="4" t="s">
         <v>180</v>
@@ -12284,7 +12301,7 @@
         <v>193</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>1572</v>
+        <v>1553</v>
       </c>
       <c r="H171" s="4" t="s">
         <v>180</v>
@@ -12316,7 +12333,7 @@
         <v>200</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>1573</v>
+        <v>1554</v>
       </c>
       <c r="H172" s="4" t="s">
         <v>180</v>
@@ -12348,7 +12365,7 @@
         <v>178</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>1574</v>
+        <v>1555</v>
       </c>
       <c r="H173" s="4" t="s">
         <v>180</v>
@@ -12380,7 +12397,7 @@
         <v>193</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>1575</v>
+        <v>1556</v>
       </c>
       <c r="H174" s="4" t="s">
         <v>180</v>
@@ -12412,7 +12429,7 @@
         <v>200</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>1576</v>
+        <v>1557</v>
       </c>
       <c r="H175" s="4" t="s">
         <v>180</v>
@@ -12444,7 +12461,7 @@
         <v>186</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>1577</v>
+        <v>1558</v>
       </c>
       <c r="H176" s="4" t="s">
         <v>180</v>
@@ -12476,7 +12493,7 @@
         <v>193</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>1578</v>
+        <v>1559</v>
       </c>
       <c r="H177" s="4" t="s">
         <v>180</v>
@@ -12508,7 +12525,7 @@
         <v>178</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>1579</v>
+        <v>1560</v>
       </c>
       <c r="H178" s="4" t="s">
         <v>180</v>
@@ -12540,7 +12557,7 @@
         <v>200</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>1580</v>
+        <v>1561</v>
       </c>
       <c r="H179" s="4" t="s">
         <v>180</v>
@@ -12572,7 +12589,7 @@
         <v>178</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>1581</v>
+        <v>1562</v>
       </c>
       <c r="H180" s="4" t="s">
         <v>180</v>
@@ -12604,7 +12621,7 @@
         <v>186</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>1582</v>
+        <v>1563</v>
       </c>
       <c r="H181" s="4" t="s">
         <v>180</v>
@@ -12636,7 +12653,7 @@
         <v>193</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>1583</v>
+        <v>1564</v>
       </c>
       <c r="H182" s="4" t="s">
         <v>180</v>
@@ -12668,7 +12685,7 @@
         <v>178</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>1584</v>
+        <v>1565</v>
       </c>
       <c r="H183" s="4" t="s">
         <v>180</v>
@@ -12700,7 +12717,7 @@
         <v>200</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>1585</v>
+        <v>1566</v>
       </c>
       <c r="H184" s="4" t="s">
         <v>180</v>
@@ -12732,7 +12749,7 @@
         <v>186</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>1586</v>
+        <v>1567</v>
       </c>
       <c r="H185" s="4" t="s">
         <v>180</v>
@@ -12764,7 +12781,7 @@
         <v>178</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>1587</v>
+        <v>1568</v>
       </c>
       <c r="H186" s="4" t="s">
         <v>180</v>
@@ -12796,7 +12813,7 @@
         <v>200</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>1588</v>
+        <v>1569</v>
       </c>
       <c r="H187" s="4" t="s">
         <v>180</v>
@@ -12828,7 +12845,7 @@
         <v>193</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>1589</v>
+        <v>1570</v>
       </c>
       <c r="H188" s="4" t="s">
         <v>180</v>
@@ -12860,7 +12877,7 @@
         <v>186</v>
       </c>
       <c r="G189" s="4" t="s">
-        <v>1590</v>
+        <v>1571</v>
       </c>
       <c r="H189" s="4" t="s">
         <v>180</v>
@@ -12892,7 +12909,7 @@
         <v>193</v>
       </c>
       <c r="G190" s="4" t="s">
-        <v>1591</v>
+        <v>1572</v>
       </c>
       <c r="H190" s="4" t="s">
         <v>180</v>
@@ -12924,7 +12941,7 @@
         <v>193</v>
       </c>
       <c r="G191" s="4" t="s">
-        <v>1592</v>
+        <v>1573</v>
       </c>
       <c r="H191" s="4" t="s">
         <v>180</v>
@@ -12956,7 +12973,7 @@
         <v>186</v>
       </c>
       <c r="G192" s="4" t="s">
-        <v>1593</v>
+        <v>1574</v>
       </c>
       <c r="H192" s="4" t="s">
         <v>180</v>
@@ -12988,7 +13005,7 @@
         <v>200</v>
       </c>
       <c r="G193" s="4" t="s">
-        <v>1594</v>
+        <v>1575</v>
       </c>
       <c r="H193" s="4" t="s">
         <v>180</v>
@@ -13020,7 +13037,7 @@
         <v>186</v>
       </c>
       <c r="G194" s="4" t="s">
-        <v>1595</v>
+        <v>1576</v>
       </c>
       <c r="H194" s="4" t="s">
         <v>180</v>
@@ -13052,7 +13069,7 @@
         <v>193</v>
       </c>
       <c r="G195" s="4" t="s">
-        <v>1596</v>
+        <v>1577</v>
       </c>
       <c r="H195" s="4" t="s">
         <v>180</v>
@@ -13084,7 +13101,7 @@
         <v>186</v>
       </c>
       <c r="G196" s="4" t="s">
-        <v>1597</v>
+        <v>1578</v>
       </c>
       <c r="H196" s="4" t="s">
         <v>180</v>
@@ -13116,7 +13133,7 @@
         <v>178</v>
       </c>
       <c r="G197" s="4" t="s">
-        <v>1598</v>
+        <v>1579</v>
       </c>
       <c r="H197" s="4" t="s">
         <v>180</v>
@@ -13148,7 +13165,7 @@
         <v>186</v>
       </c>
       <c r="G198" s="4" t="s">
-        <v>1599</v>
+        <v>1580</v>
       </c>
       <c r="H198" s="4" t="s">
         <v>180</v>
@@ -13180,7 +13197,7 @@
         <v>193</v>
       </c>
       <c r="G199" s="4" t="s">
-        <v>1600</v>
+        <v>1581</v>
       </c>
       <c r="H199" s="4" t="s">
         <v>180</v>
@@ -13212,7 +13229,7 @@
         <v>193</v>
       </c>
       <c r="G200" s="4" t="s">
-        <v>1601</v>
+        <v>1582</v>
       </c>
       <c r="H200" s="4" t="s">
         <v>180</v>
@@ -13244,7 +13261,7 @@
         <v>186</v>
       </c>
       <c r="G201" s="4" t="s">
-        <v>1602</v>
+        <v>1583</v>
       </c>
       <c r="H201" s="4" t="s">
         <v>180</v>
@@ -13276,7 +13293,7 @@
         <v>193</v>
       </c>
       <c r="G202" s="4" t="s">
-        <v>1603</v>
+        <v>1584</v>
       </c>
       <c r="H202" s="4" t="s">
         <v>180</v>
@@ -13308,7 +13325,7 @@
         <v>601</v>
       </c>
       <c r="G203" s="4" t="s">
-        <v>1604</v>
+        <v>1585</v>
       </c>
       <c r="H203" s="4" t="s">
         <v>603</v>
@@ -13340,7 +13357,7 @@
         <v>601</v>
       </c>
       <c r="G204" s="4" t="s">
-        <v>1605</v>
+        <v>1586</v>
       </c>
       <c r="H204" s="4" t="s">
         <v>603</v>
@@ -13354,25 +13371,25 @@
     </row>
     <row r="205" spans="1:14" ht="50">
       <c r="A205" s="8" t="s">
-        <v>1541</v>
+        <v>1522</v>
       </c>
       <c r="B205" s="8" t="s">
-        <v>1540</v>
+        <v>1521</v>
       </c>
       <c r="C205" s="8" t="s">
-        <v>1539</v>
+        <v>1520</v>
       </c>
       <c r="D205" s="8" t="s">
-        <v>1538</v>
+        <v>1519</v>
       </c>
       <c r="E205" s="8" t="s">
-        <v>1537</v>
+        <v>1518</v>
       </c>
       <c r="F205" s="7" t="s">
-        <v>1536</v>
+        <v>1517</v>
       </c>
       <c r="G205" s="4" t="s">
-        <v>1606</v>
+        <v>1587</v>
       </c>
       <c r="H205" s="4" t="s">
         <v>603</v>
@@ -13386,25 +13403,25 @@
     </row>
     <row r="206" spans="1:14" ht="50">
       <c r="A206" s="8" t="s">
-        <v>1535</v>
+        <v>1516</v>
       </c>
       <c r="B206" s="8" t="s">
-        <v>1534</v>
+        <v>1515</v>
       </c>
       <c r="C206" s="8" t="s">
-        <v>1533</v>
+        <v>1514</v>
       </c>
       <c r="D206" s="8" t="s">
-        <v>1532</v>
+        <v>1513</v>
       </c>
       <c r="E206" s="8" t="s">
-        <v>1531</v>
+        <v>1512</v>
       </c>
       <c r="F206" s="7" t="s">
-        <v>1484</v>
+        <v>1465</v>
       </c>
       <c r="G206" s="4" t="s">
-        <v>1607</v>
+        <v>1588</v>
       </c>
       <c r="H206" s="4" t="s">
         <v>603</v>
@@ -13418,25 +13435,25 @@
     </row>
     <row r="207" spans="1:14" ht="62.5">
       <c r="A207" s="8" t="s">
-        <v>1530</v>
+        <v>1511</v>
       </c>
       <c r="B207" s="8" t="s">
-        <v>1529</v>
+        <v>1510</v>
       </c>
       <c r="C207" s="8" t="s">
-        <v>1528</v>
+        <v>1509</v>
       </c>
       <c r="D207" s="8" t="s">
-        <v>1527</v>
+        <v>1508</v>
       </c>
       <c r="E207" s="8" t="s">
-        <v>1526</v>
+        <v>1507</v>
       </c>
       <c r="F207" s="7" t="s">
-        <v>1478</v>
+        <v>1459</v>
       </c>
       <c r="G207" s="4" t="s">
-        <v>1608</v>
+        <v>1589</v>
       </c>
       <c r="H207" s="4" t="s">
         <v>603</v>
@@ -13450,25 +13467,25 @@
     </row>
     <row r="208" spans="1:14" ht="50">
       <c r="A208" s="8" t="s">
-        <v>1525</v>
+        <v>1506</v>
       </c>
       <c r="B208" s="8" t="s">
-        <v>1524</v>
+        <v>1505</v>
       </c>
       <c r="C208" s="8" t="s">
-        <v>1523</v>
+        <v>1504</v>
       </c>
       <c r="D208" s="8" t="s">
-        <v>1522</v>
+        <v>1503</v>
       </c>
       <c r="E208" s="8" t="s">
-        <v>1521</v>
+        <v>1502</v>
       </c>
       <c r="F208" s="7" t="s">
         <v>679</v>
       </c>
       <c r="G208" s="4" t="s">
-        <v>1609</v>
+        <v>1590</v>
       </c>
       <c r="H208" s="4" t="s">
         <v>603</v>
@@ -13482,25 +13499,25 @@
     </row>
     <row r="209" spans="1:14" ht="50">
       <c r="A209" s="8" t="s">
-        <v>1520</v>
+        <v>1501</v>
       </c>
       <c r="B209" s="8" t="s">
-        <v>1519</v>
+        <v>1500</v>
       </c>
       <c r="C209" s="8" t="s">
-        <v>1518</v>
+        <v>1499</v>
       </c>
       <c r="D209" s="8" t="s">
-        <v>1517</v>
+        <v>1498</v>
       </c>
       <c r="E209" s="8" t="s">
-        <v>1516</v>
+        <v>1497</v>
       </c>
       <c r="F209" s="7" t="s">
-        <v>1484</v>
+        <v>1465</v>
       </c>
       <c r="G209" s="4" t="s">
-        <v>1610</v>
+        <v>1591</v>
       </c>
       <c r="H209" s="4" t="s">
         <v>603</v>
@@ -13514,25 +13531,25 @@
     </row>
     <row r="210" spans="1:14" ht="62.5">
       <c r="A210" s="8" t="s">
-        <v>1515</v>
+        <v>1496</v>
       </c>
       <c r="B210" s="8" t="s">
-        <v>1514</v>
+        <v>1495</v>
       </c>
       <c r="C210" s="8" t="s">
-        <v>1513</v>
+        <v>1494</v>
       </c>
       <c r="D210" s="8" t="s">
-        <v>1512</v>
+        <v>1493</v>
       </c>
       <c r="E210" s="8" t="s">
-        <v>1511</v>
+        <v>1492</v>
       </c>
       <c r="F210" s="7" t="s">
-        <v>1510</v>
+        <v>1491</v>
       </c>
       <c r="G210" s="4" t="s">
-        <v>1611</v>
+        <v>1592</v>
       </c>
       <c r="H210" s="4" t="s">
         <v>603</v>
@@ -13546,25 +13563,25 @@
     </row>
     <row r="211" spans="1:14" ht="62.5">
       <c r="A211" s="8" t="s">
-        <v>1509</v>
+        <v>1490</v>
       </c>
       <c r="B211" s="8" t="s">
-        <v>1508</v>
+        <v>1489</v>
       </c>
       <c r="C211" s="8" t="s">
-        <v>1507</v>
+        <v>1488</v>
       </c>
       <c r="D211" s="8" t="s">
-        <v>1506</v>
+        <v>1487</v>
       </c>
       <c r="E211" s="8" t="s">
-        <v>1505</v>
+        <v>1486</v>
       </c>
       <c r="F211" s="7" t="s">
         <v>679</v>
       </c>
       <c r="G211" s="4" t="s">
-        <v>1612</v>
+        <v>1593</v>
       </c>
       <c r="H211" s="4" t="s">
         <v>603</v>
@@ -13578,25 +13595,25 @@
     </row>
     <row r="212" spans="1:14" ht="62.5">
       <c r="A212" s="8" t="s">
-        <v>1504</v>
+        <v>1485</v>
       </c>
       <c r="B212" s="8" t="s">
-        <v>1503</v>
+        <v>1484</v>
       </c>
       <c r="C212" s="8" t="s">
-        <v>1502</v>
+        <v>1483</v>
       </c>
       <c r="D212" s="8" t="s">
-        <v>1501</v>
+        <v>1482</v>
       </c>
       <c r="E212" s="8" t="s">
-        <v>1500</v>
+        <v>1481</v>
       </c>
       <c r="F212" s="7" t="s">
-        <v>1478</v>
+        <v>1459</v>
       </c>
       <c r="G212" s="4" t="s">
-        <v>1613</v>
+        <v>1594</v>
       </c>
       <c r="H212" s="4" t="s">
         <v>603</v>
@@ -13610,25 +13627,25 @@
     </row>
     <row r="213" spans="1:14" ht="50">
       <c r="A213" s="8" t="s">
-        <v>1499</v>
+        <v>1480</v>
       </c>
       <c r="B213" s="8" t="s">
-        <v>1498</v>
+        <v>1479</v>
       </c>
       <c r="C213" s="8" t="s">
-        <v>1497</v>
+        <v>1478</v>
       </c>
       <c r="D213" s="8" t="s">
-        <v>1496</v>
+        <v>1477</v>
       </c>
       <c r="E213" s="8" t="s">
-        <v>1495</v>
+        <v>1476</v>
       </c>
       <c r="F213" s="7" t="s">
         <v>679</v>
       </c>
       <c r="G213" s="4" t="s">
-        <v>1614</v>
+        <v>1595</v>
       </c>
       <c r="H213" s="4" t="s">
         <v>603</v>
@@ -13642,25 +13659,25 @@
     </row>
     <row r="214" spans="1:14" ht="75">
       <c r="A214" s="8" t="s">
-        <v>1494</v>
+        <v>1475</v>
       </c>
       <c r="B214" s="8" t="s">
-        <v>1493</v>
+        <v>1474</v>
       </c>
       <c r="C214" s="8" t="s">
-        <v>1492</v>
+        <v>1473</v>
       </c>
       <c r="D214" s="8" t="s">
-        <v>1491</v>
+        <v>1472</v>
       </c>
       <c r="E214" s="8" t="s">
-        <v>1490</v>
+        <v>1471</v>
       </c>
       <c r="F214" s="7" t="s">
         <v>634</v>
       </c>
       <c r="G214" s="4" t="s">
-        <v>1615</v>
+        <v>1596</v>
       </c>
       <c r="H214" s="4" t="s">
         <v>603</v>
@@ -13674,25 +13691,25 @@
     </row>
     <row r="215" spans="1:14" ht="50">
       <c r="A215" s="8" t="s">
-        <v>1489</v>
+        <v>1470</v>
       </c>
       <c r="B215" s="8" t="s">
-        <v>1488</v>
+        <v>1469</v>
       </c>
       <c r="C215" s="8" t="s">
-        <v>1487</v>
+        <v>1468</v>
       </c>
       <c r="D215" s="8" t="s">
-        <v>1486</v>
+        <v>1467</v>
       </c>
       <c r="E215" s="8" t="s">
-        <v>1485</v>
+        <v>1466</v>
       </c>
       <c r="F215" s="7" t="s">
-        <v>1484</v>
+        <v>1465</v>
       </c>
       <c r="G215" s="4" t="s">
-        <v>1616</v>
+        <v>1597</v>
       </c>
       <c r="H215" s="4" t="s">
         <v>603</v>
@@ -13706,25 +13723,25 @@
     </row>
     <row r="216" spans="1:14" ht="50">
       <c r="A216" s="8" t="s">
-        <v>1483</v>
+        <v>1464</v>
       </c>
       <c r="B216" s="8" t="s">
-        <v>1482</v>
+        <v>1463</v>
       </c>
       <c r="C216" s="8" t="s">
-        <v>1481</v>
+        <v>1462</v>
       </c>
       <c r="D216" s="8" t="s">
-        <v>1480</v>
+        <v>1461</v>
       </c>
       <c r="E216" s="8" t="s">
-        <v>1479</v>
+        <v>1460</v>
       </c>
       <c r="F216" s="7" t="s">
-        <v>1478</v>
+        <v>1459</v>
       </c>
       <c r="G216" s="4" t="s">
-        <v>1617</v>
+        <v>1598</v>
       </c>
       <c r="H216" s="4" t="s">
         <v>603</v>
@@ -13738,25 +13755,25 @@
     </row>
     <row r="217" spans="1:14" ht="62.5">
       <c r="A217" s="8" t="s">
-        <v>1477</v>
+        <v>1458</v>
       </c>
       <c r="B217" s="8" t="s">
-        <v>1476</v>
+        <v>1457</v>
       </c>
       <c r="C217" s="8" t="s">
-        <v>1475</v>
+        <v>1456</v>
       </c>
       <c r="D217" s="8" t="s">
-        <v>1474</v>
+        <v>1455</v>
       </c>
       <c r="E217" s="8" t="s">
-        <v>1473</v>
+        <v>1454</v>
       </c>
       <c r="F217" s="7" t="s">
-        <v>798</v>
+        <v>782</v>
       </c>
       <c r="G217" s="4" t="s">
-        <v>1618</v>
+        <v>1599</v>
       </c>
       <c r="H217" s="4" t="s">
         <v>603</v>
@@ -13770,25 +13787,25 @@
     </row>
     <row r="218" spans="1:14" ht="75">
       <c r="A218" s="8" t="s">
-        <v>1472</v>
+        <v>1453</v>
       </c>
       <c r="B218" s="8" t="s">
-        <v>1471</v>
+        <v>1452</v>
       </c>
       <c r="C218" s="8" t="s">
-        <v>1470</v>
+        <v>1451</v>
       </c>
       <c r="D218" s="8" t="s">
-        <v>1469</v>
+        <v>1450</v>
       </c>
       <c r="E218" s="8" t="s">
-        <v>1468</v>
+        <v>1449</v>
       </c>
       <c r="F218" s="7" t="s">
-        <v>798</v>
+        <v>782</v>
       </c>
       <c r="G218" s="4" t="s">
-        <v>1619</v>
+        <v>1600</v>
       </c>
       <c r="H218" s="4" t="s">
         <v>603</v>
@@ -13802,25 +13819,25 @@
     </row>
     <row r="219" spans="1:14" ht="62.5">
       <c r="A219" s="8" t="s">
-        <v>1467</v>
+        <v>1448</v>
       </c>
       <c r="B219" s="8" t="s">
-        <v>1466</v>
+        <v>1447</v>
       </c>
       <c r="C219" s="8" t="s">
-        <v>1465</v>
+        <v>1446</v>
       </c>
       <c r="D219" s="8" t="s">
-        <v>1464</v>
+        <v>1445</v>
       </c>
       <c r="E219" s="8" t="s">
-        <v>1463</v>
+        <v>1444</v>
       </c>
       <c r="F219" s="7" t="s">
-        <v>798</v>
+        <v>782</v>
       </c>
       <c r="G219" s="4" t="s">
-        <v>1620</v>
+        <v>1601</v>
       </c>
       <c r="H219" s="4" t="s">
         <v>603</v>
@@ -13852,7 +13869,7 @@
         <v>615</v>
       </c>
       <c r="G220" s="4" t="s">
-        <v>1621</v>
+        <v>1602</v>
       </c>
       <c r="H220" s="4" t="s">
         <v>603</v>
@@ -13884,7 +13901,7 @@
         <v>601</v>
       </c>
       <c r="G221" s="4" t="s">
-        <v>1622</v>
+        <v>1603</v>
       </c>
       <c r="H221" s="4" t="s">
         <v>603</v>
@@ -13916,7 +13933,7 @@
         <v>601</v>
       </c>
       <c r="G222" s="4" t="s">
-        <v>1623</v>
+        <v>1604</v>
       </c>
       <c r="H222" s="4" t="s">
         <v>603</v>
@@ -13948,7 +13965,7 @@
         <v>634</v>
       </c>
       <c r="G223" s="4" t="s">
-        <v>1624</v>
+        <v>1605</v>
       </c>
       <c r="H223" s="4" t="s">
         <v>603</v>
@@ -13980,7 +13997,7 @@
         <v>634</v>
       </c>
       <c r="G224" s="4" t="s">
-        <v>1625</v>
+        <v>1606</v>
       </c>
       <c r="H224" s="4" t="s">
         <v>603</v>
@@ -14012,7 +14029,7 @@
         <v>634</v>
       </c>
       <c r="G225" s="4" t="s">
-        <v>1626</v>
+        <v>1607</v>
       </c>
       <c r="H225" s="4" t="s">
         <v>603</v>
@@ -14044,7 +14061,7 @@
         <v>634</v>
       </c>
       <c r="G226" s="4" t="s">
-        <v>1627</v>
+        <v>1608</v>
       </c>
       <c r="H226" s="4" t="s">
         <v>603</v>
@@ -14076,7 +14093,7 @@
         <v>601</v>
       </c>
       <c r="G227" s="4" t="s">
-        <v>1628</v>
+        <v>1609</v>
       </c>
       <c r="H227" s="4" t="s">
         <v>603</v>
@@ -14108,7 +14125,7 @@
         <v>665</v>
       </c>
       <c r="G228" s="4" t="s">
-        <v>1629</v>
+        <v>1610</v>
       </c>
       <c r="H228" s="4" t="s">
         <v>603</v>
@@ -14140,7 +14157,7 @@
         <v>672</v>
       </c>
       <c r="G229" s="4" t="s">
-        <v>1630</v>
+        <v>1611</v>
       </c>
       <c r="H229" s="4" t="s">
         <v>603</v>
@@ -14172,7 +14189,7 @@
         <v>679</v>
       </c>
       <c r="G230" s="4" t="s">
-        <v>1631</v>
+        <v>1612</v>
       </c>
       <c r="H230" s="4" t="s">
         <v>603</v>
@@ -14189,22 +14206,22 @@
         <v>681</v>
       </c>
       <c r="B231" s="10" t="s">
-        <v>682</v>
+        <v>1669</v>
       </c>
       <c r="C231" s="10" t="s">
-        <v>683</v>
+        <v>1670</v>
       </c>
       <c r="D231" s="10" t="s">
-        <v>684</v>
+        <v>1671</v>
       </c>
       <c r="E231" s="10" t="s">
-        <v>685</v>
+        <v>1672</v>
       </c>
       <c r="F231" s="4" t="s">
         <v>665</v>
       </c>
       <c r="G231" s="4" t="s">
-        <v>1632</v>
+        <v>1613</v>
       </c>
       <c r="H231" s="4" t="s">
         <v>603</v>
@@ -14218,25 +14235,25 @@
     </row>
     <row r="232" spans="1:14" ht="72.5">
       <c r="A232" s="4" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="B232" s="10" t="s">
-        <v>688</v>
+        <v>1673</v>
       </c>
       <c r="C232" s="10" t="s">
-        <v>689</v>
+        <v>1674</v>
       </c>
       <c r="D232" s="10" t="s">
-        <v>690</v>
+        <v>1675</v>
       </c>
       <c r="E232" s="10" t="s">
-        <v>691</v>
+        <v>1676</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="G232" s="4" t="s">
-        <v>1633</v>
+        <v>1614</v>
       </c>
       <c r="H232" s="4" t="s">
         <v>603</v>
@@ -14250,25 +14267,25 @@
     </row>
     <row r="233" spans="1:14" ht="58">
       <c r="A233" s="4" t="s">
-        <v>694</v>
+        <v>686</v>
       </c>
       <c r="B233" s="10" t="s">
-        <v>695</v>
+        <v>1677</v>
       </c>
       <c r="C233" s="10" t="s">
-        <v>696</v>
+        <v>1678</v>
       </c>
       <c r="D233" s="10" t="s">
-        <v>697</v>
+        <v>1679</v>
       </c>
       <c r="E233" s="10" t="s">
-        <v>698</v>
+        <v>1680</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>699</v>
+        <v>687</v>
       </c>
       <c r="G233" s="4" t="s">
-        <v>1634</v>
+        <v>1615</v>
       </c>
       <c r="H233" s="4" t="s">
         <v>603</v>
@@ -14282,25 +14299,25 @@
     </row>
     <row r="234" spans="1:14" ht="101.5">
       <c r="A234" s="4" t="s">
-        <v>701</v>
+        <v>689</v>
       </c>
       <c r="B234" s="10" t="s">
-        <v>702</v>
+        <v>1681</v>
       </c>
       <c r="C234" s="10" t="s">
-        <v>703</v>
+        <v>1682</v>
       </c>
       <c r="D234" s="10" t="s">
-        <v>704</v>
+        <v>1683</v>
       </c>
       <c r="E234" s="10" t="s">
-        <v>705</v>
+        <v>1684</v>
       </c>
       <c r="F234" s="4" t="s">
         <v>615</v>
       </c>
       <c r="G234" s="4" t="s">
-        <v>1635</v>
+        <v>1616</v>
       </c>
       <c r="H234" s="4" t="s">
         <v>603</v>
@@ -14314,25 +14331,25 @@
     </row>
     <row r="235" spans="1:14" ht="29">
       <c r="A235" s="4" t="s">
-        <v>707</v>
+        <v>691</v>
       </c>
       <c r="B235" s="10" t="s">
-        <v>708</v>
+        <v>692</v>
       </c>
       <c r="C235" s="10" t="s">
-        <v>709</v>
+        <v>693</v>
       </c>
       <c r="D235" s="10" t="s">
-        <v>710</v>
+        <v>694</v>
       </c>
       <c r="E235" s="10" t="s">
-        <v>711</v>
+        <v>695</v>
       </c>
       <c r="F235" s="4" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="G235" s="4" t="s">
-        <v>1636</v>
+        <v>1617</v>
       </c>
       <c r="H235" s="4" t="s">
         <v>603</v>
@@ -14346,25 +14363,25 @@
     </row>
     <row r="236" spans="1:14" ht="29">
       <c r="A236" s="4" t="s">
-        <v>713</v>
+        <v>697</v>
       </c>
       <c r="B236" s="10" t="s">
-        <v>714</v>
+        <v>698</v>
       </c>
       <c r="C236" s="10" t="s">
-        <v>715</v>
+        <v>699</v>
       </c>
       <c r="D236" s="10" t="s">
-        <v>716</v>
+        <v>700</v>
       </c>
       <c r="E236" s="10" t="s">
-        <v>717</v>
+        <v>701</v>
       </c>
       <c r="F236" s="4" t="s">
         <v>601</v>
       </c>
       <c r="G236" s="4" t="s">
-        <v>1637</v>
+        <v>1618</v>
       </c>
       <c r="H236" s="4" t="s">
         <v>603</v>
@@ -14378,25 +14395,25 @@
     </row>
     <row r="237" spans="1:14" ht="43.5">
       <c r="A237" s="4" t="s">
-        <v>719</v>
+        <v>703</v>
       </c>
       <c r="B237" s="10" t="s">
-        <v>720</v>
+        <v>704</v>
       </c>
       <c r="C237" s="10" t="s">
-        <v>721</v>
+        <v>705</v>
       </c>
       <c r="D237" s="10" t="s">
-        <v>722</v>
+        <v>706</v>
       </c>
       <c r="E237" s="10" t="s">
-        <v>723</v>
+        <v>707</v>
       </c>
       <c r="F237" s="4" t="s">
         <v>601</v>
       </c>
       <c r="G237" s="4" t="s">
-        <v>1638</v>
+        <v>1619</v>
       </c>
       <c r="H237" s="4" t="s">
         <v>603</v>
@@ -14410,25 +14427,25 @@
     </row>
     <row r="238" spans="1:14" ht="43.5">
       <c r="A238" s="4" t="s">
-        <v>725</v>
+        <v>709</v>
       </c>
       <c r="B238" s="10" t="s">
-        <v>726</v>
+        <v>710</v>
       </c>
       <c r="C238" s="10" t="s">
-        <v>727</v>
+        <v>711</v>
       </c>
       <c r="D238" s="10" t="s">
-        <v>728</v>
+        <v>712</v>
       </c>
       <c r="E238" s="10" t="s">
-        <v>729</v>
+        <v>713</v>
       </c>
       <c r="F238" s="4" t="s">
         <v>601</v>
       </c>
       <c r="G238" s="4" t="s">
-        <v>1639</v>
+        <v>1620</v>
       </c>
       <c r="H238" s="4" t="s">
         <v>603</v>
@@ -14442,25 +14459,25 @@
     </row>
     <row r="239" spans="1:14" ht="43.5">
       <c r="A239" s="4" t="s">
-        <v>731</v>
+        <v>715</v>
       </c>
       <c r="B239" s="10" t="s">
-        <v>732</v>
+        <v>716</v>
       </c>
       <c r="C239" s="10" t="s">
-        <v>733</v>
+        <v>717</v>
       </c>
       <c r="D239" s="10" t="s">
-        <v>734</v>
+        <v>718</v>
       </c>
       <c r="E239" s="10" t="s">
-        <v>735</v>
+        <v>719</v>
       </c>
       <c r="F239" s="4" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="G239" s="4" t="s">
-        <v>1640</v>
+        <v>1621</v>
       </c>
       <c r="H239" s="4" t="s">
         <v>603</v>
@@ -14474,25 +14491,25 @@
     </row>
     <row r="240" spans="1:14" ht="43.5">
       <c r="A240" s="4" t="s">
-        <v>737</v>
+        <v>721</v>
       </c>
       <c r="B240" s="10" t="s">
-        <v>738</v>
+        <v>722</v>
       </c>
       <c r="C240" s="10" t="s">
-        <v>739</v>
+        <v>723</v>
       </c>
       <c r="D240" s="10" t="s">
-        <v>740</v>
+        <v>724</v>
       </c>
       <c r="E240" s="10" t="s">
-        <v>741</v>
+        <v>725</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="G240" s="4" t="s">
-        <v>1641</v>
+        <v>1622</v>
       </c>
       <c r="H240" s="4" t="s">
         <v>603</v>
@@ -14506,25 +14523,25 @@
     </row>
     <row r="241" spans="1:14" ht="43.5">
       <c r="A241" s="4" t="s">
-        <v>743</v>
+        <v>727</v>
       </c>
       <c r="B241" s="10" t="s">
-        <v>744</v>
+        <v>728</v>
       </c>
       <c r="C241" s="10" t="s">
-        <v>745</v>
+        <v>729</v>
       </c>
       <c r="D241" s="10" t="s">
-        <v>746</v>
+        <v>730</v>
       </c>
       <c r="E241" s="10" t="s">
-        <v>747</v>
+        <v>731</v>
       </c>
       <c r="F241" s="4" t="s">
-        <v>699</v>
+        <v>687</v>
       </c>
       <c r="G241" s="4" t="s">
-        <v>1642</v>
+        <v>1623</v>
       </c>
       <c r="H241" s="4" t="s">
         <v>603</v>
@@ -14538,25 +14555,25 @@
     </row>
     <row r="242" spans="1:14" ht="58">
       <c r="A242" s="4" t="s">
-        <v>749</v>
+        <v>733</v>
       </c>
       <c r="B242" s="10" t="s">
-        <v>750</v>
+        <v>734</v>
       </c>
       <c r="C242" s="10" t="s">
-        <v>751</v>
+        <v>735</v>
       </c>
       <c r="D242" s="10" t="s">
-        <v>752</v>
+        <v>736</v>
       </c>
       <c r="E242" s="10" t="s">
-        <v>753</v>
+        <v>737</v>
       </c>
       <c r="F242" s="4" t="s">
-        <v>754</v>
+        <v>738</v>
       </c>
       <c r="G242" s="4" t="s">
-        <v>1643</v>
+        <v>1624</v>
       </c>
       <c r="H242" s="4" t="s">
         <v>603</v>
@@ -14570,25 +14587,25 @@
     </row>
     <row r="243" spans="1:14" ht="58">
       <c r="A243" s="4" t="s">
-        <v>756</v>
+        <v>740</v>
       </c>
       <c r="B243" s="10" t="s">
-        <v>757</v>
+        <v>741</v>
       </c>
       <c r="C243" s="10" t="s">
-        <v>758</v>
+        <v>742</v>
       </c>
       <c r="D243" s="10" t="s">
-        <v>759</v>
+        <v>743</v>
       </c>
       <c r="E243" s="10" t="s">
-        <v>760</v>
+        <v>744</v>
       </c>
       <c r="F243" s="4" t="s">
         <v>672</v>
       </c>
       <c r="G243" s="4" t="s">
-        <v>1644</v>
+        <v>1625</v>
       </c>
       <c r="H243" s="4" t="s">
         <v>603</v>
@@ -14602,25 +14619,25 @@
     </row>
     <row r="244" spans="1:14" ht="43.5">
       <c r="A244" s="4" t="s">
-        <v>762</v>
+        <v>746</v>
       </c>
       <c r="B244" s="10" t="s">
-        <v>763</v>
+        <v>747</v>
       </c>
       <c r="C244" s="10" t="s">
-        <v>764</v>
+        <v>748</v>
       </c>
       <c r="D244" s="10" t="s">
-        <v>765</v>
+        <v>749</v>
       </c>
       <c r="E244" s="10" t="s">
-        <v>766</v>
+        <v>750</v>
       </c>
       <c r="F244" s="4" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="G244" s="4" t="s">
-        <v>1645</v>
+        <v>1626</v>
       </c>
       <c r="H244" s="4" t="s">
         <v>603</v>
@@ -14634,25 +14651,25 @@
     </row>
     <row r="245" spans="1:14" ht="58">
       <c r="A245" s="4" t="s">
-        <v>768</v>
+        <v>752</v>
       </c>
       <c r="B245" s="10" t="s">
-        <v>769</v>
+        <v>753</v>
       </c>
       <c r="C245" s="10" t="s">
-        <v>770</v>
+        <v>754</v>
       </c>
       <c r="D245" s="10" t="s">
-        <v>771</v>
+        <v>755</v>
       </c>
       <c r="E245" s="10" t="s">
-        <v>772</v>
+        <v>756</v>
       </c>
       <c r="F245" s="4" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="G245" s="4" t="s">
-        <v>1646</v>
+        <v>1627</v>
       </c>
       <c r="H245" s="4" t="s">
         <v>603</v>
@@ -14666,25 +14683,25 @@
     </row>
     <row r="246" spans="1:14" ht="43.5">
       <c r="A246" s="4" t="s">
-        <v>774</v>
+        <v>758</v>
       </c>
       <c r="B246" s="10" t="s">
-        <v>775</v>
+        <v>759</v>
       </c>
       <c r="C246" s="10" t="s">
-        <v>776</v>
+        <v>760</v>
       </c>
       <c r="D246" s="10" t="s">
-        <v>777</v>
+        <v>761</v>
       </c>
       <c r="E246" s="10" t="s">
-        <v>778</v>
+        <v>762</v>
       </c>
       <c r="F246" s="4" t="s">
         <v>634</v>
       </c>
       <c r="G246" s="4" t="s">
-        <v>1647</v>
+        <v>1628</v>
       </c>
       <c r="H246" s="4" t="s">
         <v>603</v>
@@ -14698,25 +14715,25 @@
     </row>
     <row r="247" spans="1:14" ht="43.5">
       <c r="A247" s="4" t="s">
-        <v>780</v>
+        <v>764</v>
       </c>
       <c r="B247" s="10" t="s">
-        <v>781</v>
+        <v>765</v>
       </c>
       <c r="C247" s="10" t="s">
-        <v>782</v>
+        <v>766</v>
       </c>
       <c r="D247" s="10" t="s">
-        <v>783</v>
+        <v>767</v>
       </c>
       <c r="E247" s="10" t="s">
-        <v>784</v>
+        <v>768</v>
       </c>
       <c r="F247" s="4" t="s">
-        <v>785</v>
+        <v>769</v>
       </c>
       <c r="G247" s="4" t="s">
-        <v>1648</v>
+        <v>1629</v>
       </c>
       <c r="H247" s="4" t="s">
         <v>603</v>
@@ -14730,25 +14747,25 @@
     </row>
     <row r="248" spans="1:14" ht="58">
       <c r="A248" s="4" t="s">
-        <v>787</v>
+        <v>771</v>
       </c>
       <c r="B248" s="10" t="s">
-        <v>788</v>
+        <v>772</v>
       </c>
       <c r="C248" s="10" t="s">
-        <v>789</v>
+        <v>773</v>
       </c>
       <c r="D248" s="10" t="s">
-        <v>790</v>
+        <v>774</v>
       </c>
       <c r="E248" s="10" t="s">
-        <v>791</v>
+        <v>775</v>
       </c>
       <c r="F248" s="4" t="s">
         <v>665</v>
       </c>
       <c r="G248" s="4" t="s">
-        <v>1649</v>
+        <v>1630</v>
       </c>
       <c r="H248" s="4" t="s">
         <v>603</v>
@@ -14762,25 +14779,25 @@
     </row>
     <row r="249" spans="1:14" ht="43.5">
       <c r="A249" s="4" t="s">
-        <v>793</v>
+        <v>777</v>
       </c>
       <c r="B249" s="10" t="s">
-        <v>794</v>
+        <v>778</v>
       </c>
       <c r="C249" s="10" t="s">
-        <v>795</v>
+        <v>779</v>
       </c>
       <c r="D249" s="10" t="s">
-        <v>796</v>
+        <v>780</v>
       </c>
       <c r="E249" s="10" t="s">
-        <v>797</v>
+        <v>781</v>
       </c>
       <c r="F249" s="4" t="s">
-        <v>798</v>
+        <v>782</v>
       </c>
       <c r="G249" s="4" t="s">
-        <v>1650</v>
+        <v>1631</v>
       </c>
       <c r="H249" s="4" t="s">
         <v>603</v>
@@ -14794,17 +14811,17 @@
     </row>
     <row r="250" spans="1:14" ht="29">
       <c r="A250" s="4" t="s">
-        <v>800</v>
+        <v>784</v>
       </c>
       <c r="B250" s="10"/>
       <c r="C250" s="10"/>
       <c r="D250" s="10"/>
       <c r="E250" s="10"/>
       <c r="F250" s="4" t="s">
-        <v>801</v>
+        <v>785</v>
       </c>
       <c r="G250" s="4" t="s">
-        <v>1651</v>
+        <v>1632</v>
       </c>
       <c r="H250" s="4" t="s">
         <v>603</v>
@@ -14818,17 +14835,17 @@
     </row>
     <row r="251" spans="1:14">
       <c r="A251" s="4" t="s">
-        <v>803</v>
+        <v>787</v>
       </c>
       <c r="B251" s="10"/>
       <c r="C251" s="10"/>
       <c r="D251" s="10"/>
       <c r="E251" s="10"/>
       <c r="F251" s="4" t="s">
-        <v>804</v>
+        <v>788</v>
       </c>
       <c r="G251" s="4" t="s">
-        <v>1652</v>
+        <v>1633</v>
       </c>
       <c r="H251" s="4" t="s">
         <v>603</v>
@@ -14842,17 +14859,17 @@
     </row>
     <row r="252" spans="1:14">
       <c r="A252" s="4" t="s">
-        <v>806</v>
+        <v>790</v>
       </c>
       <c r="B252" s="10"/>
       <c r="C252" s="10"/>
       <c r="D252" s="10"/>
       <c r="E252" s="10"/>
       <c r="F252" s="4" t="s">
-        <v>801</v>
+        <v>785</v>
       </c>
       <c r="G252" s="4" t="s">
-        <v>1653</v>
+        <v>1634</v>
       </c>
       <c r="H252" s="4" t="s">
         <v>603</v>
@@ -14866,17 +14883,17 @@
     </row>
     <row r="253" spans="1:14" ht="29">
       <c r="A253" s="4" t="s">
-        <v>808</v>
+        <v>792</v>
       </c>
       <c r="B253" s="10"/>
       <c r="C253" s="10"/>
       <c r="D253" s="10"/>
       <c r="E253" s="10"/>
       <c r="F253" s="4" t="s">
-        <v>804</v>
+        <v>788</v>
       </c>
       <c r="G253" s="4" t="s">
-        <v>1654</v>
+        <v>1635</v>
       </c>
       <c r="H253" s="4" t="s">
         <v>603</v>
@@ -14890,17 +14907,17 @@
     </row>
     <row r="254" spans="1:14">
       <c r="A254" s="4" t="s">
-        <v>810</v>
+        <v>794</v>
       </c>
       <c r="B254" s="10"/>
       <c r="C254" s="10"/>
       <c r="D254" s="10"/>
       <c r="E254" s="10"/>
       <c r="F254" s="4" t="s">
-        <v>801</v>
+        <v>785</v>
       </c>
       <c r="G254" s="4" t="s">
-        <v>1655</v>
+        <v>1636</v>
       </c>
       <c r="H254" s="4" t="s">
         <v>603</v>
@@ -14914,17 +14931,17 @@
     </row>
     <row r="255" spans="1:14">
       <c r="A255" s="4" t="s">
-        <v>812</v>
+        <v>796</v>
       </c>
       <c r="B255" s="10"/>
       <c r="C255" s="10"/>
       <c r="D255" s="10"/>
       <c r="E255" s="10"/>
       <c r="F255" s="4" t="s">
-        <v>801</v>
+        <v>785</v>
       </c>
       <c r="G255" s="4" t="s">
-        <v>1656</v>
+        <v>1637</v>
       </c>
       <c r="H255" s="4" t="s">
         <v>603</v>
@@ -14938,17 +14955,17 @@
     </row>
     <row r="256" spans="1:14" ht="29">
       <c r="A256" s="4" t="s">
-        <v>814</v>
+        <v>798</v>
       </c>
       <c r="B256" s="10"/>
       <c r="C256" s="10"/>
       <c r="D256" s="10"/>
       <c r="E256" s="10"/>
       <c r="F256" s="4" t="s">
-        <v>801</v>
+        <v>785</v>
       </c>
       <c r="G256" s="4" t="s">
-        <v>1657</v>
+        <v>1638</v>
       </c>
       <c r="H256" s="4" t="s">
         <v>603</v>
@@ -14962,17 +14979,17 @@
     </row>
     <row r="257" spans="1:14" ht="29">
       <c r="A257" s="4" t="s">
-        <v>816</v>
+        <v>800</v>
       </c>
       <c r="B257" s="10"/>
       <c r="C257" s="10"/>
       <c r="D257" s="10"/>
       <c r="E257" s="10"/>
       <c r="F257" s="4" t="s">
-        <v>801</v>
+        <v>785</v>
       </c>
       <c r="G257" s="4" t="s">
-        <v>1658</v>
+        <v>1639</v>
       </c>
       <c r="H257" s="4" t="s">
         <v>603</v>
@@ -14986,20 +15003,20 @@
     </row>
     <row r="258" spans="1:14" ht="29">
       <c r="A258" s="4" t="s">
-        <v>818</v>
+        <v>802</v>
       </c>
       <c r="B258" s="10"/>
       <c r="C258" s="10"/>
       <c r="D258" s="10"/>
       <c r="E258" s="10"/>
       <c r="F258" s="4" t="s">
-        <v>819</v>
+        <v>803</v>
       </c>
       <c r="G258" s="4" t="s">
-        <v>1659</v>
+        <v>1640</v>
       </c>
       <c r="H258" s="4" t="s">
-        <v>821</v>
+        <v>805</v>
       </c>
       <c r="I258" s="4"/>
       <c r="J258" s="4"/>
@@ -15010,20 +15027,20 @@
     </row>
     <row r="259" spans="1:14">
       <c r="A259" s="4" t="s">
-        <v>822</v>
+        <v>806</v>
       </c>
       <c r="B259" s="10"/>
       <c r="C259" s="10"/>
       <c r="D259" s="10"/>
       <c r="E259" s="10"/>
       <c r="F259" s="4" t="s">
-        <v>823</v>
+        <v>807</v>
       </c>
       <c r="G259" s="4" t="s">
-        <v>1660</v>
+        <v>1641</v>
       </c>
       <c r="H259" s="4" t="s">
-        <v>821</v>
+        <v>805</v>
       </c>
       <c r="I259" s="4"/>
       <c r="J259" s="4"/>
@@ -15034,20 +15051,20 @@
     </row>
     <row r="260" spans="1:14" ht="29">
       <c r="A260" s="4" t="s">
-        <v>825</v>
+        <v>809</v>
       </c>
       <c r="B260" s="10"/>
       <c r="C260" s="10"/>
       <c r="D260" s="10"/>
       <c r="E260" s="10"/>
       <c r="F260" s="4" t="s">
-        <v>826</v>
+        <v>810</v>
       </c>
       <c r="G260" s="4" t="s">
-        <v>1661</v>
+        <v>1642</v>
       </c>
       <c r="H260" s="4" t="s">
-        <v>821</v>
+        <v>805</v>
       </c>
       <c r="I260" s="4"/>
       <c r="J260" s="4"/>
@@ -15058,20 +15075,20 @@
     </row>
     <row r="261" spans="1:14">
       <c r="A261" s="4" t="s">
-        <v>828</v>
+        <v>812</v>
       </c>
       <c r="B261" s="10"/>
       <c r="C261" s="10"/>
       <c r="D261" s="10"/>
       <c r="E261" s="10"/>
       <c r="F261" s="4" t="s">
-        <v>829</v>
+        <v>813</v>
       </c>
       <c r="G261" s="4" t="s">
-        <v>1662</v>
+        <v>1643</v>
       </c>
       <c r="H261" s="4" t="s">
-        <v>821</v>
+        <v>805</v>
       </c>
       <c r="I261" s="4"/>
       <c r="J261" s="4"/>
@@ -15082,20 +15099,20 @@
     </row>
     <row r="262" spans="1:14">
       <c r="A262" s="4" t="s">
-        <v>831</v>
+        <v>815</v>
       </c>
       <c r="B262" s="10"/>
       <c r="C262" s="10"/>
       <c r="D262" s="10"/>
       <c r="E262" s="10"/>
       <c r="F262" s="4" t="s">
-        <v>832</v>
+        <v>816</v>
       </c>
       <c r="G262" s="4" t="s">
-        <v>1663</v>
+        <v>1644</v>
       </c>
       <c r="H262" s="4" t="s">
-        <v>821</v>
+        <v>805</v>
       </c>
       <c r="I262" s="4"/>
       <c r="J262" s="4"/>
@@ -15106,20 +15123,20 @@
     </row>
     <row r="263" spans="1:14">
       <c r="A263" s="4" t="s">
-        <v>834</v>
+        <v>818</v>
       </c>
       <c r="B263" s="10"/>
       <c r="C263" s="10"/>
       <c r="D263" s="10"/>
       <c r="E263" s="10"/>
       <c r="F263" s="4" t="s">
-        <v>835</v>
+        <v>819</v>
       </c>
       <c r="G263" s="4" t="s">
-        <v>1664</v>
+        <v>1645</v>
       </c>
       <c r="H263" s="4" t="s">
-        <v>821</v>
+        <v>805</v>
       </c>
       <c r="I263" s="4"/>
       <c r="J263" s="4"/>
@@ -15130,20 +15147,20 @@
     </row>
     <row r="264" spans="1:14" ht="29">
       <c r="A264" s="4" t="s">
-        <v>837</v>
+        <v>821</v>
       </c>
       <c r="B264" s="10"/>
       <c r="C264" s="10"/>
       <c r="D264" s="10"/>
       <c r="E264" s="10"/>
       <c r="F264" s="4" t="s">
-        <v>838</v>
+        <v>822</v>
       </c>
       <c r="G264" s="4" t="s">
-        <v>1665</v>
+        <v>1646</v>
       </c>
       <c r="H264" s="4" t="s">
-        <v>821</v>
+        <v>805</v>
       </c>
       <c r="I264" s="4"/>
       <c r="J264" s="4"/>
@@ -15154,20 +15171,20 @@
     </row>
     <row r="265" spans="1:14">
       <c r="A265" s="4" t="s">
-        <v>840</v>
+        <v>824</v>
       </c>
       <c r="B265" s="10"/>
       <c r="C265" s="10"/>
       <c r="D265" s="10"/>
       <c r="E265" s="10"/>
       <c r="F265" s="4" t="s">
-        <v>841</v>
+        <v>825</v>
       </c>
       <c r="G265" s="4" t="s">
-        <v>1666</v>
+        <v>1647</v>
       </c>
       <c r="H265" s="4" t="s">
-        <v>821</v>
+        <v>805</v>
       </c>
       <c r="I265" s="4"/>
       <c r="J265" s="4"/>
@@ -15178,20 +15195,20 @@
     </row>
     <row r="266" spans="1:14">
       <c r="A266" s="4" t="s">
-        <v>843</v>
+        <v>827</v>
       </c>
       <c r="B266" s="10"/>
       <c r="C266" s="10"/>
       <c r="D266" s="10"/>
       <c r="E266" s="10"/>
       <c r="F266" s="4" t="s">
-        <v>844</v>
+        <v>828</v>
       </c>
       <c r="G266" s="4" t="s">
-        <v>1667</v>
+        <v>1648</v>
       </c>
       <c r="H266" s="4" t="s">
-        <v>821</v>
+        <v>805</v>
       </c>
       <c r="I266" s="4"/>
       <c r="J266" s="4"/>
@@ -15202,20 +15219,20 @@
     </row>
     <row r="267" spans="1:14">
       <c r="A267" s="4" t="s">
-        <v>846</v>
+        <v>830</v>
       </c>
       <c r="B267" s="10"/>
       <c r="C267" s="10"/>
       <c r="D267" s="10"/>
       <c r="E267" s="10"/>
       <c r="F267" s="4" t="s">
-        <v>847</v>
+        <v>831</v>
       </c>
       <c r="G267" s="4" t="s">
-        <v>1668</v>
+        <v>1649</v>
       </c>
       <c r="H267" s="4" t="s">
-        <v>821</v>
+        <v>805</v>
       </c>
       <c r="I267" s="4"/>
       <c r="J267" s="4"/>
@@ -15226,20 +15243,20 @@
     </row>
     <row r="268" spans="1:14" ht="29">
       <c r="A268" s="4" t="s">
-        <v>849</v>
+        <v>833</v>
       </c>
       <c r="B268" s="10"/>
       <c r="C268" s="10"/>
       <c r="D268" s="10"/>
       <c r="E268" s="10"/>
       <c r="F268" s="4" t="s">
-        <v>850</v>
+        <v>834</v>
       </c>
       <c r="G268" s="4" t="s">
-        <v>1669</v>
+        <v>1650</v>
       </c>
       <c r="H268" s="4" t="s">
-        <v>821</v>
+        <v>805</v>
       </c>
       <c r="I268" s="4"/>
       <c r="J268" s="4"/>
@@ -15250,20 +15267,20 @@
     </row>
     <row r="269" spans="1:14">
       <c r="A269" s="4" t="s">
-        <v>852</v>
+        <v>836</v>
       </c>
       <c r="B269" s="10"/>
       <c r="C269" s="10"/>
       <c r="D269" s="10"/>
       <c r="E269" s="10"/>
       <c r="F269" s="4" t="s">
-        <v>853</v>
+        <v>837</v>
       </c>
       <c r="G269" s="4" t="s">
-        <v>1670</v>
+        <v>1651</v>
       </c>
       <c r="H269" s="4" t="s">
-        <v>821</v>
+        <v>805</v>
       </c>
       <c r="I269" s="4"/>
       <c r="J269" s="4"/>
@@ -15274,20 +15291,20 @@
     </row>
     <row r="270" spans="1:14">
       <c r="A270" s="4" t="s">
-        <v>855</v>
+        <v>839</v>
       </c>
       <c r="B270" s="10"/>
       <c r="C270" s="10"/>
       <c r="D270" s="10"/>
       <c r="E270" s="10"/>
       <c r="F270" s="4" t="s">
-        <v>856</v>
+        <v>840</v>
       </c>
       <c r="G270" s="4" t="s">
-        <v>1671</v>
+        <v>1652</v>
       </c>
       <c r="H270" s="4" t="s">
-        <v>821</v>
+        <v>805</v>
       </c>
       <c r="I270" s="4"/>
       <c r="J270" s="4"/>
@@ -15298,20 +15315,20 @@
     </row>
     <row r="271" spans="1:14">
       <c r="A271" s="4" t="s">
-        <v>858</v>
+        <v>842</v>
       </c>
       <c r="B271" s="10"/>
       <c r="C271" s="10"/>
       <c r="D271" s="10"/>
       <c r="E271" s="10"/>
       <c r="F271" s="4" t="s">
-        <v>859</v>
+        <v>843</v>
       </c>
       <c r="G271" s="4" t="s">
-        <v>1672</v>
+        <v>1653</v>
       </c>
       <c r="H271" s="4" t="s">
-        <v>821</v>
+        <v>805</v>
       </c>
       <c r="I271" s="4"/>
       <c r="J271" s="4"/>
@@ -15322,20 +15339,20 @@
     </row>
     <row r="272" spans="1:14">
       <c r="A272" s="4" t="s">
-        <v>861</v>
+        <v>845</v>
       </c>
       <c r="B272" s="10"/>
       <c r="C272" s="10"/>
       <c r="D272" s="10"/>
       <c r="E272" s="10"/>
       <c r="F272" s="4" t="s">
-        <v>862</v>
+        <v>846</v>
       </c>
       <c r="G272" s="4" t="s">
-        <v>1673</v>
+        <v>1654</v>
       </c>
       <c r="H272" s="4" t="s">
-        <v>821</v>
+        <v>805</v>
       </c>
       <c r="I272" s="4"/>
       <c r="J272" s="4"/>
@@ -15346,20 +15363,20 @@
     </row>
     <row r="273" spans="1:14">
       <c r="A273" s="4" t="s">
-        <v>864</v>
+        <v>848</v>
       </c>
       <c r="B273" s="10"/>
       <c r="C273" s="10"/>
       <c r="D273" s="10"/>
       <c r="E273" s="10"/>
       <c r="F273" s="4" t="s">
-        <v>865</v>
+        <v>849</v>
       </c>
       <c r="G273" s="4" t="s">
-        <v>1674</v>
+        <v>1655</v>
       </c>
       <c r="H273" s="4" t="s">
-        <v>821</v>
+        <v>805</v>
       </c>
       <c r="I273" s="4"/>
       <c r="J273" s="4"/>
@@ -15370,20 +15387,20 @@
     </row>
     <row r="274" spans="1:14">
       <c r="A274" s="4" t="s">
-        <v>867</v>
+        <v>851</v>
       </c>
       <c r="B274" s="10"/>
       <c r="C274" s="10"/>
       <c r="D274" s="10"/>
       <c r="E274" s="10"/>
       <c r="F274" s="4" t="s">
-        <v>868</v>
+        <v>852</v>
       </c>
       <c r="G274" s="4" t="s">
-        <v>1675</v>
+        <v>1656</v>
       </c>
       <c r="H274" s="4" t="s">
-        <v>821</v>
+        <v>805</v>
       </c>
       <c r="I274" s="4"/>
       <c r="J274" s="4"/>
@@ -15394,20 +15411,20 @@
     </row>
     <row r="275" spans="1:14">
       <c r="A275" s="4" t="s">
-        <v>870</v>
+        <v>854</v>
       </c>
       <c r="B275" s="10"/>
       <c r="C275" s="10"/>
       <c r="D275" s="10"/>
       <c r="E275" s="10"/>
       <c r="F275" s="4" t="s">
-        <v>868</v>
+        <v>852</v>
       </c>
       <c r="G275" s="4" t="s">
-        <v>1676</v>
+        <v>1657</v>
       </c>
       <c r="H275" s="4" t="s">
-        <v>821</v>
+        <v>805</v>
       </c>
       <c r="I275" s="4"/>
       <c r="J275" s="4"/>
@@ -15418,20 +15435,20 @@
     </row>
     <row r="276" spans="1:14">
       <c r="A276" s="4" t="s">
-        <v>872</v>
+        <v>856</v>
       </c>
       <c r="B276" s="10"/>
       <c r="C276" s="10"/>
       <c r="D276" s="10"/>
       <c r="E276" s="10"/>
       <c r="F276" s="4" t="s">
-        <v>873</v>
+        <v>857</v>
       </c>
       <c r="G276" s="4" t="s">
-        <v>1677</v>
+        <v>1658</v>
       </c>
       <c r="H276" s="4" t="s">
-        <v>821</v>
+        <v>805</v>
       </c>
       <c r="I276" s="4"/>
       <c r="J276" s="4"/>
@@ -15442,20 +15459,20 @@
     </row>
     <row r="277" spans="1:14" ht="29">
       <c r="A277" s="4" t="s">
-        <v>875</v>
+        <v>859</v>
       </c>
       <c r="B277" s="10"/>
       <c r="C277" s="10"/>
       <c r="D277" s="10"/>
       <c r="E277" s="10"/>
       <c r="F277" s="4" t="s">
-        <v>876</v>
+        <v>860</v>
       </c>
       <c r="G277" s="4" t="s">
-        <v>1678</v>
+        <v>1659</v>
       </c>
       <c r="H277" s="4" t="s">
-        <v>821</v>
+        <v>805</v>
       </c>
       <c r="I277" s="4"/>
       <c r="J277" s="4"/>
@@ -15466,20 +15483,20 @@
     </row>
     <row r="278" spans="1:14" ht="29">
       <c r="A278" s="4" t="s">
-        <v>878</v>
+        <v>862</v>
       </c>
       <c r="B278" s="10"/>
       <c r="C278" s="10"/>
       <c r="D278" s="10"/>
       <c r="E278" s="10"/>
       <c r="F278" s="4" t="s">
-        <v>879</v>
+        <v>863</v>
       </c>
       <c r="G278" s="4" t="s">
-        <v>1679</v>
+        <v>1660</v>
       </c>
       <c r="H278" s="4" t="s">
-        <v>821</v>
+        <v>805</v>
       </c>
       <c r="I278" s="4"/>
       <c r="J278" s="4"/>
@@ -15490,20 +15507,20 @@
     </row>
     <row r="279" spans="1:14" ht="29">
       <c r="A279" s="4" t="s">
-        <v>1681</v>
+        <v>1662</v>
       </c>
       <c r="B279" s="10"/>
       <c r="C279" s="10"/>
       <c r="D279" s="10"/>
       <c r="E279" s="10"/>
       <c r="F279" s="4" t="s">
-        <v>881</v>
+        <v>865</v>
       </c>
       <c r="G279" s="4" t="s">
-        <v>1680</v>
+        <v>1661</v>
       </c>
       <c r="H279" s="4" t="s">
-        <v>821</v>
+        <v>805</v>
       </c>
       <c r="I279" s="4"/>
       <c r="J279" s="4"/>
@@ -15529,7 +15546,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15.5">
       <c r="A1" s="5" t="s">
-        <v>883</v>
+        <v>867</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="15.5">
@@ -15537,17 +15554,17 @@
     </row>
     <row r="3" spans="1:1" ht="15.5">
       <c r="A3" s="6" t="s">
-        <v>884</v>
+        <v>868</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="15.5">
       <c r="A4" s="6" t="s">
-        <v>885</v>
+        <v>869</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="15.5">
       <c r="A5" s="6" t="s">
-        <v>886</v>
+        <v>870</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="15.5">
@@ -15555,17 +15572,17 @@
     </row>
     <row r="7" spans="1:1" ht="15.5">
       <c r="A7" s="6" t="s">
-        <v>887</v>
+        <v>871</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="15.5">
       <c r="A8" s="6" t="s">
-        <v>888</v>
+        <v>872</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="15.5">
       <c r="A9" s="6" t="s">
-        <v>889</v>
+        <v>873</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="15.5">
@@ -15573,17 +15590,17 @@
     </row>
     <row r="11" spans="1:1" ht="15.5">
       <c r="A11" s="6" t="s">
-        <v>890</v>
+        <v>874</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="15.5">
       <c r="A12" s="6" t="s">
-        <v>891</v>
+        <v>875</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="15.5">
       <c r="A13" s="6" t="s">
-        <v>892</v>
+        <v>876</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="15.5">
@@ -15591,17 +15608,17 @@
     </row>
     <row r="15" spans="1:1" ht="15.5">
       <c r="A15" s="6" t="s">
-        <v>893</v>
+        <v>877</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="15.5">
       <c r="A16" s="6" t="s">
-        <v>894</v>
+        <v>878</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15.5">
       <c r="A17" s="6" t="s">
-        <v>895</v>
+        <v>879</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15.5">
@@ -15609,12 +15626,12 @@
     </row>
     <row r="19" spans="1:1" ht="15.5">
       <c r="A19" s="6" t="s">
-        <v>896</v>
+        <v>880</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15.5">
       <c r="A20" s="6" t="s">
-        <v>897</v>
+        <v>881</v>
       </c>
     </row>
   </sheetData>

--- a/data/ontap111.xlsx
+++ b/data/ontap111.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tdtam\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3B61778-BF0B-4AFF-9847-D97D34815A1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1451647-6ABB-4C42-BD1F-8BA3F684DDC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HOCSINH" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,14 @@
     <sheet name="HUONGDAN" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CAUHOI!$A$1:$N$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CAUHOI!$A$1:$N$138</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1311" uniqueCount="895">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1327" uniqueCount="909">
   <si>
     <t>ID</t>
   </si>
@@ -2442,57 +2442,27 @@
     <t>Q109</t>
   </si>
   <si>
-    <t>Hệ điều hành là phần mềm hệ thống quản lý tài nguyên máy tính.</t>
-  </si>
-  <si>
-    <t>Đúng</t>
-  </si>
-  <si>
     <t>Q110</t>
   </si>
   <si>
-    <t>RAM lưu dữ liệu vĩnh viễn kể cả khi tắt máy.</t>
-  </si>
-  <si>
-    <t>Sai</t>
-  </si>
-  <si>
     <t>Q111</t>
   </si>
   <si>
-    <t>SSD thường nhanh hơn HDD.</t>
-  </si>
-  <si>
     <t>Q112</t>
   </si>
   <si>
-    <t>Phần mềm nguồn mở luôn miễn phí và không có bản quyền.</t>
-  </si>
-  <si>
     <t>Q113</t>
   </si>
   <si>
-    <t>Trong phép cộng trong hệ nhị phân: 1+1=10</t>
-  </si>
-  <si>
     <t>Q114</t>
   </si>
   <si>
-    <t>Trong phép cộng trong hệ nhị phân: 1+1+1=11</t>
-  </si>
-  <si>
     <t>Q115</t>
   </si>
   <si>
-    <t>Kết quả của phép cộng trong hệ nhị phân: 101 + 010 là 111</t>
-  </si>
-  <si>
     <t>Q116</t>
   </si>
   <si>
-    <t>Khi cộng hai số nhị phân, nếu tổng tại một cột bằng 2 hoặc 3 thì phải nhớ 1 sang cột bên trái.</t>
-  </si>
-  <si>
     <t>Q117</t>
   </si>
   <si>
@@ -2682,18 +2652,12 @@
     <t>110110</t>
   </si>
   <si>
-    <t>Q138</t>
-  </si>
-  <si>
     <t>Giá trị của số 111010 là bao nhiêu sang hệ thập phân:?</t>
   </si>
   <si>
     <t>58</t>
   </si>
   <si>
-    <t>Q139</t>
-  </si>
-  <si>
     <t>HƯỚNG DẪN — ontap111.xlsx</t>
   </si>
   <si>
@@ -2710,13 +2674,91 @@
   </si>
   <si>
     <t>3. Media: dán URL (GitHub raw / YouTube), không Insert Picture trong Excel.</t>
+  </si>
+  <si>
+    <t>Thiết bị nào sau đây không nằm trong bảng mạch chính của máy tính?</t>
+  </si>
+  <si>
+    <t>Bộ xử lý trung tâm (CPU)</t>
+  </si>
+  <si>
+    <t>Bộ nhớ trong (RAM, ROM)</t>
+  </si>
+  <si>
+    <t>Bộ nhớ ngoài (đĩa cứng, SSD)</t>
+  </si>
+  <si>
+    <t>Cổng giao tiếp USB</t>
+  </si>
+  <si>
+    <t>ĐĐSĐ</t>
+  </si>
+  <si>
+    <t>Phát biểu nào sau đây về CPU là đúng?</t>
+  </si>
+  <si>
+    <t>CPU chỉ có một đơn vị xử lý</t>
+  </si>
+  <si>
+    <t>CPU có thể thực hiện song song nhiều công việc nhờ có nhiều lõi xử lý</t>
+  </si>
+  <si>
+    <t>CPU không thể đồng bộ các hoạt động trong máy tính</t>
+  </si>
+  <si>
+    <t>CPU chỉ thực hiện các phép toán lôgic mà không thực hiện phép toán số học</t>
+  </si>
+  <si>
+    <t>Thiết bị nào sau đây là thiết bị vào thông dụng nhất khi kết nối với máy tính?</t>
+  </si>
+  <si>
+    <t>Cổng nào sau đây được sử dụng để kết nối máy tính với màn hình và truyền đồng thời âm thanh và hình ảnh?</t>
+  </si>
+  <si>
+    <t>Cổng VGA</t>
+  </si>
+  <si>
+    <t>Cổng USB</t>
+  </si>
+  <si>
+    <t>Cổng mạng</t>
+  </si>
+  <si>
+    <t>Dịch vụ lưu trữ và chia sẻ tệp tin trực tuyến thường được gọi là gì?</t>
+  </si>
+  <si>
+    <t>Lưu trữ cục bộ</t>
+  </si>
+  <si>
+    <t>Lưu trữ đám mây</t>
+  </si>
+  <si>
+    <t>Lưu trữ mạng nội bộ</t>
+  </si>
+  <si>
+    <t>Lưu trữ vật lý</t>
+  </si>
+  <si>
+    <t>Một trong những ưu điểm của việc lưu trữ tệp tin trực tuyến là gì?</t>
+  </si>
+  <si>
+    <t>Dữ liệu chỉ có thể được truy cập từ một thiết bị duy nhất</t>
+  </si>
+  <si>
+    <t>Có thể chia sẻ tệp tin với nhiều người dùng và thiết lập quyền truy cập khác nhau.</t>
+  </si>
+  <si>
+    <t>Không cần kết nối Internet để truy cập dữ liệu.</t>
+  </si>
+  <si>
+    <t>Không thể quản lý và tổ chức dữ liệu hiệu quả.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2742,6 +2784,17 @@
     <font>
       <sz val="12"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -2784,7 +2837,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2801,6 +2854,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4889,7 +4945,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N140"/>
+  <dimension ref="A1:N138"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -8435,17 +8491,25 @@
     </row>
     <row r="111" spans="1:14" ht="29">
       <c r="A111" s="5" t="s">
+        <v>883</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>885</v>
+      </c>
+      <c r="D111" s="5" t="s">
+        <v>886</v>
+      </c>
+      <c r="E111" s="5" t="s">
+        <v>887</v>
+      </c>
+      <c r="F111" s="8" t="s">
+        <v>888</v>
+      </c>
+      <c r="G111" s="5" t="s">
         <v>805</v>
-      </c>
-      <c r="B111" s="5"/>
-      <c r="C111" s="5"/>
-      <c r="D111" s="5"/>
-      <c r="E111" s="5"/>
-      <c r="F111" s="5" t="s">
-        <v>806</v>
-      </c>
-      <c r="G111" s="5" t="s">
-        <v>807</v>
       </c>
       <c r="H111" s="5" t="s">
         <v>608</v>
@@ -8457,19 +8521,27 @@
       <c r="M111" s="5"/>
       <c r="N111" s="5"/>
     </row>
-    <row r="112" spans="1:14">
+    <row r="112" spans="1:14" ht="29">
       <c r="A112" s="5" t="s">
-        <v>808</v>
-      </c>
-      <c r="B112" s="5"/>
-      <c r="C112" s="5"/>
-      <c r="D112" s="5"/>
-      <c r="E112" s="5"/>
-      <c r="F112" s="5" t="s">
-        <v>809</v>
+        <v>894</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>528</v>
+      </c>
+      <c r="E112" s="5" t="s">
+        <v>561</v>
+      </c>
+      <c r="F112" s="8" t="s">
+        <v>606</v>
       </c>
       <c r="G112" s="5" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="H112" s="5" t="s">
         <v>608</v>
@@ -8481,19 +8553,27 @@
       <c r="M112" s="5"/>
       <c r="N112" s="5"/>
     </row>
-    <row r="113" spans="1:14">
+    <row r="113" spans="1:14" ht="29">
       <c r="A113" s="5" t="s">
-        <v>811</v>
-      </c>
-      <c r="B113" s="5"/>
-      <c r="C113" s="5"/>
-      <c r="D113" s="5"/>
-      <c r="E113" s="5"/>
+        <v>899</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>900</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>901</v>
+      </c>
+      <c r="D113" s="5" t="s">
+        <v>902</v>
+      </c>
+      <c r="E113" s="5" t="s">
+        <v>903</v>
+      </c>
       <c r="F113" s="5" t="s">
-        <v>806</v>
+        <v>697</v>
       </c>
       <c r="G113" s="5" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="H113" s="5" t="s">
         <v>608</v>
@@ -8505,19 +8585,27 @@
       <c r="M113" s="5"/>
       <c r="N113" s="5"/>
     </row>
-    <row r="114" spans="1:14" ht="29">
+    <row r="114" spans="1:14" ht="43.5">
       <c r="A114" s="5" t="s">
-        <v>813</v>
-      </c>
-      <c r="B114" s="5"/>
-      <c r="C114" s="5"/>
-      <c r="D114" s="5"/>
-      <c r="E114" s="5"/>
+        <v>889</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>890</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>891</v>
+      </c>
+      <c r="D114" s="5" t="s">
+        <v>892</v>
+      </c>
+      <c r="E114" s="5" t="s">
+        <v>893</v>
+      </c>
       <c r="F114" s="5" t="s">
-        <v>809</v>
+        <v>697</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>814</v>
+        <v>808</v>
       </c>
       <c r="H114" s="5" t="s">
         <v>608</v>
@@ -8529,19 +8617,27 @@
       <c r="M114" s="5"/>
       <c r="N114" s="5"/>
     </row>
-    <row r="115" spans="1:14">
+    <row r="115" spans="1:14" ht="43.5">
       <c r="A115" s="5" t="s">
-        <v>815</v>
-      </c>
-      <c r="B115" s="5"/>
-      <c r="C115" s="5"/>
-      <c r="D115" s="5"/>
-      <c r="E115" s="5"/>
+        <v>895</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>896</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="D115" s="5" t="s">
+        <v>897</v>
+      </c>
+      <c r="E115" s="5" t="s">
+        <v>898</v>
+      </c>
       <c r="F115" s="5" t="s">
-        <v>806</v>
+        <v>697</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>816</v>
+        <v>809</v>
       </c>
       <c r="H115" s="5" t="s">
         <v>608</v>
@@ -8553,19 +8649,27 @@
       <c r="M115" s="5"/>
       <c r="N115" s="5"/>
     </row>
-    <row r="116" spans="1:14">
+    <row r="116" spans="1:14" ht="58">
       <c r="A116" s="5" t="s">
-        <v>817</v>
-      </c>
-      <c r="B116" s="5"/>
-      <c r="C116" s="5"/>
-      <c r="D116" s="5"/>
-      <c r="E116" s="5"/>
+        <v>904</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>905</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="D116" s="5" t="s">
+        <v>907</v>
+      </c>
+      <c r="E116" s="5" t="s">
+        <v>908</v>
+      </c>
       <c r="F116" s="5" t="s">
-        <v>806</v>
+        <v>697</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>818</v>
+        <v>810</v>
       </c>
       <c r="H116" s="5" t="s">
         <v>608</v>
@@ -8579,20 +8683,20 @@
     </row>
     <row r="117" spans="1:14" ht="29">
       <c r="A117" s="5" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="B117" s="5"/>
       <c r="C117" s="5"/>
       <c r="D117" s="5"/>
       <c r="E117" s="5"/>
       <c r="F117" s="5" t="s">
-        <v>806</v>
+        <v>814</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="H117" s="5" t="s">
-        <v>608</v>
+        <v>816</v>
       </c>
       <c r="I117" s="5"/>
       <c r="J117" s="5"/>
@@ -8601,22 +8705,22 @@
       <c r="M117" s="5"/>
       <c r="N117" s="5"/>
     </row>
-    <row r="118" spans="1:14" ht="29">
+    <row r="118" spans="1:14">
       <c r="A118" s="5" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="B118" s="5"/>
       <c r="C118" s="5"/>
       <c r="D118" s="5"/>
       <c r="E118" s="5"/>
       <c r="F118" s="5" t="s">
-        <v>806</v>
+        <v>818</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>822</v>
+        <v>812</v>
       </c>
       <c r="H118" s="5" t="s">
-        <v>608</v>
+        <v>816</v>
       </c>
       <c r="I118" s="5"/>
       <c r="J118" s="5"/>
@@ -8627,20 +8731,20 @@
     </row>
     <row r="119" spans="1:14" ht="29">
       <c r="A119" s="5" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="B119" s="5"/>
       <c r="C119" s="5"/>
       <c r="D119" s="5"/>
       <c r="E119" s="5"/>
       <c r="F119" s="5" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>825</v>
+        <v>815</v>
       </c>
       <c r="H119" s="5" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
       <c r="I119" s="5"/>
       <c r="J119" s="5"/>
@@ -8651,20 +8755,20 @@
     </row>
     <row r="120" spans="1:14">
       <c r="A120" s="5" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="B120" s="5"/>
       <c r="C120" s="5"/>
       <c r="D120" s="5"/>
       <c r="E120" s="5"/>
       <c r="F120" s="5" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>829</v>
+        <v>819</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
       <c r="I120" s="5"/>
       <c r="J120" s="5"/>
@@ -8673,22 +8777,22 @@
       <c r="M120" s="5"/>
       <c r="N120" s="5"/>
     </row>
-    <row r="121" spans="1:14" ht="29">
+    <row r="121" spans="1:14">
       <c r="A121" s="5" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="B121" s="5"/>
       <c r="C121" s="5"/>
       <c r="D121" s="5"/>
       <c r="E121" s="5"/>
       <c r="F121" s="5" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="G121" s="5" t="s">
-        <v>832</v>
+        <v>822</v>
       </c>
       <c r="H121" s="5" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
       <c r="I121" s="5"/>
       <c r="J121" s="5"/>
@@ -8699,20 +8803,20 @@
     </row>
     <row r="122" spans="1:14">
       <c r="A122" s="5" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="B122" s="5"/>
       <c r="C122" s="5"/>
       <c r="D122" s="5"/>
       <c r="E122" s="5"/>
       <c r="F122" s="5" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="G122" s="5" t="s">
-        <v>835</v>
+        <v>825</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
       <c r="I122" s="5"/>
       <c r="J122" s="5"/>
@@ -8721,22 +8825,22 @@
       <c r="M122" s="5"/>
       <c r="N122" s="5"/>
     </row>
-    <row r="123" spans="1:14">
+    <row r="123" spans="1:14" ht="29">
       <c r="A123" s="5" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="B123" s="5"/>
       <c r="C123" s="5"/>
       <c r="D123" s="5"/>
       <c r="E123" s="5"/>
       <c r="F123" s="5" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>838</v>
+        <v>828</v>
       </c>
       <c r="H123" s="5" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
       <c r="I123" s="5"/>
       <c r="J123" s="5"/>
@@ -8747,20 +8851,20 @@
     </row>
     <row r="124" spans="1:14">
       <c r="A124" s="5" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="B124" s="5"/>
       <c r="C124" s="5"/>
       <c r="D124" s="5"/>
       <c r="E124" s="5"/>
       <c r="F124" s="5" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>841</v>
+        <v>831</v>
       </c>
       <c r="H124" s="5" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
       <c r="I124" s="5"/>
       <c r="J124" s="5"/>
@@ -8769,22 +8873,22 @@
       <c r="M124" s="5"/>
       <c r="N124" s="5"/>
     </row>
-    <row r="125" spans="1:14" ht="29">
+    <row r="125" spans="1:14">
       <c r="A125" s="5" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="B125" s="5"/>
       <c r="C125" s="5"/>
       <c r="D125" s="5"/>
       <c r="E125" s="5"/>
       <c r="F125" s="5" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>844</v>
+        <v>834</v>
       </c>
       <c r="H125" s="5" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
       <c r="I125" s="5"/>
       <c r="J125" s="5"/>
@@ -8795,20 +8899,20 @@
     </row>
     <row r="126" spans="1:14">
       <c r="A126" s="5" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
       <c r="D126" s="5"/>
       <c r="E126" s="5"/>
       <c r="F126" s="5" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="G126" s="5" t="s">
-        <v>847</v>
+        <v>837</v>
       </c>
       <c r="H126" s="5" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
       <c r="I126" s="5"/>
       <c r="J126" s="5"/>
@@ -8817,22 +8921,22 @@
       <c r="M126" s="5"/>
       <c r="N126" s="5"/>
     </row>
-    <row r="127" spans="1:14">
+    <row r="127" spans="1:14" ht="29">
       <c r="A127" s="5" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="B127" s="5"/>
       <c r="C127" s="5"/>
       <c r="D127" s="5"/>
       <c r="E127" s="5"/>
       <c r="F127" s="5" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>850</v>
+        <v>840</v>
       </c>
       <c r="H127" s="5" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
       <c r="I127" s="5"/>
       <c r="J127" s="5"/>
@@ -8843,20 +8947,20 @@
     </row>
     <row r="128" spans="1:14">
       <c r="A128" s="5" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="B128" s="5"/>
       <c r="C128" s="5"/>
       <c r="D128" s="5"/>
       <c r="E128" s="5"/>
       <c r="F128" s="5" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>853</v>
+        <v>843</v>
       </c>
       <c r="H128" s="5" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
       <c r="I128" s="5"/>
       <c r="J128" s="5"/>
@@ -8865,22 +8969,22 @@
       <c r="M128" s="5"/>
       <c r="N128" s="5"/>
     </row>
-    <row r="129" spans="1:14" ht="29">
+    <row r="129" spans="1:14">
       <c r="A129" s="5" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="B129" s="5"/>
       <c r="C129" s="5"/>
       <c r="D129" s="5"/>
       <c r="E129" s="5"/>
       <c r="F129" s="5" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="G129" s="5" t="s">
-        <v>856</v>
+        <v>846</v>
       </c>
       <c r="H129" s="5" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
       <c r="I129" s="5"/>
       <c r="J129" s="5"/>
@@ -8891,20 +8995,20 @@
     </row>
     <row r="130" spans="1:14">
       <c r="A130" s="5" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="B130" s="5"/>
       <c r="C130" s="5"/>
       <c r="D130" s="5"/>
       <c r="E130" s="5"/>
       <c r="F130" s="5" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>859</v>
+        <v>849</v>
       </c>
       <c r="H130" s="5" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
       <c r="I130" s="5"/>
       <c r="J130" s="5"/>
@@ -8915,20 +9019,20 @@
     </row>
     <row r="131" spans="1:14">
       <c r="A131" s="5" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="B131" s="5"/>
       <c r="C131" s="5"/>
       <c r="D131" s="5"/>
       <c r="E131" s="5"/>
       <c r="F131" s="5" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>862</v>
+        <v>852</v>
       </c>
       <c r="H131" s="5" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
       <c r="I131" s="5"/>
       <c r="J131" s="5"/>
@@ -8939,20 +9043,20 @@
     </row>
     <row r="132" spans="1:14">
       <c r="A132" s="5" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="B132" s="5"/>
       <c r="C132" s="5"/>
       <c r="D132" s="5"/>
       <c r="E132" s="5"/>
       <c r="F132" s="5" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>865</v>
+        <v>855</v>
       </c>
       <c r="H132" s="5" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
       <c r="I132" s="5"/>
       <c r="J132" s="5"/>
@@ -8963,20 +9067,20 @@
     </row>
     <row r="133" spans="1:14">
       <c r="A133" s="5" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="B133" s="5"/>
       <c r="C133" s="5"/>
       <c r="D133" s="5"/>
       <c r="E133" s="5"/>
       <c r="F133" s="5" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="G133" s="5" t="s">
-        <v>868</v>
+        <v>858</v>
       </c>
       <c r="H133" s="5" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
       <c r="I133" s="5"/>
       <c r="J133" s="5"/>
@@ -8987,20 +9091,20 @@
     </row>
     <row r="134" spans="1:14">
       <c r="A134" s="5" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="B134" s="5"/>
       <c r="C134" s="5"/>
       <c r="D134" s="5"/>
       <c r="E134" s="5"/>
       <c r="F134" s="5" t="s">
-        <v>870</v>
+        <v>863</v>
       </c>
       <c r="G134" s="5" t="s">
-        <v>871</v>
+        <v>861</v>
       </c>
       <c r="H134" s="5" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
       <c r="I134" s="5"/>
       <c r="J134" s="5"/>
@@ -9011,20 +9115,20 @@
     </row>
     <row r="135" spans="1:14">
       <c r="A135" s="5" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="B135" s="5"/>
       <c r="C135" s="5"/>
       <c r="D135" s="5"/>
       <c r="E135" s="5"/>
       <c r="F135" s="5" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>874</v>
+        <v>864</v>
       </c>
       <c r="H135" s="5" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
       <c r="I135" s="5"/>
       <c r="J135" s="5"/>
@@ -9033,22 +9137,22 @@
       <c r="M135" s="5"/>
       <c r="N135" s="5"/>
     </row>
-    <row r="136" spans="1:14">
+    <row r="136" spans="1:14" ht="29">
       <c r="A136" s="5" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="B136" s="5"/>
       <c r="C136" s="5"/>
       <c r="D136" s="5"/>
       <c r="E136" s="5"/>
       <c r="F136" s="5" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="G136" s="5" t="s">
-        <v>876</v>
+        <v>866</v>
       </c>
       <c r="H136" s="5" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
       <c r="I136" s="5"/>
       <c r="J136" s="5"/>
@@ -9057,22 +9161,22 @@
       <c r="M136" s="5"/>
       <c r="N136" s="5"/>
     </row>
-    <row r="137" spans="1:14">
+    <row r="137" spans="1:14" ht="29">
       <c r="A137" s="5" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
       <c r="D137" s="5"/>
       <c r="E137" s="5"/>
       <c r="F137" s="5" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="H137" s="5" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
       <c r="I137" s="5"/>
       <c r="J137" s="5"/>
@@ -9083,20 +9187,20 @@
     </row>
     <row r="138" spans="1:14" ht="29">
       <c r="A138" s="5" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="B138" s="5"/>
       <c r="C138" s="5"/>
       <c r="D138" s="5"/>
       <c r="E138" s="5"/>
       <c r="F138" s="5" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>882</v>
+        <v>872</v>
       </c>
       <c r="H138" s="5" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
       <c r="I138" s="5"/>
       <c r="J138" s="5"/>
@@ -9105,56 +9209,9 @@
       <c r="M138" s="5"/>
       <c r="N138" s="5"/>
     </row>
-    <row r="139" spans="1:14" ht="29">
-      <c r="A139" s="5" t="s">
-        <v>883</v>
-      </c>
-      <c r="B139" s="5"/>
-      <c r="C139" s="5"/>
-      <c r="D139" s="5"/>
-      <c r="E139" s="5"/>
-      <c r="F139" s="5" t="s">
-        <v>884</v>
-      </c>
-      <c r="G139" s="5" t="s">
-        <v>885</v>
-      </c>
-      <c r="H139" s="5" t="s">
-        <v>826</v>
-      </c>
-      <c r="I139" s="5"/>
-      <c r="J139" s="5"/>
-      <c r="K139" s="5"/>
-      <c r="L139" s="5"/>
-      <c r="M139" s="5"/>
-      <c r="N139" s="5"/>
-    </row>
-    <row r="140" spans="1:14" ht="29">
-      <c r="A140" s="5" t="s">
-        <v>886</v>
-      </c>
-      <c r="B140" s="5"/>
-      <c r="C140" s="5"/>
-      <c r="D140" s="5"/>
-      <c r="E140" s="5"/>
-      <c r="F140" s="5" t="s">
-        <v>887</v>
-      </c>
-      <c r="G140" s="5" t="s">
-        <v>888</v>
-      </c>
-      <c r="H140" s="5" t="s">
-        <v>826</v>
-      </c>
-      <c r="I140" s="5"/>
-      <c r="J140" s="5"/>
-      <c r="K140" s="5"/>
-      <c r="L140" s="5"/>
-      <c r="M140" s="5"/>
-      <c r="N140" s="5"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:N140" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:N138" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9169,7 +9226,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15.5">
       <c r="A1" s="6" t="s">
-        <v>889</v>
+        <v>877</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="15.5">
@@ -9177,27 +9234,27 @@
     </row>
     <row r="3" spans="1:1" ht="15.5">
       <c r="A3" s="7" t="s">
-        <v>890</v>
+        <v>878</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="15.5">
       <c r="A4" s="7" t="s">
-        <v>891</v>
+        <v>879</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="15.5">
       <c r="A5" s="7" t="s">
-        <v>892</v>
+        <v>880</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="15.5">
       <c r="A6" s="7" t="s">
-        <v>893</v>
+        <v>881</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="15.5">
       <c r="A7" s="7" t="s">
-        <v>894</v>
+        <v>882</v>
       </c>
     </row>
   </sheetData>
